--- a/Result/checksun_type/ITO導電基板.xlsx
+++ b/Result/checksun_type/ITO導電基板.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1498.0</t>
+          <t>390.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>65.67</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17.50</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>86.42</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>69.08</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-124.37</t>
+          <t>-120.78</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>83395.5998552822</t>
+          <t>83295.19942196531</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>36258.0</t>
+          <t>9279.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>16891.0</t>
+          <t>18210.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>10195.3</t>
+          <t>10729.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>10437.66</t>
+          <t>8369.26</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>390.5343885617743</t>
+          <t>779.7799219306776</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>3886.84</v>
+        <v>2920.63</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,42 +1177,42 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-7.376381350194507</t>
+          <t>-13.42998910113004</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-8.26694245871643</t>
+          <t>-25.43417574544826</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-3.481449886138677</t>
+          <t>-6.333574654154932</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>108.41</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1623.0</t>
+          <t>1498.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>65.67</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>61.41</t>
+          <t>86.42</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>46.64</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-127.21</t>
+          <t>-124.37</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>83395.5998552822</t>
+          <t>83295.19942196531</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>38343.0</t>
+          <t>36258.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>10310.4</t>
+          <t>16891.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>7058.7</t>
+          <t>10195.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>13160.96</t>
+          <t>10437.66</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-245.1581173895633</t>
+          <t>390.5343885617743</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>2237.72</v>
+        <v>3886.84</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,42 +1608,42 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-7.376381350194507</t>
+          <t>-13.42998910113004</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-8.26694245871643</t>
+          <t>-25.43417574544826</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-3.481449886138677</t>
+          <t>-6.333574654154932</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>108.41</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>1623.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-16.18</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-13.49</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>61.41</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>26.72</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-129.03</t>
+          <t>-127.21</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>83395.5998552822</t>
+          <t>83295.19942196531</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4524.0</t>
+          <t>38343.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>10310.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3638.9</t>
+          <t>7058.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>12810.66</t>
+          <t>13160.96</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-588</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-696.5912702806586</t>
+          <t>-245.1581173895633</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-421.47</v>
+        <v>2237.72</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-15.18</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,42 +2039,42 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-7.376381350194507</t>
+          <t>-13.42998910113004</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-8.26694245871643</t>
+          <t>-25.43417574544826</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-3.481449886138677</t>
+          <t>-6.333574654154932</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>108.41</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-26.87</t>
+          <t>-16.18</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-13.49</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,72 +2302,72 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-11.42</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-128.78</t>
+          <t>-129.03</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>83395.5998552822</t>
+          <t>83295.19942196531</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2647.0</t>
+          <t>4524.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>2718.6</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3717.5</t>
+          <t>3638.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>13031.08</t>
+          <t>12810.66</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-998</t>
+          <t>-588</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-746.6130345102762</t>
+          <t>-696.5912702806586</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-581.8099999999999</v>
+        <v>-421.47</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-16.93</t>
+          <t>-15.18</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,27 +2470,27 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-7.376381350194507</t>
+          <t>-13.42998910113004</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-8.26694245871643</t>
+          <t>-25.43417574544826</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-3.481449886138677</t>
+          <t>-6.333574654154932</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>108.41</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-15.70</t>
+          <t>-26.87</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-15.87</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,67 +2733,67 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>23.73</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>-11.42</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-127.96</t>
+          <t>-128.78</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>83395.5998552822</t>
+          <t>83295.19942196531</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2683.0</t>
+          <t>2647.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>3248.8</t>
+          <t>2718.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3854.0</t>
+          <t>3717.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>13496.96</t>
+          <t>13031.08</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-605</t>
+          <t>-998</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-776.5779763001415</t>
+          <t>-746.6130345102762</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-588.97</v>
+        <v>-581.8099999999999</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-17.51</t>
+          <t>-16.93</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,27 +2901,27 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-7.376381350194507</t>
+          <t>-13.42998910113004</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-8.26694245871643</t>
+          <t>-25.43417574544826</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-3.481449886138677</t>
+          <t>-6.333574654154932</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>108.41</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2991,17 +2991,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>10.92</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-13.67</t>
+          <t>-15.70</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-14.29</t>
+          <t>-15.87</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,17 +3164,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,57 +3184,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>21.52</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-13.09</t>
+          <t>-14.16</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-126.97</t>
+          <t>-127.96</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>83395.5998552822</t>
+          <t>83295.19942196531</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3355.0</t>
+          <t>2683.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>3499.6</t>
+          <t>3248.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4053.7</t>
+          <t>3854.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>13799.2</t>
+          <t>13496.96</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-554</t>
+          <t>-605</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-810.6887149656693</t>
+          <t>-776.5779763001415</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-582.02</v>
+        <v>-588.97</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-15.95</t>
+          <t>-17.51</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,27 +3332,27 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-7.376381350194507</t>
+          <t>-13.42998910113004</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-8.26694245871643</t>
+          <t>-25.43417574544826</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-3.481449886138677</t>
+          <t>-6.333574654154932</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>108.41</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-13.67</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-13.89</t>
+          <t>-14.29</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,67 +3595,67 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.77</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-16.06</t>
+          <t>-13.09</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-126.09</t>
+          <t>-126.97</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>83395.5998552822</t>
+          <t>83295.19942196531</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2041.0</t>
+          <t>3355.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>3807.0</t>
+          <t>3499.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3998.4</t>
+          <t>4053.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>14454.38</t>
+          <t>13799.2</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-191</t>
+          <t>-554</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-852.264046081364</t>
+          <t>-810.6887149656693</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-623.3200000000001</v>
+        <v>-582.02</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-15.56</t>
+          <t>-15.95</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,27 +3763,27 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-7.376381350194507</t>
+          <t>-13.42998910113004</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-8.26694245871643</t>
+          <t>-25.43417574544826</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-3.481449886138677</t>
+          <t>-6.333574654154932</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>108.41</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-14.88</t>
+          <t>-13.89</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.89</t>
+          <t>21.77</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-20.05</t>
+          <t>-16.06</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-125.04</t>
+          <t>-126.09</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>83395.5998552822</t>
+          <t>83295.19942196531</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2867.0</t>
+          <t>2041.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>4227.8</t>
+          <t>3807.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4048.6</t>
+          <t>3998.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>16723.7</t>
+          <t>14454.38</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>-191</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-893.8907697781259</t>
+          <t>-852.264046081364</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-519.26</v>
+        <v>-623.3200000000001</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-16.54</t>
+          <t>-15.56</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,22 +4194,22 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-7.376381350194507</t>
+          <t>-13.42998910113004</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-8.26694245871643</t>
+          <t>-25.43417574544826</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-3.481449886138677</t>
+          <t>-6.333574654154932</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>108.41</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-14.09</t>
+          <t>-14.88</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4457,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4477,57 +4477,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>22.94</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-18.04</t>
+          <t>-20.05</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-123.78</t>
+          <t>-125.04</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>83395.5998552822</t>
+          <t>83295.19942196531</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>5298.0</t>
+          <t>2867.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>4716.4</t>
+          <t>4227.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4361.7</t>
+          <t>4048.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>17648.9</t>
+          <t>16723.7</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>179</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-962.0055353740148</t>
+          <t>-893.8907697781259</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-440.56</v>
+        <v>-519.26</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-16.54</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,27 +4625,27 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-7.376381350194507</t>
+          <t>-13.42998910113004</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-8.26694245871643</t>
+          <t>-25.43417574544826</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-3.481449886138677</t>
+          <t>-6.333574654154932</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>108.41</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.15</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>178.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-12.50</t>
+          <t>-14.09</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,17 +4888,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4908,57 +4908,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.14</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>22.94</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>24.16</t>
+          <t>24.13</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-15.15</t>
+          <t>-18.04</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-122.71</t>
+          <t>-123.78</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>83395.5998552822</t>
+          <t>83295.19942196531</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3937.0</t>
+          <t>5298.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>4459.2</t>
+          <t>4716.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4382.4</t>
+          <t>4361.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>18368.1</t>
+          <t>17648.9</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>354</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1056.81363386356</t>
+          <t>-962.0055353740148</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-572.86</v>
+        <v>-440.56</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-14.20</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,27 +5056,27 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-7.376381350194507</t>
+          <t>-13.42998910113004</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-8.26694245871643</t>
+          <t>-25.43417574544826</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-3.481449886138677</t>
+          <t>-6.333574654154932</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>108.41</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>221.0</t>
+          <t>178.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-12.70</t>
+          <t>-12.50</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>23.18</t>
+          <t>23.07</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>24.22</t>
+          <t>24.16</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-15.98</t>
+          <t>-15.15</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-121.85</t>
+          <t>-122.71</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>83395.5998552822</t>
+          <t>83295.19942196531</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4892.0</t>
+          <t>3937.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>4607.8</t>
+          <t>4459.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4347.6</t>
+          <t>4382.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>19203.82</t>
+          <t>18368.1</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1144.804397055427</t>
+          <t>-1056.81363386356</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-595.59</v>
+        <v>-572.86</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-14.40</t>
+          <t>-14.20</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,27 +5487,27 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-7.376381350194507</t>
+          <t>-13.42998910113004</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-8.26694245871643</t>
+          <t>-25.43417574544826</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-3.481449886138677</t>
+          <t>-6.333574654154932</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>108.41</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1301.232</t>
+          <t>1126.956</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,17 +5649,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -5669,77 +5669,77 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
           <t>2025-09-12 00:00:00</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>2025-09-30 00:00:00</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
       <c r="Q13" t="inlineStr">
         <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>24.8</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>27.45</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>23.45</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-8.74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,72 +5750,72 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>71.74</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>25.56</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>24.19</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>13.70</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-106.48</t>
+          <t>-106.40</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,45 +5840,45 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>214407306.0434154</t>
+          <t>214158872.6986994</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>32929925.0</t>
+          <t>28327621.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>66663290.6</t>
+          <t>64293510.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>54706545.9</t>
+          <t>53134957.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>197755621.26</t>
+          <t>197699079.6</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>11956744</t>
+          <t>11158552</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-17288797.88936103</t>
+          <t>-16773302.76279333</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-13082493.16</v>
+        <v>-13938079.57</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.50</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5923,32 +5923,32 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.8437593938200325</t>
+          <t>1.270367450950751</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-3.348963818077053</t>
+          <t>-1.228489584430356</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>4.027678330928028</t>
+          <t>1.883540353538012</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>144.18</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>9484</t>
+          <t>9428</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1463.862</t>
+          <t>1301.232</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>21.86</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6100,49 +6100,49 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
           <t>2025-09-12 00:00:00</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>2025-09-30 00:00:00</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
       <c r="Q14" t="inlineStr">
         <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
           <t>24.8</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>27.45</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>23.45</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>0</t>
@@ -6150,27 +6150,27 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-6.56</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>73.91</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>71.74</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.58</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>25.82</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>24.14</t>
+          <t>24.19</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>13.70</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-106.70</t>
+          <t>-106.48</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>214407306.0434154</t>
+          <t>214158872.6986994</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>37828336.0</t>
+          <t>32929925.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>70079408.4</t>
+          <t>66663290.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>58159640.7</t>
+          <t>54706545.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>197616845.6</t>
+          <t>197755621.26</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>11919767</t>
+          <t>11956744</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-18053580.56674417</t>
+          <t>-17288797.88936103</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-11886098.98</v>
+        <v>-13082493.16</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6354,32 +6354,32 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.8437593938200325</t>
+          <t>1.270367450950751</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-3.348963818077053</t>
+          <t>-1.228489584430356</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>4.027678330928028</t>
+          <t>1.883540353538012</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>144.18</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>9484</t>
+          <t>9428</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3002.694</t>
+          <t>1463.862</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6531,49 +6531,49 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
           <t>2025-09-12 00:00:00</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>2025-09-30 00:00:00</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
           <t>24.8</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>27.45</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>23.45</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>0</t>
@@ -6581,27 +6581,27 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-4.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,47 +6612,47 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>93.48</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -6662,27 +6662,27 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>24.09</t>
+          <t>24.14</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-107.04</t>
+          <t>-106.70</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>214407306.0434154</t>
+          <t>214158872.6986994</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>78997267.0</t>
+          <t>37828336.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>68268779.4</t>
+          <t>70079408.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>64193506.3</t>
+          <t>58159640.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>197596036.22</t>
+          <t>197616845.6</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>4075273</t>
+          <t>11919767</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-19174940.85612193</t>
+          <t>-18053580.56674417</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-10277290.64</v>
+        <v>-11886098.98</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>30.50</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6785,17 +6785,17 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.8437593938200325</t>
+          <t>1.270367450950751</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-3.348963818077053</t>
+          <t>-1.228489584430356</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>4.027678330928028</t>
+          <t>1.883540353538012</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>144.18</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>9484</t>
+          <t>9428</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5509.073</t>
+          <t>3002.694</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6962,49 +6962,49 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
           <t>2025-09-12 00:00:00</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>2025-09-30 00:00:00</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
           <t>24.8</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>27.45</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>23.45</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>0</t>
@@ -7012,27 +7012,27 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,72 +7043,72 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.48</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.03</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>25.62</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>24.04</t>
+          <t>24.09</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-34.06</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-107.14</t>
+          <t>-107.04</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>214407306.0434154</t>
+          <t>214158872.6986994</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>143384401.0</t>
+          <t>78997267.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>63407579.0</t>
+          <t>68268779.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>64225704.8</t>
+          <t>64193506.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>196763751.52</t>
+          <t>197596036.22</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-818125</t>
+          <t>4075273</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-20792695.44174149</t>
+          <t>-19174940.85612193</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-12022903.81</v>
+        <v>-10277290.64</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.50</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7216,32 +7216,32 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.8437593938200325</t>
+          <t>1.270367450950751</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-3.348963818077053</t>
+          <t>-1.228489584430356</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>4.027678330928028</t>
+          <t>1.883540353538012</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>144.18</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>9484</t>
+          <t>9428</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1642.154</t>
+          <t>5509.073</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-27.26</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7393,49 +7393,49 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
           <t>2025-09-12 00:00:00</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>2025-09-30 00:00:00</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
           <t>24.8</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>27.45</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>23.45</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
       <c r="V17" t="inlineStr">
         <is>
           <t>0</t>
@@ -7443,27 +7443,27 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-10.56</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>15.37</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>25.64</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>24.04</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-107.80</t>
+          <t>-34.06</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-106.53</t>
+          <t>-107.14</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>214407306.0434154</t>
+          <t>214158872.6986994</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>40176524.0</t>
+          <t>143384401.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>41976405.2</t>
+          <t>63407579.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>57706625.4</t>
+          <t>64225704.8</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>194790217.74</t>
+          <t>196763751.52</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-15730220</t>
+          <t>-818125</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-22387203.01197561</t>
+          <t>-20792695.44174149</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-20985868.98</v>
+        <v>-12022903.81</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7647,32 +7647,32 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.8437593938200325</t>
+          <t>1.270367450950751</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-3.348963818077053</t>
+          <t>-1.228489584430356</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>4.027678330928028</t>
+          <t>1.883540353538012</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>144.18</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>9484</t>
+          <t>9428</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2080.109</t>
+          <t>1642.154</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-35.04</t>
+          <t>-27.26</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7824,49 +7824,49 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
           <t>2025-09-12 00:00:00</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>2025-09-30 00:00:00</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
       <c r="Q18" t="inlineStr">
         <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
           <t>24.8</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>27.45</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>23.45</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
       <c r="V18" t="inlineStr">
         <is>
           <t>0</t>
@@ -7874,27 +7874,27 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-11.84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,67 +7905,67 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>9.62</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>15.37</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.64</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-184.26</t>
+          <t>-107.80</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-104.77</t>
+          <t>-106.53</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>214407306.0434154</t>
+          <t>214158872.6986994</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>50010514.0</t>
+          <t>40176524.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>42749801.2</t>
+          <t>41976405.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>65809171.5</t>
+          <t>57706625.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>195892656.92</t>
+          <t>194790217.74</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-23059370</t>
+          <t>-15730220</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-22641991.01703074</t>
+          <t>-22387203.01197561</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-21982622.81</v>
+        <v>-20985868.98</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8078,32 +8078,32 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.8437593938200325</t>
+          <t>1.270367450950751</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-3.348963818077053</t>
+          <t>-1.228489584430356</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>4.027678330928028</t>
+          <t>1.883540353538012</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>144.18</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>9484</t>
+          <t>9428</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1195.841</t>
+          <t>2080.109</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-32.74</t>
+          <t>-35.04</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8255,49 +8255,49 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
           <t>2025-09-12 00:00:00</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>2025-09-30 00:00:00</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
       <c r="Q19" t="inlineStr">
         <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
           <t>24.8</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>27.45</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>23.45</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
       <c r="V19" t="inlineStr">
         <is>
           <t>0</t>
@@ -8305,27 +8305,27 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-12.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,42 +8336,42 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>9.62</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -8381,32 +8381,32 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>25.62</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-379.56</t>
+          <t>-184.26</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-102.57</t>
+          <t>-104.77</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>214407306.0434154</t>
+          <t>214158872.6986994</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>28775191.0</t>
+          <t>50010514.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>46239873.0</t>
+          <t>42749801.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>68746635.5</t>
+          <t>65809171.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>195726576.28</t>
+          <t>195892656.92</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-22506762</t>
+          <t>-23059370</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-22761876.14531295</t>
+          <t>-22641991.01703074</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-23675104.96</v>
+        <v>-21982622.81</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8509,22 +8509,22 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.8437593938200325</t>
+          <t>1.270367450950751</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-3.348963818077053</t>
+          <t>-1.228489584430356</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>4.027678330928028</t>
+          <t>1.883540353538012</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>144.18</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>9484</t>
+          <t>9428</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8594,17 +8594,17 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2295.597</t>
+          <t>1195.841</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-26.69</t>
+          <t>-32.74</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8686,49 +8686,49 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
           <t>2025-09-12 00:00:00</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>2025-09-30 00:00:00</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
           <t>24.8</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>27.45</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>23.45</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
       <c r="V20" t="inlineStr">
         <is>
           <t>0</t>
@@ -8736,27 +8736,27 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-12.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.31</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-7630.45</t>
+          <t>-379.56</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-100.13</t>
+          <t>-102.57</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>214407306.0434154</t>
+          <t>214158872.6986994</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>54691265.0</t>
+          <t>28775191.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>60118233.2</t>
+          <t>46239873.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>82004725.1</t>
+          <t>68746635.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>195747548.06</t>
+          <t>195726576.28</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-21886491</t>
+          <t>-22506762</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-22595834.54184929</t>
+          <t>-22761876.14531295</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-22972183.97</v>
+        <v>-23675104.96</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8940,22 +8940,22 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.8437593938200325</t>
+          <t>1.270367450950751</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-3.348963818077053</t>
+          <t>-1.228489584430356</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>4.027678330928028</t>
+          <t>1.883540353538012</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>144.18</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>9484</t>
+          <t>9428</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9025,17 +9025,17 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1475.722</t>
+          <t>2295.597</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-46.47</t>
+          <t>-26.69</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9117,49 +9117,49 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
           <t>2025-09-12 00:00:00</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>2025-09-30 00:00:00</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
       <c r="Q21" t="inlineStr">
         <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
           <t>24.8</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>27.45</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>23.45</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
       <c r="V21" t="inlineStr">
         <is>
           <t>0</t>
@@ -9167,27 +9167,27 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-10.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,17 +9198,17 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -9218,57 +9218,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-4.44</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-392.62</t>
+          <t>-7630.45</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-97.62</t>
+          <t>-100.13</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>214407306.0434154</t>
+          <t>214158872.6986994</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>36228532.0</t>
+          <t>54691265.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>65043830.6</t>
+          <t>60118233.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>121499891.8</t>
+          <t>82004725.1</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>195285241.26</t>
+          <t>195747548.06</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-56456061</t>
+          <t>-21886491</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-22527407.37313884</t>
+          <t>-22595834.54184929</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-23924298.19</v>
+        <v>-22972183.97</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>22.50</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.8437593938200325</t>
+          <t>1.270367450950751</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-3.348963818077053</t>
+          <t>-1.228489584430356</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>4.027678330928028</t>
+          <t>1.883540353538012</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>144.18</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>9484</t>
+          <t>9428</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1778.967</t>
+          <t>1475.722</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-41.98</t>
+          <t>-46.47</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9548,49 +9548,49 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
           <t>2025-09-12 00:00:00</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>2025-09-30 00:00:00</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
       <c r="Q22" t="inlineStr">
         <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
           <t>24.8</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>27.45</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>23.45</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
       <c r="V22" t="inlineStr">
         <is>
           <t>0</t>
@@ -9598,27 +9598,27 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-9.47</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-4.44</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>25.24</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>25.46</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>23.69</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-192.32</t>
+          <t>-392.62</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-95.29</t>
+          <t>-97.62</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>214407306.0434154</t>
+          <t>214158872.6986994</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>44043504.0</t>
+          <t>36228532.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>73436845.6</t>
+          <t>65043830.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>126573520.6</t>
+          <t>121499891.8</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>195283806.46</t>
+          <t>195285241.26</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-53136675</t>
+          <t>-56456061</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-22273427.22410453</t>
+          <t>-22527407.37313884</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-22451872.18</v>
+        <v>-23924298.19</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>22.50</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9802,17 +9802,17 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.8437593938200325</t>
+          <t>1.270367450950751</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-3.348963818077053</t>
+          <t>-1.228489584430356</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>4.027678330928028</t>
+          <t>1.883540353538012</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>144.18</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>9484</t>
+          <t>9428</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2747.054</t>
+          <t>1778.967</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-29.43</t>
+          <t>-41.98</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9979,49 +9979,49 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
           <t>2025-09-12 00:00:00</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>2025-09-30 00:00:00</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
       <c r="Q23" t="inlineStr">
         <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
           <t>24.8</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>27.45</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>23.45</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>22.55</t>
-        </is>
-      </c>
       <c r="V23" t="inlineStr">
         <is>
           <t>0</t>
@@ -10029,27 +10029,27 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-11.84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.12</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>25.69</t>
+          <t>25.24</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>25.46</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>23.69</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-128.24</t>
+          <t>-192.32</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-93.03</t>
+          <t>-95.29</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>214407306.0434154</t>
+          <t>214158872.6986994</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>67460873.0</t>
+          <t>44043504.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>88868541.8</t>
+          <t>73436845.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>125926929.2</t>
+          <t>126573520.6</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>195112349.8</t>
+          <t>195283806.46</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-37058387</t>
+          <t>-53136675</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-22240982.68608989</t>
+          <t>-22273427.22410453</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-20383872.31</v>
+        <v>-22451872.18</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10233,22 +10233,22 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.8437593938200325</t>
+          <t>1.270367450950751</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-3.348963818077053</t>
+          <t>-1.228489584430356</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>4.027678330928028</t>
+          <t>1.883540353538012</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>144.18</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>9484</t>
+          <t>9428</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/ITO導電基板.xlsx
+++ b/Result/checksun_type/ITO導電基板.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>390.0</t>
+          <t>426.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>75.73</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>426</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>91.82</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>69.08</t>
+          <t>87.14</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-120.78</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>83295.19942196531</t>
+          <t>83196.71428571429</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>18210.2</t>
+          <t>19686.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>10729.5</t>
+          <t>11202.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>8369.26</t>
+          <t>8102.12</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>779.7799219306776</t>
+          <t>1002.520030170422</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>2920.63</v>
+        <v>2227.59</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1267,17 +1267,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>23.15</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>23.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1498.0</t>
+          <t>390.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>65.67</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>426</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>86.42</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>69.08</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-124.37</t>
+          <t>-120.78</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>83295.19942196531</t>
+          <t>83196.71428571429</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>36258.0</t>
+          <t>9279.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>16891.0</t>
+          <t>18210.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>10195.3</t>
+          <t>10729.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>10437.66</t>
+          <t>8369.26</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>390.5343885617743</t>
+          <t>779.7799219306776</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>3886.84</v>
+        <v>2920.63</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1623.0</t>
+          <t>1498.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>65.67</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>426</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>61.41</t>
+          <t>86.42</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>46.64</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-127.21</t>
+          <t>-124.37</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>83295.19942196531</t>
+          <t>83196.71428571429</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>38343.0</t>
+          <t>36258.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>10310.4</t>
+          <t>16891.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>7058.7</t>
+          <t>10195.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>13160.96</t>
+          <t>10437.66</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-245.1581173895633</t>
+          <t>390.5343885617743</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>2237.72</v>
+        <v>3886.84</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>1623.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-16.18</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-13.49</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>426</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>61.41</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>26.72</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-129.03</t>
+          <t>-127.21</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>83295.19942196531</t>
+          <t>83196.71428571429</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4524.0</t>
+          <t>38343.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>10310.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3638.9</t>
+          <t>7058.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>12810.66</t>
+          <t>13160.96</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-588</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-696.5912702806586</t>
+          <t>-245.1581173895633</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-421.47</v>
+        <v>2237.72</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-15.18</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-26.87</t>
+          <t>-16.18</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-13.49</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,72 +2733,72 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>426</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-11.42</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-128.78</t>
+          <t>-129.03</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>83295.19942196531</t>
+          <t>83196.71428571429</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2647.0</t>
+          <t>4524.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>2718.6</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3717.5</t>
+          <t>3638.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>13031.08</t>
+          <t>12810.66</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-998</t>
+          <t>-588</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-746.6130345102762</t>
+          <t>-696.5912702806586</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-581.8099999999999</v>
+        <v>-421.47</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-16.93</t>
+          <t>-15.18</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>10.92</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-15.70</t>
+          <t>-26.87</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-15.87</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,67 +3164,67 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>426</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>23.73</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>-11.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-127.96</t>
+          <t>-128.78</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>83295.19942196531</t>
+          <t>83196.71428571429</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2683.0</t>
+          <t>2647.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>3248.8</t>
+          <t>2718.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3854.0</t>
+          <t>3717.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>13496.96</t>
+          <t>13031.08</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-605</t>
+          <t>-998</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-776.5779763001415</t>
+          <t>-746.6130345102762</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-588.97</v>
+        <v>-581.8099999999999</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-17.51</t>
+          <t>-16.93</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-13.67</t>
+          <t>-15.70</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-14.29</t>
+          <t>-15.87</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,17 +3595,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>426</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3615,57 +3615,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>21.52</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-13.09</t>
+          <t>-14.16</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-126.97</t>
+          <t>-127.96</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>83295.19942196531</t>
+          <t>83196.71428571429</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3355.0</t>
+          <t>2683.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>3499.6</t>
+          <t>3248.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4053.7</t>
+          <t>3854.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>13799.2</t>
+          <t>13496.96</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-554</t>
+          <t>-605</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-810.6887149656693</t>
+          <t>-776.5779763001415</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-582.02</v>
+        <v>-588.97</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-15.95</t>
+          <t>-17.51</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-13.67</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-13.89</t>
+          <t>-14.29</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,67 +4026,67 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>426</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.77</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-16.06</t>
+          <t>-13.09</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-126.09</t>
+          <t>-126.97</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>83295.19942196531</t>
+          <t>83196.71428571429</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2041.0</t>
+          <t>3355.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>3807.0</t>
+          <t>3499.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>3998.4</t>
+          <t>4053.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>14454.38</t>
+          <t>13799.2</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-191</t>
+          <t>-554</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-852.264046081364</t>
+          <t>-810.6887149656693</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-623.3200000000001</v>
+        <v>-582.02</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-15.56</t>
+          <t>-15.95</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>7.86</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-14.88</t>
+          <t>-13.89</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>426</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.89</t>
+          <t>21.77</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-20.05</t>
+          <t>-16.06</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-125.04</t>
+          <t>-126.09</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>83295.19942196531</t>
+          <t>83196.71428571429</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2867.0</t>
+          <t>2041.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>4227.8</t>
+          <t>3807.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4048.6</t>
+          <t>3998.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>16723.7</t>
+          <t>14454.38</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>-191</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-893.8907697781259</t>
+          <t>-852.264046081364</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-519.26</v>
+        <v>-623.3200000000001</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-16.54</t>
+          <t>-15.56</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -4720,12 +4720,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-14.09</t>
+          <t>-14.88</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>426</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4908,57 +4908,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>22.94</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-18.04</t>
+          <t>-20.05</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-123.78</t>
+          <t>-125.04</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>83295.19942196531</t>
+          <t>83196.71428571429</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>5298.0</t>
+          <t>2867.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>4716.4</t>
+          <t>4227.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4361.7</t>
+          <t>4048.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>17648.9</t>
+          <t>16723.7</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>179</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-962.0055353740148</t>
+          <t>-893.8907697781259</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-440.56</v>
+        <v>-519.26</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-16.54</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.15</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>178.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-12.50</t>
+          <t>-14.09</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,17 +5319,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>426</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.14</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>22.94</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>24.16</t>
+          <t>24.13</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-15.15</t>
+          <t>-18.04</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-122.71</t>
+          <t>-123.78</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>83295.19942196531</t>
+          <t>83196.71428571429</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3937.0</t>
+          <t>5298.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>4459.2</t>
+          <t>4716.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4382.4</t>
+          <t>4361.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>18368.1</t>
+          <t>17648.9</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>354</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1056.81363386356</t>
+          <t>-962.0055353740148</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-572.86</v>
+        <v>-440.56</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-14.20</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1126.956</t>
+          <t>1604.993</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,74 +5634,74 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-0.8</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-18.78</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>24.9</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>21.00</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
         <is>
           <t>24.9</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
       <c r="T13" t="inlineStr">
         <is>
           <t>24.8</t>
@@ -5714,14 +5714,14 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>-4.22</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="X13" t="inlineStr">
         <is>
           <t>-9.29</t>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>25.56</t>
+          <t>25.44</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>25.96</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>-27.44</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-106.40</t>
+          <t>-106.87</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>214158872.6986994</t>
+          <t>213933659.5497835</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>28327621.0</t>
+          <t>38724107.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>64293510.0</t>
+          <t>43361451.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>53134957.6</t>
+          <t>53384515.1</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>197699079.6</t>
+          <t>197488634.64</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>11158552</t>
+          <t>-10023063</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-16773302.76279333</t>
+          <t>-16255687.20075533</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-13938079.57</v>
+        <v>-13408801.61</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>24.50</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>137.36</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1301.232</t>
+          <t>1126.956</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,22 +6075,22 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-4.4</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,72 +6181,72 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>71.74</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>25.56</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>24.19</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>13.70</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-106.48</t>
+          <t>-106.40</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,45 +6271,45 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>214158872.6986994</t>
+          <t>213933659.5497835</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>32929925.0</t>
+          <t>28327621.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>66663290.6</t>
+          <t>64293510.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>54706545.9</t>
+          <t>53134957.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>197755621.26</t>
+          <t>197699079.6</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>11956744</t>
+          <t>11158552</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-17288797.88936103</t>
+          <t>-16773302.76279333</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-13082493.16</v>
+        <v>-13938079.57</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.50</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6369,17 +6369,17 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>137.36</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1463.862</t>
+          <t>1301.232</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>21.86</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>73.91</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>71.74</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.58</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>25.82</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>24.14</t>
+          <t>24.19</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>13.70</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-106.70</t>
+          <t>-106.48</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>214158872.6986994</t>
+          <t>213933659.5497835</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>37828336.0</t>
+          <t>32929925.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>70079408.4</t>
+          <t>66663290.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>58159640.7</t>
+          <t>54706545.9</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>197616845.6</t>
+          <t>197755621.26</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>11919767</t>
+          <t>11956744</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-18053580.56674417</t>
+          <t>-17288797.88936103</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-11886098.98</v>
+        <v>-13082493.16</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6800,17 +6800,17 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>137.36</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3002.694</t>
+          <t>1463.862</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,47 +7043,47 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>93.48</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -7093,27 +7093,27 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>24.09</t>
+          <t>24.14</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-107.04</t>
+          <t>-106.70</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>214158872.6986994</t>
+          <t>213933659.5497835</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>78997267.0</t>
+          <t>37828336.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>68268779.4</t>
+          <t>70079408.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>64193506.3</t>
+          <t>58159640.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>197596036.22</t>
+          <t>197616845.6</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>4075273</t>
+          <t>11919767</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-19174940.85612193</t>
+          <t>-18053580.56674417</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-10277290.64</v>
+        <v>-11886098.98</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>30.50</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>137.36</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5509.073</t>
+          <t>3002.694</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,72 +7474,72 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.48</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.03</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>25.62</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>24.04</t>
+          <t>24.09</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-34.06</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-107.14</t>
+          <t>-107.04</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>214158872.6986994</t>
+          <t>213933659.5497835</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>143384401.0</t>
+          <t>78997267.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>63407579.0</t>
+          <t>68268779.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>64225704.8</t>
+          <t>64193506.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>196763751.52</t>
+          <t>197596036.22</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-818125</t>
+          <t>4075273</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-20792695.44174149</t>
+          <t>-19174940.85612193</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-12022903.81</v>
+        <v>-10277290.64</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.50</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7662,17 +7662,17 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>137.36</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1642.154</t>
+          <t>5509.073</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>-10.06</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-27.26</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>15.37</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>25.64</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>24.04</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-107.80</t>
+          <t>-34.06</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-106.53</t>
+          <t>-107.14</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>214158872.6986994</t>
+          <t>213933659.5497835</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>40176524.0</t>
+          <t>143384401.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>41976405.2</t>
+          <t>63407579.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>57706625.4</t>
+          <t>64225704.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>194790217.74</t>
+          <t>196763751.52</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-15730220</t>
+          <t>-818125</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-22387203.01197561</t>
+          <t>-20792695.44174149</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-20985868.98</v>
+        <v>-12022903.81</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8093,17 +8093,17 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>137.36</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2080.109</t>
+          <t>1642.154</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-35.04</t>
+          <t>-27.26</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,67 +8336,67 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>9.62</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>15.37</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.64</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-184.26</t>
+          <t>-107.80</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-104.77</t>
+          <t>-106.53</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>214158872.6986994</t>
+          <t>213933659.5497835</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>50010514.0</t>
+          <t>40176524.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>42749801.2</t>
+          <t>41976405.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>65809171.5</t>
+          <t>57706625.4</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>195892656.92</t>
+          <t>194790217.74</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-23059370</t>
+          <t>-15730220</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-22641991.01703074</t>
+          <t>-22387203.01197561</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-21982622.81</v>
+        <v>-20985868.98</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,17 +8524,17 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>137.36</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1195.841</t>
+          <t>2080.109</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-32.74</t>
+          <t>-35.04</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,42 +8767,42 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>9.62</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
@@ -8812,32 +8812,32 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>25.62</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-379.56</t>
+          <t>-184.26</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-102.57</t>
+          <t>-104.77</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>214158872.6986994</t>
+          <t>213933659.5497835</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>28775191.0</t>
+          <t>50010514.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>46239873.0</t>
+          <t>42749801.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>68746635.5</t>
+          <t>65809171.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>195726576.28</t>
+          <t>195892656.92</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-22506762</t>
+          <t>-23059370</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-22761876.14531295</t>
+          <t>-22641991.01703074</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-23675104.96</v>
+        <v>-21982622.81</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>137.36</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9025,17 +9025,17 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2295.597</t>
+          <t>1195.841</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-26.69</t>
+          <t>-32.74</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.31</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-7630.45</t>
+          <t>-379.56</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-100.13</t>
+          <t>-102.57</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>214158872.6986994</t>
+          <t>213933659.5497835</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>54691265.0</t>
+          <t>28775191.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>60118233.2</t>
+          <t>46239873.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>82004725.1</t>
+          <t>68746635.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>195747548.06</t>
+          <t>195726576.28</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-21886491</t>
+          <t>-22506762</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-22595834.54184929</t>
+          <t>-22761876.14531295</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-22972183.97</v>
+        <v>-23675104.96</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>137.36</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9456,17 +9456,17 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1475.722</t>
+          <t>2295.597</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-46.47</t>
+          <t>-26.69</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,17 +9629,17 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -9649,57 +9649,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.44</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-392.62</t>
+          <t>-7630.45</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-97.62</t>
+          <t>-100.13</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>214158872.6986994</t>
+          <t>213933659.5497835</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>36228532.0</t>
+          <t>54691265.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>65043830.6</t>
+          <t>60118233.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>121499891.8</t>
+          <t>82004725.1</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>195285241.26</t>
+          <t>195747548.06</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-56456061</t>
+          <t>-21886491</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-22527407.37313884</t>
+          <t>-22595834.54184929</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-23924298.19</v>
+        <v>-22972183.97</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>22.50</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>137.36</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1778.967</t>
+          <t>1475.722</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-41.98</t>
+          <t>-46.47</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-4.44</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>25.24</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>25.46</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>23.69</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-192.32</t>
+          <t>-392.62</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-95.29</t>
+          <t>-97.62</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>214158872.6986994</t>
+          <t>213933659.5497835</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>44043504.0</t>
+          <t>36228532.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>73436845.6</t>
+          <t>65043830.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>126573520.6</t>
+          <t>121499891.8</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>195283806.46</t>
+          <t>195285241.26</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-53136675</t>
+          <t>-56456061</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-22273427.22410453</t>
+          <t>-22527407.37313884</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-22451872.18</v>
+        <v>-23924298.19</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>22.50</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>137.36</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/ITO導電基板.xlsx
+++ b/Result/checksun_type/ITO導電基板.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>426.0</t>
+          <t>293.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>75.73</t>
+          <t>73.69</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>91.82</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>22.43</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>87.14</t>
+          <t>92.50</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-113.86</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>83196.71428571429</t>
+          <t>83091.50144092219</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>19686.8</t>
+          <t>20139.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>11202.7</t>
+          <t>11594.6</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>8102.12</t>
+          <t>7648.36</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>1002.520030170422</t>
+          <t>1070.358956124564</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>2227.59</v>
+        <v>1443.47</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>107.05</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>390.0</t>
+          <t>426.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>75.73</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>91.82</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>69.08</t>
+          <t>87.14</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-120.78</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>83196.71428571429</t>
+          <t>83091.50144092219</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>18210.2</t>
+          <t>19686.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>10729.5</t>
+          <t>11202.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>8369.26</t>
+          <t>8102.12</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>779.7799219306776</t>
+          <t>1002.520030170422</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>2920.63</v>
+        <v>2227.59</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>107.05</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1698,17 +1698,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>23.15</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>23.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1498.0</t>
+          <t>390.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>65.67</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>86.42</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>69.08</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-124.37</t>
+          <t>-120.78</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>83196.71428571429</t>
+          <t>83091.50144092219</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>36258.0</t>
+          <t>9279.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>16891.0</t>
+          <t>18210.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>10195.3</t>
+          <t>10729.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>10437.66</t>
+          <t>8369.26</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>390.5343885617743</t>
+          <t>779.7799219306776</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>3886.84</v>
+        <v>2920.63</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>107.05</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1623.0</t>
+          <t>1498.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>65.67</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>61.41</t>
+          <t>86.42</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>46.64</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-127.21</t>
+          <t>-124.37</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>83196.71428571429</t>
+          <t>83091.50144092219</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>38343.0</t>
+          <t>36258.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>10310.4</t>
+          <t>16891.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>7058.7</t>
+          <t>10195.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>13160.96</t>
+          <t>10437.66</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-245.1581173895633</t>
+          <t>390.5343885617743</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>2237.72</v>
+        <v>3886.84</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>107.05</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>1623.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-16.18</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-13.49</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>61.41</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>26.72</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-129.03</t>
+          <t>-127.21</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>83196.71428571429</t>
+          <t>83091.50144092219</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4524.0</t>
+          <t>38343.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>10310.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3638.9</t>
+          <t>7058.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>12810.66</t>
+          <t>13160.96</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-588</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-696.5912702806586</t>
+          <t>-245.1581173895633</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-421.47</v>
+        <v>2237.72</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-15.18</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>107.05</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-26.87</t>
+          <t>-16.18</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-13.49</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,72 +3164,72 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-11.42</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-128.78</t>
+          <t>-129.03</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>83196.71428571429</t>
+          <t>83091.50144092219</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2647.0</t>
+          <t>4524.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>2718.6</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3717.5</t>
+          <t>3638.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>13031.08</t>
+          <t>12810.66</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-998</t>
+          <t>-588</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-746.6130345102762</t>
+          <t>-696.5912702806586</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-581.8099999999999</v>
+        <v>-421.47</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-16.93</t>
+          <t>-15.18</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>107.05</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-15.70</t>
+          <t>-26.87</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-15.87</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,67 +3595,67 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>23.73</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>-11.42</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-127.96</t>
+          <t>-128.78</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>83196.71428571429</t>
+          <t>83091.50144092219</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2683.0</t>
+          <t>2647.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>3248.8</t>
+          <t>2718.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3854.0</t>
+          <t>3717.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>13496.96</t>
+          <t>13031.08</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-605</t>
+          <t>-998</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-776.5779763001415</t>
+          <t>-746.6130345102762</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-588.97</v>
+        <v>-581.8099999999999</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-17.51</t>
+          <t>-16.93</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>107.05</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3853,17 +3853,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>7.83</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-13.67</t>
+          <t>-15.70</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-14.29</t>
+          <t>-15.87</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,17 +4026,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4046,57 +4046,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>21.52</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-13.09</t>
+          <t>-14.16</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-126.97</t>
+          <t>-127.96</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>83196.71428571429</t>
+          <t>83091.50144092219</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3355.0</t>
+          <t>2683.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>3499.6</t>
+          <t>3248.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4053.7</t>
+          <t>3854.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>13799.2</t>
+          <t>13496.96</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-554</t>
+          <t>-605</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-810.6887149656693</t>
+          <t>-776.5779763001415</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-582.02</v>
+        <v>-588.97</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-15.95</t>
+          <t>-17.51</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>107.05</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7.86</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-13.67</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-13.89</t>
+          <t>-14.29</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,67 +4457,67 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.77</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-16.06</t>
+          <t>-13.09</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-126.09</t>
+          <t>-126.97</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>83196.71428571429</t>
+          <t>83091.50144092219</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2041.0</t>
+          <t>3355.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>3807.0</t>
+          <t>3499.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>3998.4</t>
+          <t>4053.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>14454.38</t>
+          <t>13799.2</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-191</t>
+          <t>-554</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-852.264046081364</t>
+          <t>-810.6887149656693</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-623.3200000000001</v>
+        <v>-582.02</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-15.56</t>
+          <t>-15.95</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>107.05</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-14.88</t>
+          <t>-13.89</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.89</t>
+          <t>21.77</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-20.05</t>
+          <t>-16.06</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-125.04</t>
+          <t>-126.09</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>83196.71428571429</t>
+          <t>83091.50144092219</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2867.0</t>
+          <t>2041.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>4227.8</t>
+          <t>3807.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4048.6</t>
+          <t>3998.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>16723.7</t>
+          <t>14454.38</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>-191</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-893.8907697781259</t>
+          <t>-852.264046081364</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-519.26</v>
+        <v>-623.3200000000001</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-16.54</t>
+          <t>-15.56</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>107.05</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-14.09</t>
+          <t>-14.88</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>22.94</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-18.04</t>
+          <t>-20.05</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-123.78</t>
+          <t>-125.04</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>83196.71428571429</t>
+          <t>83091.50144092219</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>5298.0</t>
+          <t>2867.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>4716.4</t>
+          <t>4227.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4361.7</t>
+          <t>4048.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>17648.9</t>
+          <t>16723.7</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>179</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-962.0055353740148</t>
+          <t>-893.8907697781259</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-440.56</v>
+        <v>-519.26</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-16.54</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>107.05</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.15</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1604.993</t>
+          <t>1646.332</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,72 +5634,72 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-3.38</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-31.86</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
           <t>23.85</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-0.8</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>-18.78</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5765,62 +5765,62 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>13.77</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>25.44</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>25.96</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-27.44</t>
+          <t>-54.01</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-106.87</t>
+          <t>-107.94</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,45 +5840,45 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>213933659.5497835</t>
+          <t>213708809.176513</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>38724107.0</t>
+          <t>38591667.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>43361451.2</t>
+          <t>35280331.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>53384515.1</t>
+          <t>51774555.3</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>197488634.64</t>
+          <t>196053683.56</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-10023063</t>
+          <t>-16494224</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-16255687.20075533</t>
+          <t>-15710661.47745765</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-13408801.61</v>
+        <v>-12713020</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>137.36</t>
+          <t>134.41</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>8784</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1126.956</t>
+          <t>1604.993</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,74 +6065,74 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-2.8</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-3.38</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-18.78</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>24.9</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>-4.4</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-0.8</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>21.00</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>24.9</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
       <c r="T14" t="inlineStr">
         <is>
           <t>24.8</t>
@@ -6145,14 +6145,14 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>-4.22</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>4.40</t>
-        </is>
-      </c>
       <c r="X14" t="inlineStr">
         <is>
           <t>-9.29</t>
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>25.56</t>
+          <t>25.44</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>25.96</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>-27.44</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-106.40</t>
+          <t>-106.87</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>213933659.5497835</t>
+          <t>213708809.176513</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>28327621.0</t>
+          <t>38724107.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>64293510.0</t>
+          <t>43361451.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>53134957.6</t>
+          <t>53384515.1</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>197699079.6</t>
+          <t>197488634.64</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>11158552</t>
+          <t>-10023063</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-16773302.76279333</t>
+          <t>-16255687.20075533</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-13938079.57</v>
+        <v>-13408801.61</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>24.50</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>137.36</t>
+          <t>134.41</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>8784</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1301.232</t>
+          <t>1126.956</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,22 +6506,22 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,72 +6612,72 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>71.74</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>25.56</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>24.19</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>13.70</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-106.48</t>
+          <t>-106.40</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,45 +6702,45 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>213933659.5497835</t>
+          <t>213708809.176513</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>32929925.0</t>
+          <t>28327621.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>66663290.6</t>
+          <t>64293510.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>54706545.9</t>
+          <t>53134957.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>197755621.26</t>
+          <t>197699079.6</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>11956744</t>
+          <t>11158552</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-17288797.88936103</t>
+          <t>-16773302.76279333</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-13082493.16</v>
+        <v>-13938079.57</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.50</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6800,17 +6800,17 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>137.36</t>
+          <t>134.41</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>8784</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1463.862</t>
+          <t>1301.232</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-7.55</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>21.86</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>73.91</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>71.74</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.58</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>25.82</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>24.14</t>
+          <t>24.19</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>13.70</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-106.70</t>
+          <t>-106.48</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>213933659.5497835</t>
+          <t>213708809.176513</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>37828336.0</t>
+          <t>32929925.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>70079408.4</t>
+          <t>66663290.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>58159640.7</t>
+          <t>54706545.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>197616845.6</t>
+          <t>197755621.26</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>11919767</t>
+          <t>11956744</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-18053580.56674417</t>
+          <t>-17288797.88936103</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-11886098.98</v>
+        <v>-13082493.16</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7231,17 +7231,17 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>137.36</t>
+          <t>134.41</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>8784</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3002.694</t>
+          <t>1463.862</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-10.56</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,47 +7474,47 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>93.48</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -7524,27 +7524,27 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>24.09</t>
+          <t>24.14</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-107.04</t>
+          <t>-106.70</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>213933659.5497835</t>
+          <t>213708809.176513</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>78997267.0</t>
+          <t>37828336.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>68268779.4</t>
+          <t>70079408.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>64193506.3</t>
+          <t>58159640.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>197596036.22</t>
+          <t>197616845.6</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>4075273</t>
+          <t>11919767</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-19174940.85612193</t>
+          <t>-18053580.56674417</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-10277290.64</v>
+        <v>-11886098.98</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>30.50</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>137.36</t>
+          <t>134.41</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>8784</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5509.073</t>
+          <t>3002.694</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-10.06</t>
+          <t>-12.5</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,72 +7905,72 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.48</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.03</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>25.62</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>24.04</t>
+          <t>24.09</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-34.06</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-107.14</t>
+          <t>-107.04</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>213933659.5497835</t>
+          <t>213708809.176513</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>143384401.0</t>
+          <t>78997267.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>63407579.0</t>
+          <t>68268779.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>64225704.8</t>
+          <t>64193506.3</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>196763751.52</t>
+          <t>197596036.22</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-818125</t>
+          <t>4075273</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-20792695.44174149</t>
+          <t>-19174940.85612193</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-12022903.81</v>
+        <v>-10277290.64</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.50</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8093,17 +8093,17 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>137.36</t>
+          <t>134.41</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>8784</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1642.154</t>
+          <t>5509.073</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-13.15</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-27.26</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>15.37</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>25.64</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>24.04</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-107.80</t>
+          <t>-34.06</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-106.53</t>
+          <t>-107.14</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>213933659.5497835</t>
+          <t>213708809.176513</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>40176524.0</t>
+          <t>143384401.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>41976405.2</t>
+          <t>63407579.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>57706625.4</t>
+          <t>64225704.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>194790217.74</t>
+          <t>196763751.52</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-15730220</t>
+          <t>-818125</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-22387203.01197561</t>
+          <t>-20792695.44174149</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-20985868.98</v>
+        <v>-12022903.81</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,17 +8524,17 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>137.36</t>
+          <t>134.41</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>8784</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2080.109</t>
+          <t>1642.154</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-35.04</t>
+          <t>-27.26</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,67 +8767,67 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>9.62</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>15.37</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.64</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-184.26</t>
+          <t>-107.80</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -8837,7 +8837,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-104.77</t>
+          <t>-106.53</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>213933659.5497835</t>
+          <t>213708809.176513</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>50010514.0</t>
+          <t>40176524.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>42749801.2</t>
+          <t>41976405.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>65809171.5</t>
+          <t>57706625.4</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>195892656.92</t>
+          <t>194790217.74</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-23059370</t>
+          <t>-15730220</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-22641991.01703074</t>
+          <t>-22387203.01197561</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-21982622.81</v>
+        <v>-20985868.98</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8955,17 +8955,17 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>137.36</t>
+          <t>134.41</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>8784</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1195.841</t>
+          <t>2080.109</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-32.74</t>
+          <t>-35.04</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,42 +9198,42 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>9.62</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
@@ -9243,32 +9243,32 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>25.62</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-379.56</t>
+          <t>-184.26</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-102.57</t>
+          <t>-104.77</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>213933659.5497835</t>
+          <t>213708809.176513</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>28775191.0</t>
+          <t>50010514.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>46239873.0</t>
+          <t>42749801.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>68746635.5</t>
+          <t>65809171.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>195726576.28</t>
+          <t>195892656.92</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-22506762</t>
+          <t>-23059370</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-22761876.14531295</t>
+          <t>-22641991.01703074</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-23675104.96</v>
+        <v>-21982622.81</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>137.36</t>
+          <t>134.41</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>8784</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9456,17 +9456,17 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2295.597</t>
+          <t>1195.841</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-26.69</t>
+          <t>-32.74</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.31</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-7630.45</t>
+          <t>-379.56</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-100.13</t>
+          <t>-102.57</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>213933659.5497835</t>
+          <t>213708809.176513</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>54691265.0</t>
+          <t>28775191.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>60118233.2</t>
+          <t>46239873.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>82004725.1</t>
+          <t>68746635.5</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>195747548.06</t>
+          <t>195726576.28</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-21886491</t>
+          <t>-22506762</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-22595834.54184929</t>
+          <t>-22761876.14531295</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-22972183.97</v>
+        <v>-23675104.96</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>137.36</t>
+          <t>134.41</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>8784</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9887,17 +9887,17 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1475.722</t>
+          <t>2295.597</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-46.47</t>
+          <t>-26.69</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,17 +10060,17 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -10080,57 +10080,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.44</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-392.62</t>
+          <t>-7630.45</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-97.62</t>
+          <t>-100.13</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>213933659.5497835</t>
+          <t>213708809.176513</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>36228532.0</t>
+          <t>54691265.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>65043830.6</t>
+          <t>60118233.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>121499891.8</t>
+          <t>82004725.1</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>195285241.26</t>
+          <t>195747548.06</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-56456061</t>
+          <t>-21886491</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-22527407.37313884</t>
+          <t>-22595834.54184929</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-23924298.19</v>
+        <v>-22972183.97</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>22.50</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>137.36</t>
+          <t>134.41</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>8784</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/ITO導電基板.xlsx
+++ b/Result/checksun_type/ITO導電基板.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>293.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,84 +893,84 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>15.60</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>73.69</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="V2" t="inlineStr">
         <is>
           <t>0</t>
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,275 +1009,275 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>81.76</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
+          <t>23.49</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>22.46</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>23.57</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>119.34</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-110.67</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>82989.77697841727</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>14123.0</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>12216.7</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>7629.54</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>1054.796642723689</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>969.2</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>-8.37</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>-13.42998910113004</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-25.43417574544826</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-6.333574654154932</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>107.05</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>19.70%</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>85.54</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>1612</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>安可-光電業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>光電業平上櫃</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>23.45</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>24.05</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>22.43</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>23.42</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>92.50</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-113.86</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>83091.50144092219</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>20139.2</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>11594.6</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>7648.36</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>8544</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>1070.358956124564</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>1443.47</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-10.51</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>-13.42998910113004</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-25.43417574544826</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-6.333574654154932</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>104.55</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>19.70%</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>-0.85%</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>84.12</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>1575</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>安可-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>光電業平上櫃</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>23.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>426.0</t>
+          <t>293.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>75.73</t>
+          <t>73.69</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>91.82</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>22.43</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>87.14</t>
+          <t>92.50</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-113.86</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>83091.50144092219</t>
+          <t>82989.77697841727</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>19686.8</t>
+          <t>20139.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>11202.7</t>
+          <t>11594.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>8102.12</t>
+          <t>7648.36</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>1002.520030170422</t>
+          <t>1070.358956124564</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>2227.59</v>
+        <v>1443.47</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>390.0</t>
+          <t>426.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>75.73</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>91.82</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>69.08</t>
+          <t>87.14</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-120.78</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>83091.50144092219</t>
+          <t>82989.77697841727</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>18210.2</t>
+          <t>19686.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>10729.5</t>
+          <t>11202.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>8369.26</t>
+          <t>8102.12</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>779.7799219306776</t>
+          <t>1002.520030170422</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>2920.63</v>
+        <v>2227.59</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>23.15</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>23.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1498.0</t>
+          <t>390.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>65.67</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>86.42</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>69.08</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-124.37</t>
+          <t>-120.78</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>83091.50144092219</t>
+          <t>82989.77697841727</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>36258.0</t>
+          <t>9279.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>16891.0</t>
+          <t>18210.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>10195.3</t>
+          <t>10729.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>10437.66</t>
+          <t>8369.26</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>390.5343885617743</t>
+          <t>779.7799219306776</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>3886.84</v>
+        <v>2920.63</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1623.0</t>
+          <t>1498.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>65.67</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>61.41</t>
+          <t>86.42</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>46.64</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-127.21</t>
+          <t>-124.37</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>83091.50144092219</t>
+          <t>82989.77697841727</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>38343.0</t>
+          <t>36258.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>10310.4</t>
+          <t>16891.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>7058.7</t>
+          <t>10195.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>13160.96</t>
+          <t>10437.66</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-245.1581173895633</t>
+          <t>390.5343885617743</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>2237.72</v>
+        <v>3886.84</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>1623.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-16.18</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-13.49</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>61.41</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>26.72</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-129.03</t>
+          <t>-127.21</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>83091.50144092219</t>
+          <t>82989.77697841727</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>4524.0</t>
+          <t>38343.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>10310.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3638.9</t>
+          <t>7058.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>12810.66</t>
+          <t>13160.96</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-588</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-696.5912702806586</t>
+          <t>-245.1581173895633</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-421.47</v>
+        <v>2237.72</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-15.18</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-26.87</t>
+          <t>-16.18</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-13.49</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,72 +3595,72 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-11.42</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-128.78</t>
+          <t>-129.03</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>83091.50144092219</t>
+          <t>82989.77697841727</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2647.0</t>
+          <t>4524.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>2718.6</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3717.5</t>
+          <t>3638.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>13031.08</t>
+          <t>12810.66</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-998</t>
+          <t>-588</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-746.6130345102762</t>
+          <t>-696.5912702806586</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-581.8099999999999</v>
+        <v>-421.47</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-16.93</t>
+          <t>-15.18</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-15.70</t>
+          <t>-26.87</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-15.87</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,67 +4026,67 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>23.73</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>-11.42</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-127.96</t>
+          <t>-128.78</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>83091.50144092219</t>
+          <t>82989.77697841727</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2683.0</t>
+          <t>2647.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>3248.8</t>
+          <t>2718.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>3854.0</t>
+          <t>3717.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>13496.96</t>
+          <t>13031.08</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-605</t>
+          <t>-998</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-776.5779763001415</t>
+          <t>-746.6130345102762</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-588.97</v>
+        <v>-581.8099999999999</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-17.51</t>
+          <t>-16.93</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-13.67</t>
+          <t>-15.70</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-14.29</t>
+          <t>-15.87</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,17 +4457,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4477,57 +4477,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>21.52</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-13.09</t>
+          <t>-14.16</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-126.97</t>
+          <t>-127.96</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>83091.50144092219</t>
+          <t>82989.77697841727</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>3355.0</t>
+          <t>2683.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>3499.6</t>
+          <t>3248.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4053.7</t>
+          <t>3854.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>13799.2</t>
+          <t>13496.96</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-554</t>
+          <t>-605</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-810.6887149656693</t>
+          <t>-776.5779763001415</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-582.02</v>
+        <v>-588.97</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-15.95</t>
+          <t>-17.51</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-13.67</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-13.89</t>
+          <t>-14.29</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,67 +4888,67 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.77</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-16.06</t>
+          <t>-13.09</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-126.09</t>
+          <t>-126.97</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>83091.50144092219</t>
+          <t>82989.77697841727</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2041.0</t>
+          <t>3355.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>3807.0</t>
+          <t>3499.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>3998.4</t>
+          <t>4053.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>14454.38</t>
+          <t>13799.2</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-191</t>
+          <t>-554</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-852.264046081364</t>
+          <t>-810.6887149656693</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-623.3200000000001</v>
+        <v>-582.02</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-15.56</t>
+          <t>-15.95</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>7.86</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-14.88</t>
+          <t>-13.89</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.89</t>
+          <t>21.77</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-20.05</t>
+          <t>-16.06</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-125.04</t>
+          <t>-126.09</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>83091.50144092219</t>
+          <t>82989.77697841727</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2867.0</t>
+          <t>2041.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>4227.8</t>
+          <t>3807.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4048.6</t>
+          <t>3998.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>16723.7</t>
+          <t>14454.38</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>-191</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-893.8907697781259</t>
+          <t>-852.264046081364</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-519.26</v>
+        <v>-623.3200000000001</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-16.54</t>
+          <t>-15.56</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1646.332</t>
+          <t>1579.409</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-31.86</t>
+          <t>-32.96</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,67 +5750,67 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.07</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>13.77</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>6.62</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>24.37</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-54.01</t>
+          <t>-39.74</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-107.94</t>
+          <t>-108.82</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>213708809.176513</t>
+          <t>213483512.1820144</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>38591667.0</t>
+          <t>38084932.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>35280331.2</t>
+          <t>35331650.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>51774555.3</t>
+          <t>52705529.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>196053683.56</t>
+          <t>195762947.24</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-16494224</t>
+          <t>-17373879</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-15710661.47745765</t>
+          <t>-15131506.2497225</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-12713020</v>
+        <v>-11946152.5</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>21.50</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,17 +5938,17 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>134.41</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1604.993</t>
+          <t>1646.332</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,72 +6065,72 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4.53</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-1.29</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-31.86</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
           <t>23.85</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>-2.8</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-3.38</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>-18.78</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6196,62 +6196,62 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>13.77</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>25.44</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>25.96</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-27.44</t>
+          <t>-54.01</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-106.87</t>
+          <t>-107.94</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,45 +6271,45 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>213708809.176513</t>
+          <t>213483512.1820144</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>38724107.0</t>
+          <t>38591667.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>43361451.2</t>
+          <t>35280331.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>53384515.1</t>
+          <t>51774555.3</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>197488634.64</t>
+          <t>196053683.56</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-10023063</t>
+          <t>-16494224</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-16255687.20075533</t>
+          <t>-15710661.47745765</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-13408801.61</v>
+        <v>-12713020</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>134.41</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1126.956</t>
+          <t>1604.993</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,74 +6496,74 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-1.29</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-18.78</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>24.9</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-7.33</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-3.38</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>21.00</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>24.9</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
       <c r="T15" t="inlineStr">
         <is>
           <t>24.8</t>
@@ -6576,14 +6576,14 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>-4.22</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>4.40</t>
-        </is>
-      </c>
       <c r="X15" t="inlineStr">
         <is>
           <t>-9.29</t>
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>25.56</t>
+          <t>25.44</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>25.96</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>-27.44</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-106.40</t>
+          <t>-106.87</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>213708809.176513</t>
+          <t>213483512.1820144</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>28327621.0</t>
+          <t>38724107.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>64293510.0</t>
+          <t>43361451.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>53134957.6</t>
+          <t>53384515.1</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>197699079.6</t>
+          <t>197488634.64</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>11158552</t>
+          <t>-10023063</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-16773302.76279333</t>
+          <t>-16255687.20075533</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-13938079.57</v>
+        <v>-13408801.61</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>24.50</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>134.41</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1301.232</t>
+          <t>1126.956</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,22 +6937,22 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,72 +7043,72 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>71.74</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>25.56</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>24.19</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>13.70</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-106.48</t>
+          <t>-106.40</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,45 +7133,45 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>213708809.176513</t>
+          <t>213483512.1820144</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>32929925.0</t>
+          <t>28327621.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>66663290.6</t>
+          <t>64293510.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>54706545.9</t>
+          <t>53134957.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>197755621.26</t>
+          <t>197699079.6</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>11956744</t>
+          <t>11158552</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-17288797.88936103</t>
+          <t>-16773302.76279333</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-13082493.16</v>
+        <v>-13938079.57</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.50</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,17 +7231,17 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>134.41</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1463.862</t>
+          <t>1301.232</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-10.56</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>21.86</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>73.91</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>71.74</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.58</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>25.82</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>24.14</t>
+          <t>24.19</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>13.70</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-106.70</t>
+          <t>-106.48</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>213708809.176513</t>
+          <t>213483512.1820144</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>37828336.0</t>
+          <t>32929925.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>70079408.4</t>
+          <t>66663290.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>58159640.7</t>
+          <t>54706545.9</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>197616845.6</t>
+          <t>197755621.26</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>11919767</t>
+          <t>11956744</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-18053580.56674417</t>
+          <t>-17288797.88936103</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-11886098.98</v>
+        <v>-13082493.16</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,17 +7662,17 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>134.41</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3002.694</t>
+          <t>1463.862</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-12.5</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,47 +7905,47 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>93.48</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -7955,27 +7955,27 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>24.09</t>
+          <t>24.14</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-107.04</t>
+          <t>-106.70</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>213708809.176513</t>
+          <t>213483512.1820144</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>78997267.0</t>
+          <t>37828336.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>68268779.4</t>
+          <t>70079408.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>64193506.3</t>
+          <t>58159640.7</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>197596036.22</t>
+          <t>197616845.6</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>4075273</t>
+          <t>11919767</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-19174940.85612193</t>
+          <t>-18053580.56674417</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-10277290.64</v>
+        <v>-11886098.98</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>30.50</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>134.41</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5509.073</t>
+          <t>3002.694</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-13.15</t>
+          <t>-7.41</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,72 +8336,72 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.48</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.03</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>25.62</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>24.04</t>
+          <t>24.09</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-34.06</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-107.14</t>
+          <t>-107.04</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>213708809.176513</t>
+          <t>213483512.1820144</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>143384401.0</t>
+          <t>78997267.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>63407579.0</t>
+          <t>68268779.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>64225704.8</t>
+          <t>64193506.3</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>196763751.52</t>
+          <t>197596036.22</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-818125</t>
+          <t>4075273</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-20792695.44174149</t>
+          <t>-19174940.85612193</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-12022903.81</v>
+        <v>-10277290.64</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.50</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,17 +8524,17 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>134.41</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1642.154</t>
+          <t>5509.073</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-27.26</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>15.37</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>25.64</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>24.04</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-107.80</t>
+          <t>-34.06</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-106.53</t>
+          <t>-107.14</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>213708809.176513</t>
+          <t>213483512.1820144</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>40176524.0</t>
+          <t>143384401.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>41976405.2</t>
+          <t>63407579.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>57706625.4</t>
+          <t>64225704.8</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>194790217.74</t>
+          <t>196763751.52</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-15730220</t>
+          <t>-818125</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-22387203.01197561</t>
+          <t>-20792695.44174149</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-20985868.98</v>
+        <v>-12022903.81</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,17 +8955,17 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>134.41</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2080.109</t>
+          <t>1642.154</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-35.04</t>
+          <t>-27.26</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,67 +9198,67 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>9.62</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>15.37</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.64</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-184.26</t>
+          <t>-107.80</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-104.77</t>
+          <t>-106.53</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>213708809.176513</t>
+          <t>213483512.1820144</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>50010514.0</t>
+          <t>40176524.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>42749801.2</t>
+          <t>41976405.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>65809171.5</t>
+          <t>57706625.4</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>195892656.92</t>
+          <t>194790217.74</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-23059370</t>
+          <t>-15730220</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-22641991.01703074</t>
+          <t>-22387203.01197561</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-21982622.81</v>
+        <v>-20985868.98</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>134.41</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,42 +9498,42 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2080.109</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>24.2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>0.41</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>1195.841</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>24.05</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>-3.66</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-32.74</t>
+          <t>-35.04</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,42 +9629,42 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>9.62</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
@@ -9674,32 +9674,32 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>25.63</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>25.62</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-379.56</t>
+          <t>-184.26</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-102.57</t>
+          <t>-104.77</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>213708809.176513</t>
+          <t>213483512.1820144</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>28775191.0</t>
+          <t>50010514.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>46239873.0</t>
+          <t>42749801.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>68746635.5</t>
+          <t>65809171.5</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>195726576.28</t>
+          <t>195892656.92</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-22506762</t>
+          <t>-23059370</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-22761876.14531295</t>
+          <t>-22641991.01703074</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-23675104.96</v>
+        <v>-21982622.81</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>134.41</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9887,17 +9887,17 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2295.597</t>
+          <t>1195.841</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-26.69</t>
+          <t>-32.74</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.31</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-7630.45</t>
+          <t>-379.56</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-100.13</t>
+          <t>-102.57</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>213708809.176513</t>
+          <t>213483512.1820144</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>54691265.0</t>
+          <t>28775191.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>60118233.2</t>
+          <t>46239873.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>82004725.1</t>
+          <t>68746635.5</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>195747548.06</t>
+          <t>195726576.28</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-21886491</t>
+          <t>-22506762</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-22595834.54184929</t>
+          <t>-22761876.14531295</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-22972183.97</v>
+        <v>-23675104.96</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>134.41</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10318,17 +10318,17 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/ITO導電基板.xlsx
+++ b/Result/checksun_type/ITO導電基板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-34.19</t>
+          <t>-41.51</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.32</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,72 +1019,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>64.93</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>108.28</t>
+          <t>115.43</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-108.40</t>
+          <t>-106.52</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>82885.7650862069</t>
+          <t>82778.67073170732</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>8284.4</t>
+          <t>7527.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>12587.7</t>
+          <t>12868.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>7563.22</t>
+          <t>7378.32</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-4303</t>
+          <t>-5341</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>973.0141484809627</t>
+          <t>835.6442375117817</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>523.2104301459694</t>
+          <t>80.10972718128687</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>7065</v>
+        <v>5494</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-12.06</t>
+          <t>-10.70</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>104.32</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-4.2</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>-34.19</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-10.32</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1455,72 +1455,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>81.76</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>23.33</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>119.34</t>
+          <t>108.28</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-108.40</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>82885.7650862069</t>
+          <t>82778.67073170732</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>14123.0</t>
+          <t>8284.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>12216.7</t>
+          <t>12587.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>7629.54</t>
+          <t>7563.22</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>-4303</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>1054.796642723689</t>
+          <t>973.0141484809627</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>969.2039190188734</t>
+          <t>523.2104301459694</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>8262</v>
+        <v>7065</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-12.06</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>104.32</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>293.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,84 +1770,84 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-2.61</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-2.69</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>15.60</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-1.77</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-1.58</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>73.69</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1891,275 +1891,275 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>81.76</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
+          <t>23.49</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>22.46</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>23.57</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>119.34</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-110.67</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>82778.67073170732</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>14123.0</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>12216.7</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>7629.54</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>1054.796642723689</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>969.2039190188734</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>8262</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>-8.37</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>-13.42998910113004</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>-25.43417574544826</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>-6.333574654154932</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>104.32</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>19.70%</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>84.96</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>1571</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>安可-光電業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>光電業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>23.45</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>24.05</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>22.43</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>23.42</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>92.50</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-113.86</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>82885.7650862069</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>20139.2</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>11594.6</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>7648.36</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>8544</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>1070.358956124564</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>1443.473048872349</t>
-        </is>
-      </c>
-      <c r="BD4" t="n">
-        <v>6786</v>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>-10.51</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>-13.42998910113004</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>-25.43417574544826</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>-6.333574654154932</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>102.73</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>19.70%</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>-0.85%</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>83.58</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>1547</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>安可-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>光電業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>23.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>426.0</t>
+          <t>293.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.2</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>75.73</t>
+          <t>73.69</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2327,72 +2327,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>91.82</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>22.43</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>87.14</t>
+          <t>92.50</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-113.86</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>82885.7650862069</t>
+          <t>82778.67073170732</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>19686.8</t>
+          <t>20139.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>11202.7</t>
+          <t>11594.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>8102.12</t>
+          <t>7648.36</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>1002.520030170422</t>
+          <t>1070.358956124564</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>2227.590625489014</t>
+          <t>1443.473048872349</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>10030</v>
+        <v>6786</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>104.32</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>390.0</t>
+          <t>426.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>75.73</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2763,72 +2763,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>91.82</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>69.08</t>
+          <t>87.14</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-120.78</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>82885.7650862069</t>
+          <t>82778.67073170732</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>18210.2</t>
+          <t>19686.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>10729.5</t>
+          <t>11202.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>8369.26</t>
+          <t>8102.12</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>779.7799219306776</t>
+          <t>1002.520030170422</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>2920.630355459645</t>
+          <t>2227.590625489014</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>9279</v>
+        <v>10030</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>104.32</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3021,17 +3021,17 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
+          <t>23.15</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>23.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1498.0</t>
+          <t>390.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.2</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>65.67</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3199,72 +3199,72 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>86.42</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>69.08</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-124.37</t>
+          <t>-120.78</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>82885.7650862069</t>
+          <t>82778.67073170732</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>36258.0</t>
+          <t>9279.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>16891.0</t>
+          <t>18210.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>10195.3</t>
+          <t>10729.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>10437.66</t>
+          <t>8369.26</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>390.5343885617743</t>
+          <t>779.7799219306776</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>3886.843171294131</t>
+          <t>2920.630355459645</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>36258</v>
+        <v>9279</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>104.32</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1623.0</t>
+          <t>1498.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>65.67</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3635,72 +3635,72 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>61.41</t>
+          <t>86.42</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>46.64</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-127.21</t>
+          <t>-124.37</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>82885.7650862069</t>
+          <t>82778.67073170732</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>38343.0</t>
+          <t>36258.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>10310.4</t>
+          <t>16891.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7058.7</t>
+          <t>10195.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>13160.96</t>
+          <t>10437.66</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-245.1581173895633</t>
+          <t>390.5343885617743</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>2237.724223511461</t>
+          <t>3886.843171294131</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>38343</v>
+        <v>36258</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>104.32</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>1623.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-16.18</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-13.49</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4071,72 +4071,72 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>61.41</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>26.72</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-129.03</t>
+          <t>-127.21</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>82885.7650862069</t>
+          <t>82778.67073170732</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>4524.0</t>
+          <t>38343.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>10310.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>3638.9</t>
+          <t>7058.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>12810.66</t>
+          <t>13160.96</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-588</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-696.5912702806586</t>
+          <t>-245.1581173895633</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-421.4715670177616</t>
+          <t>2237.724223511461</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>4524</v>
+        <v>38343</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-15.18</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>104.32</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-26.87</t>
+          <t>-16.18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-13.49</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4507,67 +4507,67 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-11.42</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-128.78</t>
+          <t>-129.03</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>82885.7650862069</t>
+          <t>82778.67073170732</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2647.0</t>
+          <t>4524.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2718.6</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>3717.5</t>
+          <t>3638.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>13031.08</t>
+          <t>12810.66</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-998</t>
+          <t>-588</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-746.6130345102762</t>
+          <t>-696.5912702806586</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-581.8058546660172</t>
+          <t>-421.4715670177616</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>2647</v>
+        <v>4524</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-16.93</t>
+          <t>-15.18</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>104.32</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-15.70</t>
+          <t>-26.87</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-15.87</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4943,62 +4943,62 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>23.73</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>-11.42</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-127.96</t>
+          <t>-128.78</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>82885.7650862069</t>
+          <t>82778.67073170732</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2683.0</t>
+          <t>2647.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>3248.8</t>
+          <t>2718.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>3854.0</t>
+          <t>3717.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>13496.96</t>
+          <t>13031.08</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-605</t>
+          <t>-998</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-776.5779763001415</t>
+          <t>-746.6130345102762</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-588.9689136397383</t>
+          <t>-581.8058546660172</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>2683</v>
+        <v>2647</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-17.51</t>
+          <t>-16.93</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>104.32</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5201,17 +5201,17 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-13.67</t>
+          <t>-15.70</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-14.29</t>
+          <t>-15.87</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5394,57 +5394,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>21.52</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-13.09</t>
+          <t>-14.16</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-126.97</t>
+          <t>-127.96</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>82885.7650862069</t>
+          <t>82778.67073170732</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3355.0</t>
+          <t>2683.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>3499.6</t>
+          <t>3248.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4053.7</t>
+          <t>3854.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>13799.2</t>
+          <t>13496.96</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-554</t>
+          <t>-605</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-810.6887149656693</t>
+          <t>-776.5779763001415</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-582.0243938293488</t>
+          <t>-588.9689136397383</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>3355</v>
+        <v>2683</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-15.95</t>
+          <t>-17.51</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>104.32</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2112.165</t>
+          <t>1462.411</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-26.70</t>
+          <t>-23.72</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,12 +5810,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5830,57 +5830,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-48.21</t>
+          <t>-50.35</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-110.02</t>
+          <t>-111.47</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>213282615.9913793</t>
+          <t>213049101.1527977</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>49106509.0</t>
+          <t>33681849.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>38566967.2</t>
+          <t>39637812.8</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>52615128.9</t>
+          <t>51965661.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>195992723.02</t>
+          <t>195984000.1</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-14048161</t>
+          <t>-12327848</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-14385747.31257303</t>
+          <t>-13714150.07864561</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-10284073.15825091</t>
+          <t>-10020365.29204483</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>49106509</v>
+        <v>33681849</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>15.75</t>
+          <t>14.50</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>132.73</t>
+          <t>134.29</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1579.409</t>
+          <t>2112.165</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-32.96</t>
+          <t>-26.70</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,17 +6246,17 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>36.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -6266,32 +6266,32 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>6.62</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>23.88</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>25.06</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -6301,22 +6301,22 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>24.37</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-39.74</t>
+          <t>-48.21</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-108.82</t>
+          <t>-110.02</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>213282615.9913793</t>
+          <t>213049101.1527977</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>38084932.0</t>
+          <t>49106509.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>35331650.4</t>
+          <t>38566967.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>52705529.4</t>
+          <t>52615128.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>195762947.24</t>
+          <t>195992723.02</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-17373879</t>
+          <t>-14048161</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-15131506.2497225</t>
+          <t>-14385747.31257303</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-11946152.49717921</t>
+          <t>-10284073.15825091</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>38084932</v>
+        <v>49106509</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>21.50</t>
+          <t>15.75</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,17 +6439,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>132.73</t>
+          <t>134.29</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6509,17 +6509,17 @@
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1646.332</t>
+          <t>1579.409</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-31.86</t>
+          <t>-32.96</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,67 +6682,67 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.07</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>13.77</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>6.62</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>24.37</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-54.01</t>
+          <t>-39.74</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-107.94</t>
+          <t>-108.82</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>213282615.9913793</t>
+          <t>213049101.1527977</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>38591667.0</t>
+          <t>38084932.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>35280331.2</t>
+          <t>35331650.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>51774555.3</t>
+          <t>52705529.4</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>196053683.56</t>
+          <t>195762947.24</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-16494224</t>
+          <t>-17373879</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-15710661.47745765</t>
+          <t>-15131506.2497225</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-12713019.99932038</t>
+          <t>-11946152.49717921</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>38591667</v>
+        <v>38084932</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>21.50</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,17 +6875,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>132.73</t>
+          <t>134.29</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1604.993</t>
+          <t>1646.332</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,72 +7002,72 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-1.31</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-1.77</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-31.86</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
           <t>23.85</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>-3.02</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-2.35</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-18.78</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,12 +7118,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7133,62 +7133,62 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>13.77</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>25.44</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>25.96</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-27.44</t>
+          <t>-54.01</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-106.87</t>
+          <t>-107.94</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,50 +7208,50 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>213282615.9913793</t>
+          <t>213049101.1527977</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>38724107.0</t>
+          <t>38591667.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>43361451.2</t>
+          <t>35280331.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>53384515.1</t>
+          <t>51774555.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>197488634.64</t>
+          <t>196053683.56</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-10023063</t>
+          <t>-16494224</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-16255687.20075533</t>
+          <t>-15710661.47745765</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-13408801.60954632</t>
+          <t>-12713019.99932038</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>38724107</v>
+        <v>38591667</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>132.73</t>
+          <t>134.29</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1126.956</t>
+          <t>1604.993</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,74 +7438,74 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-4.15</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-1.77</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-18.78</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>24.9</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>-7.56</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-2.35</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>21.00</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>24.9</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
       <c r="T17" t="inlineStr">
         <is>
           <t>24.8</t>
@@ -7518,14 +7518,14 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>-4.22</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>4.40</t>
-        </is>
-      </c>
       <c r="X17" t="inlineStr">
         <is>
           <t>-9.29</t>
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>25.56</t>
+          <t>25.44</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>25.96</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>-27.44</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-106.40</t>
+          <t>-106.87</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>213282615.9913793</t>
+          <t>213049101.1527977</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>28327621.0</t>
+          <t>38724107.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>64293510.0</t>
+          <t>43361451.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>53134957.6</t>
+          <t>53384515.1</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>197699079.6</t>
+          <t>197488634.64</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>11158552</t>
+          <t>-10023063</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-16773302.76279333</t>
+          <t>-16255687.20075533</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-13938079.56667101</t>
+          <t>-13408801.60954632</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>28327621</v>
+        <v>38724107</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>24.50</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>132.73</t>
+          <t>134.29</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1301.232</t>
+          <t>1126.956</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,22 +7884,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -7954,12 +7954,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,72 +7990,72 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>71.74</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>25.56</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>24.19</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>13.70</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-106.48</t>
+          <t>-106.40</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,50 +8080,50 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>213282615.9913793</t>
+          <t>213049101.1527977</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>32929925.0</t>
+          <t>28327621.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>66663290.6</t>
+          <t>64293510.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>54706545.9</t>
+          <t>53134957.6</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>197755621.26</t>
+          <t>197699079.6</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>11956744</t>
+          <t>11158552</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-17288797.88936103</t>
+          <t>-16773302.76279333</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-13082493.16375375</t>
+          <t>-13938079.56667101</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>32929925</v>
+        <v>28327621</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.50</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,17 +8183,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>132.73</t>
+          <t>134.29</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1463.862</t>
+          <t>1301.232</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-10.8</t>
+          <t>-9.39</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>21.86</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,77 +8426,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>73.91</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>71.74</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.58</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>25.82</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>24.14</t>
+          <t>24.19</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>13.70</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-106.70</t>
+          <t>-106.48</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>213282615.9913793</t>
+          <t>213049101.1527977</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>37828336.0</t>
+          <t>32929925.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>70079408.4</t>
+          <t>66663290.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>58159640.7</t>
+          <t>54706545.9</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>197616845.6</t>
+          <t>197755621.26</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>11919767</t>
+          <t>11956744</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-18053580.56674417</t>
+          <t>-17288797.88936103</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-11886098.97516645</t>
+          <t>-13082493.16375375</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>37828336</v>
+        <v>32929925</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,17 +8619,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>132.73</t>
+          <t>134.29</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3002.694</t>
+          <t>1463.862</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-12.74</t>
+          <t>-12.01</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,47 +8862,47 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>93.48</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -8912,27 +8912,27 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>24.09</t>
+          <t>24.14</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-107.04</t>
+          <t>-106.70</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>213282615.9913793</t>
+          <t>213049101.1527977</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>78997267.0</t>
+          <t>37828336.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>68268779.4</t>
+          <t>70079408.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>64193506.3</t>
+          <t>58159640.7</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>197596036.22</t>
+          <t>197616845.6</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>4075273</t>
+          <t>11919767</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-19174940.85612193</t>
+          <t>-18053580.56674417</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-10277290.63521439</t>
+          <t>-11886098.97516645</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>78997267</v>
+        <v>37828336</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>30.50</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>132.73</t>
+          <t>134.29</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5509.073</t>
+          <t>3002.694</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-13.39</t>
+          <t>-13.97</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,72 +9298,72 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.48</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.03</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>25.62</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>24.04</t>
+          <t>24.09</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-34.06</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-107.14</t>
+          <t>-107.04</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>213282615.9913793</t>
+          <t>213049101.1527977</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>143384401.0</t>
+          <t>78997267.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>63407579.0</t>
+          <t>68268779.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>64225704.8</t>
+          <t>64193506.3</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>196763751.52</t>
+          <t>197596036.22</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-818125</t>
+          <t>4075273</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-20792695.44174149</t>
+          <t>-19174940.85612193</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-12022903.80545378</t>
+          <t>-10277290.63521439</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>143384401</v>
+        <v>78997267</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.50</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>132.73</t>
+          <t>134.29</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1642.154</t>
+          <t>5509.073</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-27.26</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>15.37</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>25.64</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>24.04</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-107.80</t>
+          <t>-34.06</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-106.53</t>
+          <t>-107.14</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>213282615.9913793</t>
+          <t>213049101.1527977</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>40176524.0</t>
+          <t>143384401.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>41976405.2</t>
+          <t>63407579.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>57706625.4</t>
+          <t>64225704.8</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>194790217.74</t>
+          <t>196763751.52</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-15730220</t>
+          <t>-818125</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-22387203.01197561</t>
+          <t>-20792695.44174149</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-20985868.9841724</t>
+          <t>-12022903.80545378</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>40176524</v>
+        <v>143384401</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>132.73</t>
+          <t>134.29</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2080.109</t>
+          <t>1642.154</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-35.04</t>
+          <t>-27.26</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,67 +10170,67 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>9.62</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>15.37</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-5.05</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.64</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-184.26</t>
+          <t>-107.80</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
@@ -10240,7 +10240,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-104.77</t>
+          <t>-106.53</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>213282615.9913793</t>
+          <t>213049101.1527977</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>50010514.0</t>
+          <t>40176524.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>42749801.2</t>
+          <t>41976405.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>65809171.5</t>
+          <t>57706625.4</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>195892656.92</t>
+          <t>194790217.74</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-23059370</t>
+          <t>-15730220</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-22641991.01703074</t>
+          <t>-22387203.01197561</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-21982622.81147857</t>
+          <t>-20985868.9841724</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>50010514</v>
+        <v>40176524</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>132.73</t>
+          <t>134.29</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/ITO導電基板.xlsx
+++ b/Result/checksun_type/ITO導電基板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-41.51</t>
+          <t>-51.37</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,72 +1019,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>64.93</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>23.61</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>115.43</t>
+          <t>160.83</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.52</t>
+          <t>-104.65</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>82778.67073170732</t>
+          <t>82668.7005730659</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>7527.4</t>
+          <t>6324.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>12868.8</t>
+          <t>13005.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>7378.32</t>
+          <t>7283.74</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-5341</t>
+          <t>-6681</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>835.6442375117817</t>
+          <t>654.2930458832735</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>80.10972718128687</t>
+          <t>-343.1385080735217</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>5494</v>
+        <v>4013</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-10.70</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>104.32</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-34.19</t>
+          <t>-41.51</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.32</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1455,72 +1455,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>64.93</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>108.28</t>
+          <t>115.43</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-108.40</t>
+          <t>-106.52</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>82778.67073170732</t>
+          <t>82668.7005730659</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>8284.4</t>
+          <t>7527.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>12587.7</t>
+          <t>12868.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>7563.22</t>
+          <t>7378.32</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-4303</t>
+          <t>-5341</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>973.0141484809627</t>
+          <t>835.6442375117817</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>523.2104301459694</t>
+          <t>80.10972718128687</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>7065</v>
+        <v>5494</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-12.06</t>
+          <t>-10.70</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>104.32</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>-34.19</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-10.32</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1891,72 +1891,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>81.76</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>23.33</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>119.34</t>
+          <t>108.28</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-108.40</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>82778.67073170732</t>
+          <t>82668.7005730659</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>14123.0</t>
+          <t>8284.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>12216.7</t>
+          <t>12587.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>7629.54</t>
+          <t>7563.22</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>-4303</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>1054.796642723689</t>
+          <t>973.0141484809627</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>969.2039190188734</t>
+          <t>523.2104301459694</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>8262</v>
+        <v>7065</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-12.06</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>104.32</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>293.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,84 +2206,84 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-1.84</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>15.60</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-2.69</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>73.69</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2327,275 +2327,275 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>81.76</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
+          <t>23.49</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>22.46</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>23.57</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>119.34</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-110.67</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>82668.7005730659</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>14123.0</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>12216.7</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>7629.54</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>1054.796642723689</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>969.2039190188734</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>8262</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>-8.37</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>-13.42998910113004</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>-25.43417574544826</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>-6.333574654154932</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>106.14</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>19.70%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>86.4</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>1599</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>安可-光電業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>光電業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>23.45</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>24.05</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>22.43</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>23.42</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>92.50</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-113.86</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>82778.67073170732</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>20139.2</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>11594.6</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>7648.36</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>8544</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>1070.358956124564</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>1443.473048872349</t>
-        </is>
-      </c>
-      <c r="BD5" t="n">
-        <v>6786</v>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>-10.51</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>-13.42998910113004</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>-25.43417574544826</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>-6.333574654154932</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>104.32</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>19.70%</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>-0.85%</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>84.96</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>1571</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>安可-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>光電業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>23.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>426.0</t>
+          <t>293.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>75.73</t>
+          <t>73.69</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2763,72 +2763,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>91.82</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>22.43</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>87.14</t>
+          <t>92.50</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-113.86</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>82778.67073170732</t>
+          <t>82668.7005730659</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>19686.8</t>
+          <t>20139.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>11202.7</t>
+          <t>11594.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>8102.12</t>
+          <t>7648.36</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>1002.520030170422</t>
+          <t>1070.358956124564</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>2227.590625489014</t>
+          <t>1443.473048872349</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>10030</v>
+        <v>6786</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>104.32</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>390.0</t>
+          <t>426.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>75.73</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3199,72 +3199,72 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>91.82</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>69.08</t>
+          <t>87.14</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-120.78</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>82778.67073170732</t>
+          <t>82668.7005730659</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>18210.2</t>
+          <t>19686.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>10729.5</t>
+          <t>11202.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>8369.26</t>
+          <t>8102.12</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>779.7799219306776</t>
+          <t>1002.520030170422</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>2920.630355459645</t>
+          <t>2227.590625489014</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>9279</v>
+        <v>10030</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>104.32</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3457,17 +3457,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
+          <t>23.15</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>23.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1498.0</t>
+          <t>390.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>65.67</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3635,72 +3635,72 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>86.42</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>69.08</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-124.37</t>
+          <t>-120.78</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>82778.67073170732</t>
+          <t>82668.7005730659</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>36258.0</t>
+          <t>9279.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>16891.0</t>
+          <t>18210.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>10195.3</t>
+          <t>10729.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>10437.66</t>
+          <t>8369.26</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>390.5343885617743</t>
+          <t>779.7799219306776</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>3886.843171294131</t>
+          <t>2920.630355459645</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>36258</v>
+        <v>9279</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>104.32</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1623.0</t>
+          <t>1498.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>65.67</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4071,72 +4071,72 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>61.41</t>
+          <t>86.42</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>46.64</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-127.21</t>
+          <t>-124.37</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>82778.67073170732</t>
+          <t>82668.7005730659</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>38343.0</t>
+          <t>36258.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>10310.4</t>
+          <t>16891.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>7058.7</t>
+          <t>10195.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>13160.96</t>
+          <t>10437.66</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-245.1581173895633</t>
+          <t>390.5343885617743</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>2237.724223511461</t>
+          <t>3886.843171294131</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>38343</v>
+        <v>36258</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>104.32</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>1623.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-16.18</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-13.49</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4507,72 +4507,72 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>61.41</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>26.72</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-129.03</t>
+          <t>-127.21</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>82778.67073170732</t>
+          <t>82668.7005730659</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>4524.0</t>
+          <t>38343.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>10310.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>3638.9</t>
+          <t>7058.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>12810.66</t>
+          <t>13160.96</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-588</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-696.5912702806586</t>
+          <t>-245.1581173895633</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-421.4715670177616</t>
+          <t>2237.724223511461</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>4524</v>
+        <v>38343</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-15.18</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,22 +4695,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>104.32</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-26.87</t>
+          <t>-16.18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-13.49</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4943,67 +4943,67 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-11.42</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-128.78</t>
+          <t>-129.03</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>82778.67073170732</t>
+          <t>82668.7005730659</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2647.0</t>
+          <t>4524.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2718.6</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>3717.5</t>
+          <t>3638.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>13031.08</t>
+          <t>12810.66</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-998</t>
+          <t>-588</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-746.6130345102762</t>
+          <t>-696.5912702806586</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-581.8058546660172</t>
+          <t>-421.4715670177616</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>2647</v>
+        <v>4524</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-16.93</t>
+          <t>-15.18</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>104.32</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-15.70</t>
+          <t>-26.87</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-15.87</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5379,62 +5379,62 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>23.73</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>-11.42</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-127.96</t>
+          <t>-128.78</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>82778.67073170732</t>
+          <t>82668.7005730659</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2683.0</t>
+          <t>2647.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>3248.8</t>
+          <t>2718.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>3854.0</t>
+          <t>3717.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>13496.96</t>
+          <t>13031.08</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-605</t>
+          <t>-998</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-776.5779763001415</t>
+          <t>-746.6130345102762</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-588.9689136397383</t>
+          <t>-581.8058546660172</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>2683</v>
+        <v>2647</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-17.51</t>
+          <t>-16.93</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>104.32</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5637,17 +5637,17 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1462.411</t>
+          <t>1738.819</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-23.72</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,67 +5810,67 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>24.49</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-50.35</t>
+          <t>-37.74</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-111.47</t>
+          <t>-112.66</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>213049101.1527977</t>
+          <t>212831136.732808</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>33681849.0</t>
+          <t>40606624.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>39637812.8</t>
+          <t>40014316.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>51965661.4</t>
+          <t>41687883.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>195984000.1</t>
+          <t>195169236.84</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-12327848</t>
+          <t>-1673567</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-13714150.07864561</t>
+          <t>-12999035.07091543</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-10020365.29204483</t>
+          <t>-9065902.528399438</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>33681849</v>
+        <v>40606624</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>14.50</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>134.29</t>
+          <t>137.74</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,24 +6068,24 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
+          <t>23.05</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
           <t>23.55</t>
         </is>
       </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>22.8</t>
-        </is>
-      </c>
-      <c r="CG13" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
       <c r="CH13" t="inlineStr">
         <is>
           <t>15.6</t>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="CJ13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2112.165</t>
+          <t>1462.411</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-26.70</t>
+          <t>-23.72</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,12 +6246,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6266,57 +6266,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-48.21</t>
+          <t>-50.35</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-110.02</t>
+          <t>-111.47</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>213049101.1527977</t>
+          <t>212831136.732808</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>49106509.0</t>
+          <t>33681849.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>38566967.2</t>
+          <t>39637812.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>52615128.9</t>
+          <t>51965661.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>195992723.02</t>
+          <t>195984000.1</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-14048161</t>
+          <t>-12327848</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-14385747.31257303</t>
+          <t>-13714150.07864561</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-10284073.15825091</t>
+          <t>-10020365.29204483</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>49106509</v>
+        <v>33681849</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>15.75</t>
+          <t>14.50</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>134.29</t>
+          <t>137.74</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="CJ14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1579.409</t>
+          <t>2112.165</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-32.96</t>
+          <t>-26.70</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,17 +6682,17 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>36.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -6702,32 +6702,32 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>6.62</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>23.88</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>25.06</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
@@ -6737,22 +6737,22 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>24.37</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-39.74</t>
+          <t>-48.21</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-108.82</t>
+          <t>-110.02</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>213049101.1527977</t>
+          <t>212831136.732808</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>38084932.0</t>
+          <t>49106509.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>35331650.4</t>
+          <t>38566967.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>52705529.4</t>
+          <t>52615128.9</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>195762947.24</t>
+          <t>195992723.02</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-17373879</t>
+          <t>-14048161</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-15131506.2497225</t>
+          <t>-14385747.31257303</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-11946152.49717921</t>
+          <t>-10284073.15825091</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>38084932</v>
+        <v>49106509</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>21.50</t>
+          <t>15.75</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6875,17 +6875,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>134.29</t>
+          <t>137.74</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6945,17 +6945,17 @@
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="CJ15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1646.332</t>
+          <t>1579.409</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-31.86</t>
+          <t>-32.96</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,67 +7118,67 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.07</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>13.77</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>6.62</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>24.37</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-54.01</t>
+          <t>-39.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-107.94</t>
+          <t>-108.82</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>213049101.1527977</t>
+          <t>212831136.732808</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>38591667.0</t>
+          <t>38084932.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>35280331.2</t>
+          <t>35331650.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>51774555.3</t>
+          <t>52705529.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>196053683.56</t>
+          <t>195762947.24</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-16494224</t>
+          <t>-17373879</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-15710661.47745765</t>
+          <t>-15131506.2497225</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-12713019.99932038</t>
+          <t>-11946152.49717921</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>38591667</v>
+        <v>38084932</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>21.50</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7311,17 +7311,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>134.29</t>
+          <t>137.74</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="CJ16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1604.993</t>
+          <t>1646.332</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,72 +7438,72 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-1.82</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-31.86</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
           <t>23.85</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>-4.15</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-1.77</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>-18.78</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -7518,12 +7518,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7569,62 +7569,62 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>13.77</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>25.44</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>25.96</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-27.44</t>
+          <t>-54.01</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-106.87</t>
+          <t>-107.94</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,50 +7644,50 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>213049101.1527977</t>
+          <t>212831136.732808</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>38724107.0</t>
+          <t>38591667.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>43361451.2</t>
+          <t>35280331.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>53384515.1</t>
+          <t>51774555.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>197488634.64</t>
+          <t>196053683.56</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-10023063</t>
+          <t>-16494224</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-16255687.20075533</t>
+          <t>-15710661.47745765</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-13408801.60954632</t>
+          <t>-12713019.99932038</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>38724107</v>
+        <v>38591667</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>134.29</t>
+          <t>137.74</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="CJ17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1126.956</t>
+          <t>1604.993</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,74 +7874,74 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-1.27</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-1.82</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-18.78</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>24.9</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>-8.73</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-1.77</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>21.00</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2025-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
         <is>
           <t>24.9</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
       <c r="T18" t="inlineStr">
         <is>
           <t>24.8</t>
@@ -7954,14 +7954,14 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>-4.22</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>4.40</t>
-        </is>
-      </c>
       <c r="X18" t="inlineStr">
         <is>
           <t>-9.29</t>
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,77 +7990,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>25.56</t>
+          <t>25.44</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>25.96</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>-27.44</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-106.40</t>
+          <t>-106.87</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>213049101.1527977</t>
+          <t>212831136.732808</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28327621.0</t>
+          <t>38724107.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>64293510.0</t>
+          <t>43361451.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>53134957.6</t>
+          <t>53384515.1</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>197699079.6</t>
+          <t>197488634.64</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>11158552</t>
+          <t>-10023063</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-16773302.76279333</t>
+          <t>-16255687.20075533</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-13938079.56667101</t>
+          <t>-13408801.60954632</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>28327621</v>
+        <v>38724107</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>24.50</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>134.29</t>
+          <t>137.74</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="CJ18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1301.232</t>
+          <t>1126.956</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,22 +8320,22 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-9.39</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,72 +8426,72 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>71.74</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>25.56</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>24.19</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>13.70</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-106.48</t>
+          <t>-106.40</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,50 +8516,50 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>213049101.1527977</t>
+          <t>212831136.732808</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>32929925.0</t>
+          <t>28327621.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>66663290.6</t>
+          <t>64293510.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>54706545.9</t>
+          <t>53134957.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>197755621.26</t>
+          <t>197699079.6</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>11956744</t>
+          <t>11158552</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-17288797.88936103</t>
+          <t>-16773302.76279333</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-13082493.16375375</t>
+          <t>-13938079.56667101</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>32929925</v>
+        <v>28327621</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.50</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8619,17 +8619,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>134.29</t>
+          <t>137.74</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="CJ19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1463.862</t>
+          <t>1301.232</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-12.01</t>
+          <t>-6.37</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>21.86</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,77 +8862,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>73.91</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>71.74</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.58</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>25.82</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>24.14</t>
+          <t>24.19</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>13.70</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-106.70</t>
+          <t>-106.48</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>213049101.1527977</t>
+          <t>212831136.732808</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>37828336.0</t>
+          <t>32929925.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>70079408.4</t>
+          <t>66663290.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>58159640.7</t>
+          <t>54706545.9</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>197616845.6</t>
+          <t>197755621.26</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>11919767</t>
+          <t>11956744</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-18053580.56674417</t>
+          <t>-17288797.88936103</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-11886098.97516645</t>
+          <t>-13082493.16375375</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>37828336</v>
+        <v>32929925</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -9055,17 +9055,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>134.29</t>
+          <t>137.74</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="CJ20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3002.694</t>
+          <t>1463.862</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-13.97</t>
+          <t>-8.92</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,47 +9298,47 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>93.48</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -9348,27 +9348,27 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>24.09</t>
+          <t>24.14</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-107.04</t>
+          <t>-106.70</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>213049101.1527977</t>
+          <t>212831136.732808</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>78997267.0</t>
+          <t>37828336.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>68268779.4</t>
+          <t>70079408.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>64193506.3</t>
+          <t>58159640.7</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>197596036.22</t>
+          <t>197616845.6</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>4075273</t>
+          <t>11919767</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-19174940.85612193</t>
+          <t>-18053580.56674417</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-10277290.63521439</t>
+          <t>-11886098.97516645</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>78997267</v>
+        <v>37828336</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>30.50</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>134.29</t>
+          <t>137.74</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="CJ21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5509.073</t>
+          <t>3002.694</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-10.83</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,72 +9734,72 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.48</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.03</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>25.62</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>24.04</t>
+          <t>24.09</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-34.06</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-107.14</t>
+          <t>-107.04</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>213049101.1527977</t>
+          <t>212831136.732808</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>143384401.0</t>
+          <t>78997267.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>63407579.0</t>
+          <t>68268779.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>64225704.8</t>
+          <t>64193506.3</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>196763751.52</t>
+          <t>197596036.22</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-818125</t>
+          <t>4075273</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-20792695.44174149</t>
+          <t>-19174940.85612193</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-12022903.80545378</t>
+          <t>-10277290.63521439</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>143384401</v>
+        <v>78997267</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.50</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>134.29</t>
+          <t>137.74</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="CJ22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1642.154</t>
+          <t>5509.073</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-11.46</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-27.26</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>15.37</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-5.05</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>25.57</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>25.64</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>24.04</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-107.80</t>
+          <t>-34.06</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-106.53</t>
+          <t>-107.14</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>213049101.1527977</t>
+          <t>212831136.732808</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>40176524.0</t>
+          <t>143384401.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>41976405.2</t>
+          <t>63407579.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>57706625.4</t>
+          <t>64225704.8</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>194790217.74</t>
+          <t>196763751.52</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-15730220</t>
+          <t>-818125</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-22387203.01197561</t>
+          <t>-20792695.44174149</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-20985868.9841724</t>
+          <t>-12022903.80545378</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>40176524</v>
+        <v>143384401</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>134.29</t>
+          <t>137.74</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="CJ23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/ITO導電基板.xlsx
+++ b/Result/checksun_type/ITO導電基板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-51.37</t>
+          <t>-35.31</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,52 +1014,52 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>958</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1069,22 +1069,22 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>23.61</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>160.83</t>
+          <t>430.70</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-104.65</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>82668.7005730659</t>
+          <t>82600.4592274678</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>6324.0</t>
+          <t>9629.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>13005.4</t>
+          <t>14884.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>7283.74</t>
+          <t>7449.74</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-6681</t>
+          <t>-5255</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>654.2930458832735</t>
+          <t>679.2619911243006</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-343.1385080735217</t>
+          <t>816.5911899499497</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>4013</v>
+        <v>23312</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>109.77</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-41.51</t>
+          <t>-51.37</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>958</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>64.93</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>23.61</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>115.43</t>
+          <t>160.83</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.52</t>
+          <t>-104.65</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>82668.7005730659</t>
+          <t>82600.4592274678</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>7527.4</t>
+          <t>6324.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>12868.8</t>
+          <t>13005.4</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>7378.32</t>
+          <t>7283.74</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-5341</t>
+          <t>-6681</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>835.6442375117817</t>
+          <t>654.2930458832735</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>80.10972718128687</t>
+          <t>-343.1385080735217</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>5494</v>
+        <v>4013</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-10.70</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>109.77</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-34.19</t>
+          <t>-41.51</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.32</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>958</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>64.93</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>108.28</t>
+          <t>115.43</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-108.40</t>
+          <t>-106.52</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>82668.7005730659</t>
+          <t>82600.4592274678</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>8284.4</t>
+          <t>7527.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>12587.7</t>
+          <t>12868.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>7563.22</t>
+          <t>7378.32</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-4303</t>
+          <t>-5341</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>973.0141484809627</t>
+          <t>835.6442375117817</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>523.2104301459694</t>
+          <t>80.10972718128687</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>7065</v>
+        <v>5494</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-12.06</t>
+          <t>-10.70</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>109.77</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>-34.19</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-10.32</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>958</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>81.76</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>23.33</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>119.34</t>
+          <t>108.28</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-108.40</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>82668.7005730659</t>
+          <t>82600.4592274678</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>14123.0</t>
+          <t>8284.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>12216.7</t>
+          <t>12587.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>7629.54</t>
+          <t>7563.22</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>-4303</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>1054.796642723689</t>
+          <t>973.0141484809627</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>969.2039190188734</t>
+          <t>523.2104301459694</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>8262</v>
+        <v>7065</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-12.06</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>109.77</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>293.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,84 +2642,84 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>15.60</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-1.84</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>73.69</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,280 +2758,280 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>958</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>81.76</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
+          <t>23.49</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>22.46</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>23.57</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>119.34</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-110.67</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>82600.4592274678</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>14123.0</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>12216.7</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>7629.54</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>1054.796642723689</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>969.2039190188734</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>8262</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>-8.37</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>-13.42998910113004</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-25.43417574544826</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>-6.333574654154932</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>109.77</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>19.70%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>89.09</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>1653</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>安可-光電業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>光電業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>23.45</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>24.05</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>22.43</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>23.42</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>92.50</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-113.86</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>82668.7005730659</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>20139.2</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>11594.6</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>7648.36</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>8544</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>1070.358956124564</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>1443.473048872349</t>
-        </is>
-      </c>
-      <c r="BD6" t="n">
-        <v>6786</v>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>-10.51</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>-13.42998910113004</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>-25.43417574544826</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>-6.333574654154932</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>106.14</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>19.70%</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>-0.85%</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>86.4</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>1599</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>安可-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>光電業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>23.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>426.0</t>
+          <t>293.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>75.73</t>
+          <t>73.69</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>958</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>91.82</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>22.43</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>87.14</t>
+          <t>92.50</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-113.86</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>82668.7005730659</t>
+          <t>82600.4592274678</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19686.8</t>
+          <t>20139.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>11202.7</t>
+          <t>11594.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>8102.12</t>
+          <t>7648.36</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1002.520030170422</t>
+          <t>1070.358956124564</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>2227.590625489014</t>
+          <t>1443.473048872349</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>10030</v>
+        <v>6786</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>109.77</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>390.0</t>
+          <t>426.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>75.73</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>958</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>91.82</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>69.08</t>
+          <t>87.14</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-120.78</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>82668.7005730659</t>
+          <t>82600.4592274678</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>18210.2</t>
+          <t>19686.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>10729.5</t>
+          <t>11202.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>8369.26</t>
+          <t>8102.12</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>779.7799219306776</t>
+          <t>1002.520030170422</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>2920.630355459645</t>
+          <t>2227.590625489014</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>9279</v>
+        <v>10030</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>109.77</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3893,17 +3893,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
+          <t>23.15</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>23.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1498.0</t>
+          <t>390.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>65.67</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>958</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>86.42</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>69.08</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-124.37</t>
+          <t>-120.78</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>82668.7005730659</t>
+          <t>82600.4592274678</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>36258.0</t>
+          <t>9279.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>16891.0</t>
+          <t>18210.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>10195.3</t>
+          <t>10729.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>10437.66</t>
+          <t>8369.26</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>390.5343885617743</t>
+          <t>779.7799219306776</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>3886.843171294131</t>
+          <t>2920.630355459645</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>36258</v>
+        <v>9279</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>109.77</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1623.0</t>
+          <t>1498.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>65.67</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>958</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>61.41</t>
+          <t>86.42</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>46.64</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-127.21</t>
+          <t>-124.37</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>82668.7005730659</t>
+          <t>82600.4592274678</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>38343.0</t>
+          <t>36258.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>10310.4</t>
+          <t>16891.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>7058.7</t>
+          <t>10195.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>13160.96</t>
+          <t>10437.66</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-245.1581173895633</t>
+          <t>390.5343885617743</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>2237.724223511461</t>
+          <t>3886.843171294131</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>38343</v>
+        <v>36258</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>109.77</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>1623.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-16.18</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-13.49</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>958</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>61.41</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>26.72</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-129.03</t>
+          <t>-127.21</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>82668.7005730659</t>
+          <t>82600.4592274678</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>4524.0</t>
+          <t>38343.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>10310.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>3638.9</t>
+          <t>7058.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>12810.66</t>
+          <t>13160.96</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-588</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-696.5912702806586</t>
+          <t>-245.1581173895633</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-421.4715670177616</t>
+          <t>2237.724223511461</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>4524</v>
+        <v>38343</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-15.18</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>109.77</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8.57</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-26.87</t>
+          <t>-16.18</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-13.49</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,72 +5374,72 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>958</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-11.42</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-128.78</t>
+          <t>-129.03</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>82668.7005730659</t>
+          <t>82600.4592274678</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2647.0</t>
+          <t>4524.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2718.6</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>3717.5</t>
+          <t>3638.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>13031.08</t>
+          <t>12810.66</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-998</t>
+          <t>-588</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-746.6130345102762</t>
+          <t>-696.5912702806586</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-581.8058546660172</t>
+          <t>-421.4715670177616</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>2647</v>
+        <v>4524</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-16.93</t>
+          <t>-15.18</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>109.77</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1738.819</t>
+          <t>2804.104</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>13.38</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>62.79</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>28.81</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-6.14</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>24.49</t>
+          <t>24.42</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>26.01</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-37.74</t>
+          <t>-18.96</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-112.66</t>
+          <t>-113.29</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>212831136.732808</t>
+          <t>212675580.8111588</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>40606624.0</t>
+          <t>69398365.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>40014316.2</t>
+          <t>46175655.8</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>41687883.7</t>
+          <t>40727993.5</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>195169236.84</t>
+          <t>194676121.56</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-1673567</t>
+          <t>5447662</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-12999035.07091543</t>
+          <t>-11924068.20702655</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-9065902.528399438</t>
+          <t>-6011750.455637693</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>40606624</v>
+        <v>69398365</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,17 +6003,17 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>137.74</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1462.411</t>
+          <t>1738.819</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-23.72</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,67 +6246,67 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>24.49</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-50.35</t>
+          <t>-37.74</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-111.47</t>
+          <t>-112.66</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>212831136.732808</t>
+          <t>212675580.8111588</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>33681849.0</t>
+          <t>40606624.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>39637812.8</t>
+          <t>40014316.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>51965661.4</t>
+          <t>41687883.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>195984000.1</t>
+          <t>195169236.84</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-12327848</t>
+          <t>-1673567</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-13714150.07864561</t>
+          <t>-12999035.07091543</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-10020365.29204483</t>
+          <t>-9065902.528399438</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>33681849</v>
+        <v>40606624</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>14.50</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>137.74</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
+          <t>23.05</t>
+        </is>
+      </c>
+      <c r="CG14" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>22.8</t>
-        </is>
-      </c>
-      <c r="CG14" t="inlineStr">
-        <is>
-          <t>22.9</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2112.165</t>
+          <t>1462.411</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-26.70</t>
+          <t>-23.72</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,12 +6682,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6702,57 +6702,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-48.21</t>
+          <t>-50.35</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-110.02</t>
+          <t>-111.47</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>212831136.732808</t>
+          <t>212675580.8111588</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>49106509.0</t>
+          <t>33681849.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>38566967.2</t>
+          <t>39637812.8</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>52615128.9</t>
+          <t>51965661.4</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>195992723.02</t>
+          <t>195984000.1</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-14048161</t>
+          <t>-12327848</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-14385747.31257303</t>
+          <t>-13714150.07864561</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-10284073.15825091</t>
+          <t>-10020365.29204483</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>49106509</v>
+        <v>33681849</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>15.75</t>
+          <t>14.50</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>137.74</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1579.409</t>
+          <t>2112.165</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-32.96</t>
+          <t>-26.70</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,17 +7118,17 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>36.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -7138,32 +7138,32 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>6.62</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>23.88</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>25.06</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
@@ -7173,22 +7173,22 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>24.37</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-39.74</t>
+          <t>-48.21</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-108.82</t>
+          <t>-110.02</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>212831136.732808</t>
+          <t>212675580.8111588</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>38084932.0</t>
+          <t>49106509.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>35331650.4</t>
+          <t>38566967.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>52705529.4</t>
+          <t>52615128.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>195762947.24</t>
+          <t>195992723.02</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-17373879</t>
+          <t>-14048161</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-15131506.2497225</t>
+          <t>-14385747.31257303</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-11946152.49717921</t>
+          <t>-10284073.15825091</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>38084932</v>
+        <v>49106509</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>21.50</t>
+          <t>15.75</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,17 +7311,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>137.74</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7381,17 +7381,17 @@
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1646.332</t>
+          <t>1579.409</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-31.86</t>
+          <t>-32.96</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,67 +7554,67 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.07</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>13.77</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>6.62</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>24.37</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-54.01</t>
+          <t>-39.74</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-107.94</t>
+          <t>-108.82</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>212831136.732808</t>
+          <t>212675580.8111588</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>38591667.0</t>
+          <t>38084932.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>35280331.2</t>
+          <t>35331650.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>51774555.3</t>
+          <t>52705529.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>196053683.56</t>
+          <t>195762947.24</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-16494224</t>
+          <t>-17373879</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-15710661.47745765</t>
+          <t>-15131506.2497225</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-12713019.99932038</t>
+          <t>-11946152.49717921</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>38591667</v>
+        <v>38084932</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>21.50</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,17 +7747,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>137.74</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1604.993</t>
+          <t>1646.332</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,72 +7874,72 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-2.64</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-31.86</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
           <t>23.85</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>-1.27</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-1.82</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>-18.78</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2025-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -7954,12 +7954,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8005,62 +8005,62 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>13.77</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>25.44</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>25.96</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-27.44</t>
+          <t>-54.01</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-106.87</t>
+          <t>-107.94</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,50 +8080,50 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>212831136.732808</t>
+          <t>212675580.8111588</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>38724107.0</t>
+          <t>38591667.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>43361451.2</t>
+          <t>35280331.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>53384515.1</t>
+          <t>51774555.3</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>197488634.64</t>
+          <t>196053683.56</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-10023063</t>
+          <t>-16494224</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-16255687.20075533</t>
+          <t>-15710661.47745765</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-13408801.60954632</t>
+          <t>-12713019.99932038</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>38724107</v>
+        <v>38591667</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>137.74</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1126.956</t>
+          <t>1604.993</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,74 +8310,74 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-2.64</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-18.78</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>24.9</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>-5.73</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-1.82</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>21.00</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2025-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>24.9</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
       <c r="T19" t="inlineStr">
         <is>
           <t>24.8</t>
@@ -8390,14 +8390,14 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>-4.22</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>4.40</t>
-        </is>
-      </c>
       <c r="X19" t="inlineStr">
         <is>
           <t>-9.29</t>
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,77 +8426,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>25.56</t>
+          <t>25.44</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>25.96</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>-27.44</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-106.40</t>
+          <t>-106.87</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>212831136.732808</t>
+          <t>212675580.8111588</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>28327621.0</t>
+          <t>38724107.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>64293510.0</t>
+          <t>43361451.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>53134957.6</t>
+          <t>53384515.1</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>197699079.6</t>
+          <t>197488634.64</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>11158552</t>
+          <t>-10023063</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-16773302.76279333</t>
+          <t>-16255687.20075533</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-13938079.56667101</t>
+          <t>-13408801.60954632</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>28327621</v>
+        <v>38724107</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>24.50</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>137.74</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1301.232</t>
+          <t>1126.956</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,22 +8756,22 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,72 +8862,72 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>71.74</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>25.56</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>25.94</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>24.19</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>13.70</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-106.48</t>
+          <t>-106.40</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,50 +8952,50 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>212831136.732808</t>
+          <t>212675580.8111588</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>32929925.0</t>
+          <t>28327621.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>66663290.6</t>
+          <t>64293510.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>54706545.9</t>
+          <t>53134957.6</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>197755621.26</t>
+          <t>197699079.6</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>11956744</t>
+          <t>11158552</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-17288797.88936103</t>
+          <t>-16773302.76279333</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-13082493.16375375</t>
+          <t>-13938079.56667101</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>32929925</v>
+        <v>28327621</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.50</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,17 +9055,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>137.74</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1463.862</t>
+          <t>1301.232</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-8.92</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>21.86</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,77 +9298,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>73.91</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>71.74</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.58</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>25.82</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>24.14</t>
+          <t>24.19</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>13.70</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-106.70</t>
+          <t>-106.48</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>212831136.732808</t>
+          <t>212675580.8111588</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>37828336.0</t>
+          <t>32929925.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>70079408.4</t>
+          <t>66663290.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>58159640.7</t>
+          <t>54706545.9</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>197616845.6</t>
+          <t>197755621.26</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>11919767</t>
+          <t>11956744</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-18053580.56674417</t>
+          <t>-17288797.88936103</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-11886098.97516645</t>
+          <t>-13082493.16375375</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>37828336</v>
+        <v>32929925</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,17 +9491,17 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>137.74</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3002.694</t>
+          <t>1463.862</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-10.83</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,47 +9734,47 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>93.48</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -9784,27 +9784,27 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>24.09</t>
+          <t>24.14</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-107.04</t>
+          <t>-106.70</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>212831136.732808</t>
+          <t>212675580.8111588</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>78997267.0</t>
+          <t>37828336.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>68268779.4</t>
+          <t>70079408.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>64193506.3</t>
+          <t>58159640.7</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>197596036.22</t>
+          <t>197616845.6</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>4075273</t>
+          <t>11919767</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-19174940.85612193</t>
+          <t>-18053580.56674417</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-10277290.63521439</t>
+          <t>-11886098.97516645</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>78997267</v>
+        <v>37828336</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>30.50</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>137.74</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5509.073</t>
+          <t>3002.694</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-11.46</t>
+          <t>-7.63</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,72 +10170,72 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.48</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.03</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>25.62</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>24.04</t>
+          <t>24.09</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-34.06</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-107.14</t>
+          <t>-107.04</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>212831136.732808</t>
+          <t>212675580.8111588</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>143384401.0</t>
+          <t>78997267.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>63407579.0</t>
+          <t>68268779.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>64225704.8</t>
+          <t>64193506.3</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>196763751.52</t>
+          <t>197596036.22</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-818125</t>
+          <t>4075273</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-20792695.44174149</t>
+          <t>-19174940.85612193</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-12022903.80545378</t>
+          <t>-10277290.63521439</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>143384401</v>
+        <v>78997267</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.50</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>137.74</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/ITO導電基板.xlsx
+++ b/Result/checksun_type/ITO導電基板.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>23.32</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>22.57</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>23.26</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>22.57</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>23.26</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>23312.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>9629.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>9629.200000000001</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>14884.2</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>7449.74</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>7449.74</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>816.5911899499497</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>23312</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>23312.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>23.09</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>22.5</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>23.26</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>23.26</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>4013.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>6324.0</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>6324</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>13005.4</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>7283.74</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>7283.74</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-343.1385080735217</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>4013</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>4013.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>23.13</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>22.46</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>23.28</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>23.28</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>5494.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>7527.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>7527.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>12868.8</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>7378.32</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>7378.32</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>80.10972718128687</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>5494</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>5494.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>23.3</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>22.45</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>23.33</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>23.33</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>7065.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>8284.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>8284.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>12587.7</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>7563.22</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>7563.22</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>523.2104301459694</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>7065</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>7065.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>23.49</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>22.46</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>23.38</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>23.38</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>8262.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>14123.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>14123</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>12216.7</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>7629.54</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>7629.54</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>969.2039190188734</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>8262</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>23.55</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>22.43</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>23.42</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>23.42</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>6786.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>20139.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>20139.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>11594.6</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>7648.36</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>7648.36</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>1443.473048872349</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>6786</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>6786.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>23.31</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>22.42</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>23.46</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>22.42</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>23.46</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>10030.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>19686.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>19686.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>11202.7</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>8102.12</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>8102.12</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>2227.590625489014</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>10030</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>10030.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>22.87</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>22.38</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>22.38</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>23.5</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>9279.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>18210.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>18210.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>10729.5</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>8369.26</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>8369.26</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>2920.630355459645</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>9279</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>9279.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>22.35</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>22.34</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>23.54</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>22.34</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>23.54</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>36258.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>16891.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>16891</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>10195.3</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>10437.66</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>10437.66</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>3886.843171294131</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>36258</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>36258.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>21.96</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>22.29</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>23.62</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>23.62</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>38343.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>10310.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>10310.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>7058.7</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>13160.96</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>13160.96</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>2237.724223511461</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>38343</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>38343.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>21.53</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>22.23</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>23.66</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>23.66</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>4524.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>3050.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>3050</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>3638.9</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>12810.66</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>12810.66</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-421.4715670177616</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>4524</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>4524.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>23.63</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>24.42</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>26.01</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>26.01</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>69398365.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>46175655.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>46175655.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>40727993.5</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>194676121.56</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>194676121.56</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-6011750.455637693</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>69398365</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>69398365.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>23.42</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>24.49</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>25.98</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>24.49</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>25.98</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>40606624.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>40014316.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>40014316.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>41687883.7</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>195169236.84</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>195169236.84</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-9065902.528399438</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>40606624</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>40606624.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>23.48</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>24.64</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>25.97</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>25.97</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>33681849.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>39637812.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>39637812.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>51965661.4</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>195984000.1</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>195984000.1</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-10020365.29204483</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>33681849</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>33681849.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>23.88</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>24.85</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>25.98</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>25.98</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>49106509.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>38566967.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>38566967.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>52615128.9</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>195992723.02</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>195992723.02</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-10284073.15825091</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>49106509</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>49106509.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>24.26</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>25.98</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>25.98</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>38084932.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>35331650.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>35331650.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>52705529.4</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>195762947.24</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>195762947.24</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-11946152.49717921</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>38084932</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>38084932.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>24.53</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>25.22</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>25.95</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>25.22</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>25.95</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>38591667.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>35280331.2</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>35280331.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>51774555.3</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>196053683.56</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>196053683.56</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-12713019.99932038</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>38591667</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>38591667.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>25.11</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>25.44</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>25.96</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>25.44</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>25.96</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>38724107.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>43361451.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>43361451.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>53384515.1</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>197488634.64</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>197488634.64</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-13408801.60954632</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>38724107</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>38724107.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>25.59</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>25.56</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>25.94</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>25.94</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>28327621.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>64293510.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>64293510</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>53134957.6</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>197699079.6</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>197699079.6</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-13938079.56667101</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>28327621</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>28327621.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>25.52</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>25.58</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>25.88</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>25.88</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>32929925.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>66663290.6</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>66663290.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>54706545.9</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>197755621.26</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>197755621.26</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-13082493.16375375</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>32929925</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>32929925.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>25.35</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>25.62</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>25.82</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>25.82</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>37828336.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>70079408.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>70079408.40000001</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>58159640.7</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>197616845.6</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>197616845.6</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-11886098.97516645</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>37828336</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>37828336.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>25.03</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>25.62</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>25.76</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>25.76</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>78997267.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>68268779.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>68268779.40000001</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>64193506.3</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>197596036.22</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>197596036.22</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-10277290.63521439</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>78997267</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>78997267.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/ITO導電基板.xlsx
+++ b/Result/checksun_type/ITO導電基板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>361.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-35.31</t>
+          <t>-18.48</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>361</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>72.03</t>
+          <t>82.37</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>22.57</v>
+        <v>22.66</v>
       </c>
       <c r="AN2" t="n">
         <v>23.26</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>430.70</t>
+          <t>4280.47</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-99.77</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>82600.4592274678</t>
+          <t>82501.10142857143</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>9629.200000000001</v>
+        <v>9716.799999999999</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>14884.2</t>
+          <t>11919.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>7449.74</v>
+        <v>7436.54</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-5255</t>
+          <t>-2203</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>679.2619911243006</t>
+          <t>653.54279230789</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>816.5911899499497</t>
+          <t>512.0871988176314</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>109.77</t>
+          <t>108.86</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-51.37</t>
+          <t>-35.31</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>361</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>22.5</v>
+        <v>22.57</v>
       </c>
       <c r="AN3" t="n">
         <v>23.26</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>23.61</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>160.83</t>
+          <t>430.70</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-104.65</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>82600.4592274678</t>
+          <t>82501.10142857143</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>6324</v>
+        <v>9629.200000000001</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>13005.4</t>
+          <t>14884.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>7283.74</v>
+        <v>7449.74</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-6681</t>
+          <t>-5255</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>654.2930458832735</t>
+          <t>679.2619911243006</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-343.1385080735217</t>
+          <t>816.5911899499497</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>109.77</t>
+          <t>108.86</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-41.51</t>
+          <t>-51.37</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>361</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>64.93</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>22.46</v>
+        <v>22.5</v>
       </c>
       <c r="AN4" t="n">
-        <v>23.28</v>
+        <v>23.26</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>23.61</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>115.43</t>
+          <t>160.83</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.52</t>
+          <t>-104.65</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>82600.4592274678</t>
+          <t>82501.10142857143</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>7527.4</v>
+        <v>6324</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>12868.8</t>
+          <t>13005.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>7378.32</v>
+        <v>7283.74</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-5341</t>
+          <t>-6681</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>835.6442375117817</t>
+          <t>654.2930458832735</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>80.10972718128687</t>
+          <t>-343.1385080735217</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-10.70</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>109.77</t>
+          <t>108.86</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-34.19</t>
+          <t>-41.51</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.32</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>361</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>64.93</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>22.45</v>
+        <v>22.46</v>
       </c>
       <c r="AN5" t="n">
-        <v>23.33</v>
+        <v>23.28</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>108.28</t>
+          <t>115.43</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-108.40</t>
+          <t>-106.52</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>82600.4592274678</t>
+          <t>82501.10142857143</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>8284.4</v>
+        <v>7527.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>12587.7</t>
+          <t>12868.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>7563.22</v>
+        <v>7378.32</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-4303</t>
+          <t>-5341</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>973.0141484809627</t>
+          <t>835.6442375117817</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>523.2104301459694</t>
+          <t>80.10972718128687</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-12.06</t>
+          <t>-10.70</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>109.77</t>
+          <t>108.86</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>-34.19</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-10.32</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>361</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>81.76</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>22.46</v>
+        <v>22.45</v>
       </c>
       <c r="AN6" t="n">
-        <v>23.38</v>
+        <v>23.33</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>119.34</t>
+          <t>108.28</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-108.40</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>82600.4592274678</t>
+          <t>82501.10142857143</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>14123</v>
+        <v>8284.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>12216.7</t>
+          <t>12587.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>7629.54</v>
+        <v>7563.22</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>-4303</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>1054.796642723689</t>
+          <t>973.0141484809627</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>969.2039190188734</t>
+          <t>523.2104301459694</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-12.06</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>109.77</t>
+          <t>108.86</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>293.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,84 +3048,84 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>15.60</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>4.76</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>73.69</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>0</t>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,274 +3164,274 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>361</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>81.76</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
+          <t>23.49</t>
+        </is>
+      </c>
+      <c r="AM7" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>23.57</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>119.34</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-110.67</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>82501.10142857143</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>14123</v>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>12216.7</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>7629.54</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>1054.796642723689</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>969.2039190188734</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>-8.37</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>-13.42998910113004</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>-25.43417574544826</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>-6.333574654154932</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>108.86</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>19.70%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>89.61</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>1640</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>安可-光電業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>光電業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>23.45</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>24.05</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="AM7" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>23.42</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>92.50</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-113.86</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>82600.4592274678</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="n">
-        <v>20139.2</v>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>11594.6</t>
-        </is>
-      </c>
-      <c r="AZ7" t="n">
-        <v>7648.36</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>8544</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>1070.358956124564</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>1443.473048872349</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>-10.51</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>-13.42998910113004</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>-25.43417574544826</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>-6.333574654154932</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>109.77</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>19.70%</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>-0.85%</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>89.09</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>1653</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>安可-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>光電業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>23.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>426.0</t>
+          <t>293.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>75.73</t>
+          <t>73.69</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>361</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>91.82</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>22.42</v>
+        <v>22.43</v>
       </c>
       <c r="AN8" t="n">
-        <v>23.46</v>
+        <v>23.42</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>87.14</t>
+          <t>92.50</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-113.86</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>82600.4592274678</t>
+          <t>82501.10142857143</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>19686.8</v>
+        <v>20139.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>11202.7</t>
+          <t>11594.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>8102.12</v>
+        <v>7648.36</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>1002.520030170422</t>
+          <t>1070.358956124564</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>2227.590625489014</t>
+          <t>1443.473048872349</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>109.77</t>
+          <t>108.86</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>390.0</t>
+          <t>426.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>75.73</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>361</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>91.82</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>22.38</v>
+        <v>22.42</v>
       </c>
       <c r="AN9" t="n">
-        <v>23.5</v>
+        <v>23.46</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>69.08</t>
+          <t>87.14</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-120.78</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>82600.4592274678</t>
+          <t>82501.10142857143</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>18210.2</v>
+        <v>19686.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>10729.5</t>
+          <t>11202.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>8369.26</v>
+        <v>8102.12</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>779.7799219306776</t>
+          <t>1002.520030170422</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>2920.630355459645</t>
+          <t>2227.590625489014</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>109.77</t>
+          <t>108.86</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4281,17 +4281,17 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
+          <t>23.15</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>23.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1498.0</t>
+          <t>390.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>65.67</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>361</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>86.42</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>22.34</v>
+        <v>22.38</v>
       </c>
       <c r="AN10" t="n">
-        <v>23.54</v>
+        <v>23.5</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>69.08</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-124.37</t>
+          <t>-120.78</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>82600.4592274678</t>
+          <t>82501.10142857143</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>36258.0</t>
+          <t>9279.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>16891</v>
+        <v>18210.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>10195.3</t>
+          <t>10729.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>10437.66</v>
+        <v>8369.26</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>390.5343885617743</t>
+          <t>779.7799219306776</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>3886.843171294131</t>
+          <t>2920.630355459645</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>36258.0</t>
+          <t>9279.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>109.77</t>
+          <t>108.86</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1623.0</t>
+          <t>1498.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>65.67</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>361</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>61.41</t>
+          <t>86.42</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>22.29</v>
+        <v>22.34</v>
       </c>
       <c r="AN11" t="n">
-        <v>23.62</v>
+        <v>23.54</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>46.64</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-127.21</t>
+          <t>-124.37</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>82600.4592274678</t>
+          <t>82501.10142857143</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>38343.0</t>
+          <t>36258.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>10310.4</v>
+        <v>16891</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>7058.7</t>
+          <t>10195.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>13160.96</v>
+        <v>10437.66</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-245.1581173895633</t>
+          <t>390.5343885617743</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>2237.724223511461</t>
+          <t>3886.843171294131</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>38343.0</t>
+          <t>36258.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>109.77</t>
+          <t>108.86</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>1623.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-16.18</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-13.49</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,211 +5314,211 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>361</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>61.41</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
+          <t>8.61</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>-1.49</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>-5.64</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>21.96</t>
+        </is>
+      </c>
+      <c r="AM12" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>23.48</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>26.72</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>-0.40</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-127.21</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>82501.10142857143</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>38343.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="n">
+        <v>10310.4</v>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>7058.7</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>13160.96</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>3251</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-245.1581173895633</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>2237.724223511461</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>38343.0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>-7.20</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-13.42998910113004</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>-25.43417574544826</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>-6.333574654154932</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>-3.14</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>-6.03</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>21.53</t>
-        </is>
-      </c>
-      <c r="AM12" t="n">
-        <v>22.23</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>23.66</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>23.47</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-3.44</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.60</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.58</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-129.03</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>82600.4592274678</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>4524.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="n">
-        <v>3050</v>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>3638.9</t>
-        </is>
-      </c>
-      <c r="AZ12" t="n">
-        <v>12810.66</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>-588</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-696.5912702806586</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>-421.4715670177616</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>4524.0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>-15.18</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>-13.42998910113004</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>-25.43417574544826</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>-6.333574654154932</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
       <c r="BU12" t="inlineStr">
         <is>
           <t>3.47</t>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>109.77</t>
+          <t>108.86</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2804.104</t>
+          <t>1677.95</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>13.38</t>
+          <t>13.97</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,68 +5744,68 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>62.79</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>60.48</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-6.14</t>
+          <t>-6.15</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>23.73</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>24.42</v>
+        <v>24.41</v>
       </c>
       <c r="AN13" t="n">
         <v>26.01</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>24.59</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-18.96</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -5820,53 +5820,53 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-113.29</t>
+          <t>-113.26</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>212675580.8111588</t>
+          <t>212460173.9078571</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>69398365.0</t>
+          <t>41260499.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>46175655.8</v>
+        <v>46810769.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>40727993.5</t>
+          <t>41071209.8</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>194676121.56</v>
+        <v>184113554.72</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>5447662</t>
+          <t>5739559</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-11924068.20702655</t>
+          <t>-10987117.74337839</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-6011750.455637693</t>
+          <t>-5833890.193313524</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>69398365.0</t>
+          <t>41260499.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.62</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>9182</t>
+          <t>9390</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1738.819</t>
+          <t>2804.104</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>13.38</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>62.79</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>28.81</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-6.14</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>24.49</v>
+        <v>24.42</v>
       </c>
       <c r="AN14" t="n">
-        <v>25.98</v>
+        <v>26.01</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-37.74</t>
+          <t>-18.96</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,53 +6250,53 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-112.66</t>
+          <t>-113.29</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>212675580.8111588</t>
+          <t>212460173.9078571</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>40606624.0</t>
+          <t>69398365.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>40014316.2</v>
+        <v>46175655.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>41687883.7</t>
+          <t>40727993.5</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>195169236.84</v>
+        <v>194676121.56</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-1673567</t>
+          <t>5447662</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-12999035.07091543</t>
+          <t>-11924068.20702655</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-9065902.528399438</t>
+          <t>-6011750.455637693</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>40606624.0</t>
+          <t>69398365.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,17 +6361,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.62</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>9182</t>
+          <t>9390</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1462.411</t>
+          <t>1738.819</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-23.72</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,63 +6604,63 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>24.64</v>
+        <v>24.49</v>
       </c>
       <c r="AN15" t="n">
-        <v>25.97</v>
+        <v>25.98</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-50.35</t>
+          <t>-37.74</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,53 +6680,53 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-111.47</t>
+          <t>-112.66</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>212675580.8111588</t>
+          <t>212460173.9078571</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>33681849.0</t>
+          <t>40606624.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>39637812.8</v>
+        <v>40014316.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>51965661.4</t>
+          <t>41687883.7</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>195984000.1</v>
+        <v>195169236.84</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-12327848</t>
+          <t>-1673567</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-13714150.07864561</t>
+          <t>-12999035.07091543</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-10020365.29204483</t>
+          <t>-9065902.528399438</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>33681849.0</t>
+          <t>40606624.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>14.50</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.62</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>9182</t>
+          <t>9390</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
+          <t>23.05</t>
+        </is>
+      </c>
+      <c r="CG15" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>22.8</t>
-        </is>
-      </c>
-      <c r="CG15" t="inlineStr">
-        <is>
-          <t>22.9</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2112.165</t>
+          <t>1462.411</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-26.70</t>
+          <t>-23.72</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,12 +7034,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7054,53 +7054,53 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>24.85</v>
+        <v>24.64</v>
       </c>
       <c r="AN16" t="n">
-        <v>25.98</v>
+        <v>25.97</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-48.21</t>
+          <t>-50.35</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,53 +7110,53 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-110.02</t>
+          <t>-111.47</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>212675580.8111588</t>
+          <t>212460173.9078571</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>49106509.0</t>
+          <t>33681849.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>38566967.2</v>
+        <v>39637812.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>52615128.9</t>
+          <t>51965661.4</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>195992723.02</v>
+        <v>195984000.1</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-14048161</t>
+          <t>-12327848</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-14385747.31257303</t>
+          <t>-13714150.07864561</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-10284073.15825091</t>
+          <t>-10020365.29204483</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>49106509.0</t>
+          <t>33681849.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>15.75</t>
+          <t>14.50</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.62</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>9182</t>
+          <t>9390</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1579.409</t>
+          <t>2112.165</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-32.96</t>
+          <t>-26.70</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,17 +7464,17 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>36.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -7484,53 +7484,53 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>6.62</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>23.88</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>25.06</v>
+        <v>24.85</v>
       </c>
       <c r="AN17" t="n">
         <v>25.98</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>24.37</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-39.74</t>
+          <t>-48.21</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,53 +7540,53 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-108.82</t>
+          <t>-110.02</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>212675580.8111588</t>
+          <t>212460173.9078571</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>38084932.0</t>
+          <t>49106509.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>35331650.4</v>
+        <v>38566967.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>52705529.4</t>
+          <t>52615128.9</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>195762947.24</v>
+        <v>195992723.02</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-17373879</t>
+          <t>-14048161</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-15131506.2497225</t>
+          <t>-14385747.31257303</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-11946152.49717921</t>
+          <t>-10284073.15825091</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>38084932.0</t>
+          <t>49106509.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>21.50</t>
+          <t>15.75</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.62</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>9182</t>
+          <t>9390</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7721,17 +7721,17 @@
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1646.332</t>
+          <t>1579.409</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-31.86</t>
+          <t>-32.96</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,63 +7894,63 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.07</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>13.77</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>6.62</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>25.22</v>
+        <v>25.06</v>
       </c>
       <c r="AN18" t="n">
-        <v>25.95</v>
+        <v>25.98</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>24.37</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-54.01</t>
+          <t>-39.74</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,53 +7970,53 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-107.94</t>
+          <t>-108.82</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>212675580.8111588</t>
+          <t>212460173.9078571</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>38591667.0</t>
+          <t>38084932.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>35280331.2</v>
+        <v>35331650.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>51774555.3</t>
+          <t>52705529.4</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>196053683.56</v>
+        <v>195762947.24</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-16494224</t>
+          <t>-17373879</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-15710661.47745765</t>
+          <t>-15131506.2497225</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-12713019.99932038</t>
+          <t>-11946152.49717921</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>38591667.0</t>
+          <t>38084932.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>21.50</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.62</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>9182</t>
+          <t>9390</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1604.993</t>
+          <t>1646.332</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,72 +8208,72 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6.45</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-3.59</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-31.86</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
           <t>23.85</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-2.64</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>-18.78</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2025-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,12 +8324,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8339,58 +8339,58 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>13.77</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>25.44</v>
+        <v>25.22</v>
       </c>
       <c r="AN19" t="n">
-        <v>25.96</v>
+        <v>25.95</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-27.44</t>
+          <t>-54.01</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,58 +8400,58 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-106.87</t>
+          <t>-107.94</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>212675580.8111588</t>
+          <t>212460173.9078571</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>38724107.0</t>
+          <t>38591667.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>43361451.2</v>
+        <v>35280331.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>53384515.1</t>
+          <t>51774555.3</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>197488634.64</v>
+        <v>196053683.56</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-10023063</t>
+          <t>-16494224</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-16255687.20075533</t>
+          <t>-15710661.47745765</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-13408801.60954632</t>
+          <t>-12713019.99932038</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>38724107.0</t>
+          <t>38591667.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.62</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>9182</t>
+          <t>9390</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8613,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1126.956</t>
+          <t>1604.993</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,74 +8638,74 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>3.83</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-3.59</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-18.78</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>24.9</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-2.68</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-2.64</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>21.00</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2025-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>24.9</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
       <c r="T20" t="inlineStr">
         <is>
           <t>24.8</t>
@@ -8718,14 +8718,14 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
+          <t>-4.22</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>4.40</t>
-        </is>
-      </c>
       <c r="X20" t="inlineStr">
         <is>
           <t>-9.29</t>
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>25.56</v>
+        <v>25.44</v>
       </c>
       <c r="AN20" t="n">
-        <v>25.94</v>
+        <v>25.96</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>-27.44</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,53 +8830,53 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-106.40</t>
+          <t>-106.87</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>212675580.8111588</t>
+          <t>212460173.9078571</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>28327621.0</t>
+          <t>38724107.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>64293510</v>
+        <v>43361451.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>53134957.6</t>
+          <t>53384515.1</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>197699079.6</v>
+        <v>197488634.64</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>11158552</t>
+          <t>-10023063</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-16773302.76279333</t>
+          <t>-16255687.20075533</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-13938079.56667101</t>
+          <t>-13408801.60954632</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>28327621.0</t>
+          <t>38724107.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>24.50</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.62</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>9182</t>
+          <t>9390</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1301.232</t>
+          <t>1126.956</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,22 +9078,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -9148,12 +9148,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,68 +9184,68 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>71.74</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>25.58</v>
+        <v>25.56</v>
       </c>
       <c r="AN21" t="n">
-        <v>25.88</v>
+        <v>25.94</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>24.19</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>13.70</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -9260,58 +9260,58 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-106.48</t>
+          <t>-106.40</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>212675580.8111588</t>
+          <t>212460173.9078571</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>32929925.0</t>
+          <t>28327621.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>66663290.6</v>
+        <v>64293510</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>54706545.9</t>
+          <t>53134957.6</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>197755621.26</v>
+        <v>197699079.6</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>11956744</t>
+          <t>11158552</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-17288797.88936103</t>
+          <t>-16773302.76279333</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-13082493.16375375</t>
+          <t>-13938079.56667101</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>32929925.0</t>
+          <t>28327621.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.50</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.62</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>9182</t>
+          <t>9390</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1463.862</t>
+          <t>1301.232</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>21.86</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>73.91</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>71.74</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>25.62</v>
+        <v>25.58</v>
       </c>
       <c r="AN22" t="n">
-        <v>25.82</v>
+        <v>25.88</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>24.14</t>
+          <t>24.19</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>13.70</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,53 +9690,53 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-106.70</t>
+          <t>-106.48</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>212675580.8111588</t>
+          <t>212460173.9078571</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>37828336.0</t>
+          <t>32929925.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>70079408.40000001</v>
+        <v>66663290.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>58159640.7</t>
+          <t>54706545.9</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>197616845.6</v>
+        <v>197755621.26</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>11919767</t>
+          <t>11956744</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-18053580.56674417</t>
+          <t>-17288797.88936103</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-11886098.97516645</t>
+          <t>-13082493.16375375</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>37828336.0</t>
+          <t>32929925.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.62</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>9182</t>
+          <t>9390</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3002.694</t>
+          <t>1463.862</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-7.63</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>93.48</t>
+          <t>73.91</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>25.03</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="AM23" t="n">
         <v>25.62</v>
       </c>
       <c r="AN23" t="n">
-        <v>25.76</v>
+        <v>25.82</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>24.09</t>
+          <t>24.14</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,53 +10120,53 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-107.04</t>
+          <t>-106.70</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>212675580.8111588</t>
+          <t>212460173.9078571</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>78997267.0</t>
+          <t>37828336.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>68268779.40000001</v>
+        <v>70079408.40000001</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>64193506.3</t>
+          <t>58159640.7</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>197596036.22</v>
+        <v>197616845.6</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>4075273</t>
+          <t>11919767</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-19174940.85612193</t>
+          <t>-18053580.56674417</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-10277290.63521439</t>
+          <t>-11886098.97516645</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>78997267.0</t>
+          <t>37828336.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>30.50</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>138.62</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>9182</t>
+          <t>9390</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/ITO導電基板.xlsx
+++ b/Result/checksun_type/ITO導電基板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>361.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,79 +898,79 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-1.15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>6.64</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>23.95</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-18.48</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>23.0</t>
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>77.42</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>82.37</t>
+          <t>88.17</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>22.66</v>
+        <v>22.74</v>
       </c>
       <c r="AN2" t="n">
         <v>23.26</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>4280.47</t>
+          <t>362.90</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-99.77</t>
+          <t>-97.51</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>82501.10142857143</t>
+          <t>82395.80670470756</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>9716.799999999999</v>
+        <v>9462.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>11919.9</t>
+          <t>8873.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>7436.54</v>
+        <v>7472.64</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2203</t>
+          <t>589</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>653.54279230789</t>
+          <t>563.475781961225</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>512.0871988176314</t>
+          <t>68.1072250545676</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>108.86</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
           <t>24.05</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>24.45</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>361.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-35.31</t>
+          <t>-18.48</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>72.03</t>
+          <t>82.37</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>22.57</v>
+        <v>22.66</v>
       </c>
       <c r="AN3" t="n">
         <v>23.26</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>430.70</t>
+          <t>4280.47</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-99.77</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>82501.10142857143</t>
+          <t>82395.80670470756</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>9629.200000000001</v>
+        <v>9716.799999999999</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>14884.2</t>
+          <t>11919.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>7449.74</v>
+        <v>7436.54</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-5255</t>
+          <t>-2203</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>679.2619911243006</t>
+          <t>653.54279230789</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>816.5911899499497</t>
+          <t>512.0871988176314</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>108.86</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-51.37</t>
+          <t>-35.31</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>22.5</v>
+        <v>22.57</v>
       </c>
       <c r="AN4" t="n">
         <v>23.26</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>23.61</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>160.83</t>
+          <t>430.70</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.65</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>82501.10142857143</t>
+          <t>82395.80670470756</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>6324</v>
+        <v>9629.200000000001</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>13005.4</t>
+          <t>14884.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>7283.74</v>
+        <v>7449.74</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-6681</t>
+          <t>-5255</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>654.2930458832735</t>
+          <t>679.2619911243006</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-343.1385080735217</t>
+          <t>816.5911899499497</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>108.86</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-41.51</t>
+          <t>-51.37</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>64.93</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>22.46</v>
+        <v>22.5</v>
       </c>
       <c r="AN5" t="n">
-        <v>23.28</v>
+        <v>23.26</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>23.61</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>115.43</t>
+          <t>160.83</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-106.52</t>
+          <t>-104.65</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>82501.10142857143</t>
+          <t>82395.80670470756</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>7527.4</v>
+        <v>6324</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>12868.8</t>
+          <t>13005.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>7378.32</v>
+        <v>7283.74</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-5341</t>
+          <t>-6681</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>835.6442375117817</t>
+          <t>654.2930458832735</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>80.10972718128687</t>
+          <t>-343.1385080735217</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-10.70</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>108.86</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-34.19</t>
+          <t>-41.51</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.32</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>64.93</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>22.45</v>
+        <v>22.46</v>
       </c>
       <c r="AN6" t="n">
-        <v>23.33</v>
+        <v>23.28</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>108.28</t>
+          <t>115.43</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-108.40</t>
+          <t>-106.52</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>82501.10142857143</t>
+          <t>82395.80670470756</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>8284.4</v>
+        <v>7527.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>12587.7</t>
+          <t>12868.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>7563.22</v>
+        <v>7378.32</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-4303</t>
+          <t>-5341</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>973.0141484809627</t>
+          <t>835.6442375117817</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>523.2104301459694</t>
+          <t>80.10972718128687</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-12.06</t>
+          <t>-10.70</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>108.86</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>-34.19</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-10.32</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>81.76</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>22.46</v>
+        <v>22.45</v>
       </c>
       <c r="AN7" t="n">
-        <v>23.38</v>
+        <v>23.33</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>119.34</t>
+          <t>108.28</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-108.40</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>82501.10142857143</t>
+          <t>82395.80670470756</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>14123</v>
+        <v>8284.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>12216.7</t>
+          <t>12587.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>7629.54</v>
+        <v>7563.22</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>-4303</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1054.796642723689</t>
+          <t>973.0141484809627</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>969.2039190188734</t>
+          <t>523.2104301459694</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-12.06</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>108.86</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>293.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,84 +3478,84 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-1.15</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>15.60</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>3.97</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>73.69</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,274 +3594,274 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>81.76</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
+          <t>23.49</t>
+        </is>
+      </c>
+      <c r="AM8" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>23.57</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>119.34</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-110.67</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>82395.80670470756</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>14123</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>12216.7</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>7629.54</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>1054.796642723689</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>969.2039190188734</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>-8.37</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>-13.42998910113004</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>-25.43417574544826</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>-6.333574654154932</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>108.18</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>19.70%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>89.32</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>1630</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>安可-光電業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>光電業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>23.45</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>24.05</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="AM8" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>23.42</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>92.50</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-113.86</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>82501.10142857143</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="n">
-        <v>20139.2</v>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>11594.6</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>7648.36</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>8544</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>1070.358956124564</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>1443.473048872349</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>-10.51</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>-13.42998910113004</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>-25.43417574544826</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>-6.333574654154932</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>108.86</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>19.70%</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>-0.85%</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>89.61</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>1640</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>安可-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>光電業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>23.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>426.0</t>
+          <t>293.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>75.73</t>
+          <t>73.69</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>91.82</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>22.42</v>
+        <v>22.43</v>
       </c>
       <c r="AN9" t="n">
-        <v>23.46</v>
+        <v>23.42</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>87.14</t>
+          <t>92.50</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-113.86</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>82501.10142857143</t>
+          <t>82395.80670470756</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>19686.8</v>
+        <v>20139.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>11202.7</t>
+          <t>11594.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>8102.12</v>
+        <v>7648.36</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1002.520030170422</t>
+          <t>1070.358956124564</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>2227.590625489014</t>
+          <t>1443.473048872349</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>108.86</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,42 +4323,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>-1.05</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>426.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>1.05</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>390.0</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>23.8</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>75.73</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>91.82</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>22.38</v>
+        <v>22.42</v>
       </c>
       <c r="AN10" t="n">
-        <v>23.5</v>
+        <v>23.46</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>69.08</t>
+          <t>87.14</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-120.78</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>82501.10142857143</t>
+          <t>82395.80670470756</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>18210.2</v>
+        <v>19686.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>10729.5</t>
+          <t>11202.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>8369.26</v>
+        <v>8102.12</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>779.7799219306776</t>
+          <t>1002.520030170422</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>2920.630355459645</t>
+          <t>2227.590625489014</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>108.86</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4711,17 +4711,17 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
+          <t>23.15</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>23.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1498.0</t>
+          <t>390.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>65.67</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>86.42</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>22.34</v>
+        <v>22.38</v>
       </c>
       <c r="AN11" t="n">
-        <v>23.54</v>
+        <v>23.5</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>69.08</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-124.37</t>
+          <t>-120.78</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>82501.10142857143</t>
+          <t>82395.80670470756</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>36258.0</t>
+          <t>9279.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>16891</v>
+        <v>18210.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>10195.3</t>
+          <t>10729.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>10437.66</v>
+        <v>8369.26</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>390.5343885617743</t>
+          <t>779.7799219306776</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>3886.843171294131</t>
+          <t>2920.630355459645</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>36258.0</t>
+          <t>9279.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>108.86</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1623.0</t>
+          <t>1498.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>65.67</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>61.41</t>
+          <t>86.42</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>22.29</v>
+        <v>22.34</v>
       </c>
       <c r="AN12" t="n">
-        <v>23.62</v>
+        <v>23.54</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>46.64</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-127.21</t>
+          <t>-124.37</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>82501.10142857143</t>
+          <t>82395.80670470756</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>38343.0</t>
+          <t>36258.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>10310.4</v>
+        <v>16891</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7058.7</t>
+          <t>10195.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>13160.96</v>
+        <v>10437.66</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-245.1581173895633</t>
+          <t>390.5343885617743</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>2237.724223511461</t>
+          <t>3886.843171294131</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>38343.0</t>
+          <t>36258.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>108.86</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1677.95</t>
+          <t>1979.388</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,79 +5628,79 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-3.64</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>9.89</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>24.8</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-3.59</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>13.97</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>24.8</t>
-        </is>
-      </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>27.45</t>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>6.92</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,68 +5749,68 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>60.48</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-6.15</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>24.41</v>
+        <v>24.48</v>
       </c>
       <c r="AN13" t="n">
-        <v>26.01</v>
+        <v>25.98</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>24.59</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>25.69</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-113.26</t>
+          <t>-112.46</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>212460173.9078571</t>
+          <t>212264527.542796</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>41260499.0</t>
+          <t>50208048.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>46810769.2</v>
+        <v>47031077</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>41071209.8</t>
+          <t>42799022.1</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>184113554.72</v>
+        <v>181073786.02</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>5739559</t>
+          <t>4232054</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-10987117.74337839</t>
+          <t>-10049480.33360537</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-5833890.193313524</t>
+          <t>-4892474.579853766</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>41260499.0</t>
+          <t>50208048.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>27.50</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>138.62</t>
+          <t>139.52</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>9390</t>
+          <t>9655</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6033,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2804.104</t>
+          <t>1677.95</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13.38</t>
+          <t>13.97</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,63 +6179,63 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>62.79</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>60.48</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-6.14</t>
+          <t>-6.15</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>23.73</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>24.42</v>
+        <v>24.41</v>
       </c>
       <c r="AN14" t="n">
         <v>26.01</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>24.59</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-18.96</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-113.29</t>
+          <t>-113.26</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>212460173.9078571</t>
+          <t>212264527.542796</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>69398365.0</t>
+          <t>41260499.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>46175655.8</v>
+        <v>46810769.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>40727993.5</t>
+          <t>41071209.8</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>194676121.56</v>
+        <v>184113554.72</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>5447662</t>
+          <t>5739559</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-11924068.20702655</t>
+          <t>-10987117.74337839</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-6011750.455637693</t>
+          <t>-5833890.193313524</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>69398365.0</t>
+          <t>41260499.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>138.62</t>
+          <t>139.52</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>9390</t>
+          <t>9655</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1738.819</t>
+          <t>2804.104</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>13.38</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,68 +6609,68 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>62.79</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>28.81</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-6.14</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>24.49</v>
+        <v>24.42</v>
       </c>
       <c r="AN15" t="n">
-        <v>25.98</v>
+        <v>26.01</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-37.74</t>
+          <t>-18.96</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-112.66</t>
+          <t>-113.29</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>212460173.9078571</t>
+          <t>212264527.542796</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>40606624.0</t>
+          <t>69398365.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>40014316.2</v>
+        <v>46175655.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>41687883.7</t>
+          <t>40727993.5</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>195169236.84</v>
+        <v>194676121.56</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-1673567</t>
+          <t>5447662</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-12999035.07091543</t>
+          <t>-11924068.20702655</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-9065902.528399438</t>
+          <t>-6011750.455637693</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>40606624.0</t>
+          <t>69398365.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,17 +6791,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>138.62</t>
+          <t>139.52</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>9390</t>
+          <t>9655</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1462.411</t>
+          <t>1738.819</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-23.72</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,58 +7039,58 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>24.64</v>
+        <v>24.49</v>
       </c>
       <c r="AN16" t="n">
-        <v>25.97</v>
+        <v>25.98</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-50.35</t>
+          <t>-37.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-111.47</t>
+          <t>-112.66</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>212460173.9078571</t>
+          <t>212264527.542796</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>33681849.0</t>
+          <t>40606624.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>39637812.8</v>
+        <v>40014316.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>51965661.4</t>
+          <t>41687883.7</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>195984000.1</v>
+        <v>195169236.84</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-12327848</t>
+          <t>-1673567</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-13714150.07864561</t>
+          <t>-12999035.07091543</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-10020365.29204483</t>
+          <t>-9065902.528399438</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>33681849.0</t>
+          <t>40606624.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>14.50</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>138.62</t>
+          <t>139.52</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>9390</t>
+          <t>9655</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
+          <t>23.05</t>
+        </is>
+      </c>
+      <c r="CG16" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>22.8</t>
-        </is>
-      </c>
-      <c r="CG16" t="inlineStr">
-        <is>
-          <t>22.9</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2112.165</t>
+          <t>1462.411</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-26.70</t>
+          <t>-23.72</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7484,53 +7484,53 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>24.85</v>
+        <v>24.64</v>
       </c>
       <c r="AN17" t="n">
-        <v>25.98</v>
+        <v>25.97</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-48.21</t>
+          <t>-50.35</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-110.02</t>
+          <t>-111.47</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>212460173.9078571</t>
+          <t>212264527.542796</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>49106509.0</t>
+          <t>33681849.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>38566967.2</v>
+        <v>39637812.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>52615128.9</t>
+          <t>51965661.4</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>195992723.02</v>
+        <v>195984000.1</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-14048161</t>
+          <t>-12327848</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-14385747.31257303</t>
+          <t>-13714150.07864561</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-10284073.15825091</t>
+          <t>-10020365.29204483</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>49106509.0</t>
+          <t>33681849.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>15.75</t>
+          <t>14.50</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>138.62</t>
+          <t>139.52</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>9390</t>
+          <t>9655</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1579.409</t>
+          <t>2112.165</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>9.22</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-32.96</t>
+          <t>-26.70</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,12 +7899,12 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>36.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -7914,53 +7914,53 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>6.62</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>23.88</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>25.06</v>
+        <v>24.85</v>
       </c>
       <c r="AN18" t="n">
         <v>25.98</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>24.37</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-39.74</t>
+          <t>-48.21</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-108.82</t>
+          <t>-110.02</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>212460173.9078571</t>
+          <t>212264527.542796</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>38084932.0</t>
+          <t>49106509.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>35331650.4</v>
+        <v>38566967.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>52705529.4</t>
+          <t>52615128.9</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>195762947.24</v>
+        <v>195992723.02</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-17373879</t>
+          <t>-14048161</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-15131506.2497225</t>
+          <t>-14385747.31257303</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-11946152.49717921</t>
+          <t>-10284073.15825091</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>38084932.0</t>
+          <t>49106509.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>21.50</t>
+          <t>15.75</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>138.62</t>
+          <t>139.52</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>9390</t>
+          <t>9655</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8151,17 +8151,17 @@
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1646.332</t>
+          <t>1579.409</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-31.86</t>
+          <t>-32.96</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,58 +8329,58 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.07</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>13.77</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>6.62</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>25.22</v>
+        <v>25.06</v>
       </c>
       <c r="AN19" t="n">
-        <v>25.95</v>
+        <v>25.98</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>24.37</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-54.01</t>
+          <t>-39.74</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-107.94</t>
+          <t>-108.82</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>212460173.9078571</t>
+          <t>212264527.542796</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>38591667.0</t>
+          <t>38084932.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>35280331.2</v>
+        <v>35331650.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>51774555.3</t>
+          <t>52705529.4</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>196053683.56</v>
+        <v>195762947.24</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-16494224</t>
+          <t>-17373879</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-15710661.47745765</t>
+          <t>-15131506.2497225</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-12713019.99932038</t>
+          <t>-11946152.49717921</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>38591667.0</t>
+          <t>38084932.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>21.50</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,17 +8511,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>138.62</t>
+          <t>139.52</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>9390</t>
+          <t>9655</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1604.993</t>
+          <t>1646.332</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,72 +8638,72 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>9.02</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-3.64</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-31.86</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
           <t>23.85</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>3.83</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-3.59</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>-18.78</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2025-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8769,58 +8769,58 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>13.77</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>25.44</v>
+        <v>25.22</v>
       </c>
       <c r="AN20" t="n">
-        <v>25.96</v>
+        <v>25.95</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-27.44</t>
+          <t>-54.01</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-106.87</t>
+          <t>-107.94</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,48 +8840,48 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>212460173.9078571</t>
+          <t>212264527.542796</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>38724107.0</t>
+          <t>38591667.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>43361451.2</v>
+        <v>35280331.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>53384515.1</t>
+          <t>51774555.3</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>197488634.64</v>
+        <v>196053683.56</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-10023063</t>
+          <t>-16494224</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-16255687.20075533</t>
+          <t>-15710661.47745765</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-13408801.60954632</t>
+          <t>-12713019.99932038</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>38724107.0</t>
+          <t>38591667.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>138.62</t>
+          <t>139.52</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>9390</t>
+          <t>9655</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9043,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1126.956</t>
+          <t>1604.993</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,74 +9068,74 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>6.47</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-3.64</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-18.78</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>24.9</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-3.59</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>21.00</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>24.9</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
       <c r="T21" t="inlineStr">
         <is>
           <t>24.8</t>
@@ -9148,14 +9148,14 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
+          <t>-4.22</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>4.40</t>
-        </is>
-      </c>
       <c r="X21" t="inlineStr">
         <is>
           <t>-9.29</t>
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,68 +9189,68 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>25.56</v>
+        <v>25.44</v>
       </c>
       <c r="AN21" t="n">
-        <v>25.94</v>
+        <v>25.96</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>-27.44</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-106.40</t>
+          <t>-106.87</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>212460173.9078571</t>
+          <t>212264527.542796</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>28327621.0</t>
+          <t>38724107.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>64293510</v>
+        <v>43361451.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>53134957.6</t>
+          <t>53384515.1</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>197699079.6</v>
+        <v>197488634.64</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>11158552</t>
+          <t>-10023063</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-16773302.76279333</t>
+          <t>-16255687.20075533</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-13938079.56667101</t>
+          <t>-13408801.60954632</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>28327621.0</t>
+          <t>38724107.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>24.50</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>138.62</t>
+          <t>139.52</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>9390</t>
+          <t>9655</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1301.232</t>
+          <t>1126.956</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,22 +9508,22 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,63 +9619,63 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>71.74</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>25.58</v>
+        <v>25.56</v>
       </c>
       <c r="AN22" t="n">
-        <v>25.88</v>
+        <v>25.94</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>24.19</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>13.70</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-106.48</t>
+          <t>-106.40</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,48 +9700,48 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>212460173.9078571</t>
+          <t>212264527.542796</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>32929925.0</t>
+          <t>28327621.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>66663290.6</v>
+        <v>64293510</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>54706545.9</t>
+          <t>53134957.6</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>197755621.26</v>
+        <v>197699079.6</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>11956744</t>
+          <t>11158552</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-17288797.88936103</t>
+          <t>-16773302.76279333</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-13082493.16375375</t>
+          <t>-13938079.56667101</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>32929925.0</t>
+          <t>28327621.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.50</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>138.62</t>
+          <t>139.52</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>9390</t>
+          <t>9655</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1463.862</t>
+          <t>1301.232</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>21.86</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,68 +10049,68 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>73.91</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>71.74</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>25.62</v>
+        <v>25.58</v>
       </c>
       <c r="AN23" t="n">
-        <v>25.82</v>
+        <v>25.88</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>24.14</t>
+          <t>24.19</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>13.70</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-106.70</t>
+          <t>-106.48</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>212460173.9078571</t>
+          <t>212264527.542796</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>37828336.0</t>
+          <t>32929925.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>70079408.40000001</v>
+        <v>66663290.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>58159640.7</t>
+          <t>54706545.9</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>197616845.6</v>
+        <v>197755621.26</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>11919767</t>
+          <t>11956744</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-18053580.56674417</t>
+          <t>-17288797.88936103</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-11886098.97516645</t>
+          <t>-13082493.16375375</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>37828336.0</t>
+          <t>32929925.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>138.62</t>
+          <t>139.52</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>9390</t>
+          <t>9655</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>25.25</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/ITO導電基板.xlsx
+++ b/Result/checksun_type/ITO導電基板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-7.74</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>77.42</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>88.17</t>
+          <t>68.82</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>22.74</v>
+        <v>22.8</v>
       </c>
       <c r="AN2" t="n">
-        <v>23.26</v>
+        <v>23.25</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.67</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>362.90</t>
+          <t>154.33</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-97.51</t>
+          <t>-95.95</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>82395.80670470756</t>
+          <t>82288.22863247864</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>5793.0</t>
+          <t>4584.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>9462.4</v>
+        <v>9280.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>8873.4</t>
+          <t>8403.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>7472.64</v>
+        <v>7418.64</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>876</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>563.475781961225</t>
+          <t>425.2400559355071</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>68.1072250545676</t>
+          <t>-335.0564372059416</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>5793.0</t>
+          <t>4584.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>105.68</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>361.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,79 +1328,79 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-2.37</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6.64</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>23.95</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-0.63</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-18.48</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>23.0</t>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>77.42</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>82.37</t>
+          <t>88.17</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>22.66</v>
+        <v>22.74</v>
       </c>
       <c r="AN3" t="n">
         <v>23.26</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>4280.47</t>
+          <t>362.90</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-99.77</t>
+          <t>-97.51</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>82395.80670470756</t>
+          <t>82288.22863247864</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>9716.799999999999</v>
+        <v>9462.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>11919.9</t>
+          <t>8873.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>7436.54</v>
+        <v>7472.64</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2203</t>
+          <t>589</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>653.54279230789</t>
+          <t>563.475781961225</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>512.0871988176314</t>
+          <t>68.1072250545676</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>105.68</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>24.05</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>24.45</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>361.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>-3.01</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>-1.47</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-35.31</t>
+          <t>-18.48</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>72.03</t>
+          <t>82.37</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>22.57</v>
+        <v>22.66</v>
       </c>
       <c r="AN4" t="n">
         <v>23.26</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>430.70</t>
+          <t>4280.47</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-99.77</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>82395.80670470756</t>
+          <t>82288.22863247864</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>9629.200000000001</v>
+        <v>9716.799999999999</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>14884.2</t>
+          <t>11919.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>7449.74</v>
+        <v>7436.54</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-5255</t>
+          <t>-2203</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>679.2619911243006</t>
+          <t>653.54279230789</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>816.5911899499497</t>
+          <t>512.0871988176314</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>105.68</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-51.37</t>
+          <t>-35.31</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>22.5</v>
+        <v>22.57</v>
       </c>
       <c r="AN5" t="n">
         <v>23.26</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.61</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>160.83</t>
+          <t>430.70</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.65</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>82395.80670470756</t>
+          <t>82288.22863247864</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>6324</v>
+        <v>9629.200000000001</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>13005.4</t>
+          <t>14884.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>7283.74</v>
+        <v>7449.74</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-6681</t>
+          <t>-5255</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>654.2930458832735</t>
+          <t>679.2619911243006</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-343.1385080735217</t>
+          <t>816.5911899499497</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>105.68</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-41.51</t>
+          <t>-51.37</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>64.93</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>22.46</v>
+        <v>22.5</v>
       </c>
       <c r="AN6" t="n">
-        <v>23.28</v>
+        <v>23.26</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>23.61</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>115.43</t>
+          <t>160.83</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.52</t>
+          <t>-104.65</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>82395.80670470756</t>
+          <t>82288.22863247864</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>7527.4</v>
+        <v>6324</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>12868.8</t>
+          <t>13005.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>7378.32</v>
+        <v>7283.74</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-5341</t>
+          <t>-6681</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>835.6442375117817</t>
+          <t>654.2930458832735</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>80.10972718128687</t>
+          <t>-343.1385080735217</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-10.70</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>105.68</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-34.19</t>
+          <t>-41.51</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-10.32</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>64.93</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>22.45</v>
+        <v>22.46</v>
       </c>
       <c r="AN7" t="n">
-        <v>23.33</v>
+        <v>23.28</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>108.28</t>
+          <t>115.43</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-108.40</t>
+          <t>-106.52</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>82395.80670470756</t>
+          <t>82288.22863247864</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>8284.4</v>
+        <v>7527.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>12587.7</t>
+          <t>12868.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>7563.22</v>
+        <v>7378.32</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-4303</t>
+          <t>-5341</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>973.0141484809627</t>
+          <t>835.6442375117817</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>523.2104301459694</t>
+          <t>80.10972718128687</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-12.06</t>
+          <t>-10.70</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>105.68</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>-34.19</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-10.32</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>81.76</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>22.46</v>
+        <v>22.45</v>
       </c>
       <c r="AN8" t="n">
-        <v>23.38</v>
+        <v>23.33</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>119.34</t>
+          <t>108.28</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-108.40</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>82395.80670470756</t>
+          <t>82288.22863247864</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>14123</v>
+        <v>8284.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>12216.7</t>
+          <t>12587.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>7629.54</v>
+        <v>7563.22</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>-4303</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>1054.796642723689</t>
+          <t>973.0141484809627</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>969.2039190188734</t>
+          <t>523.2104301459694</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-12.06</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>105.68</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>293.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,84 +3908,84 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-1.29</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>15.60</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>3.36</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>73.69</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>0</t>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,274 +4024,274 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>81.76</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
+          <t>23.49</t>
+        </is>
+      </c>
+      <c r="AM9" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>23.57</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>119.34</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-110.67</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>82288.22863247864</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="n">
+        <v>14123</v>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>12216.7</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>7629.54</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>1054.796642723689</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>969.2039190188734</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>-8.37</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-13.42998910113004</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-25.43417574544826</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>-6.333574654154932</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>105.68</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>19.70%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>1592</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>安可-光電業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>光電業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>23.45</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>24.05</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="AM9" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>23.42</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>92.50</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-113.86</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>82395.80670470756</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="n">
-        <v>20139.2</v>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>11594.6</t>
-        </is>
-      </c>
-      <c r="AZ9" t="n">
-        <v>7648.36</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>8544</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>1070.358956124564</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>1443.473048872349</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>-10.51</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>-13.42998910113004</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>-25.43417574544826</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>-6.333574654154932</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>108.18</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>19.70%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>-0.85%</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>89.32</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>1630</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>安可-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>光電業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>23.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>426.0</t>
+          <t>293.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>75.73</t>
+          <t>73.69</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>91.82</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>22.42</v>
+        <v>22.43</v>
       </c>
       <c r="AN10" t="n">
-        <v>23.46</v>
+        <v>23.42</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>87.14</t>
+          <t>92.50</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-113.86</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>82395.80670470756</t>
+          <t>82288.22863247864</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>19686.8</v>
+        <v>20139.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>11202.7</t>
+          <t>11594.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>8102.12</v>
+        <v>7648.36</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1002.520030170422</t>
+          <t>1070.358956124564</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>2227.590625489014</t>
+          <t>1443.473048872349</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>105.68</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>390.0</t>
+          <t>426.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>75.73</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>91.82</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>22.38</v>
+        <v>22.42</v>
       </c>
       <c r="AN11" t="n">
-        <v>23.5</v>
+        <v>23.46</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>69.08</t>
+          <t>87.14</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-120.78</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>82395.80670470756</t>
+          <t>82288.22863247864</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>18210.2</v>
+        <v>19686.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>10729.5</t>
+          <t>11202.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>8369.26</v>
+        <v>8102.12</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>779.7799219306776</t>
+          <t>1002.520030170422</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>2920.630355459645</t>
+          <t>2227.590625489014</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>105.68</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
+          <t>23.15</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>23.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1498.0</t>
+          <t>390.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>65.67</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>86.42</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>22.34</v>
+        <v>22.38</v>
       </c>
       <c r="AN12" t="n">
-        <v>23.54</v>
+        <v>23.5</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>69.08</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-124.37</t>
+          <t>-120.78</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>82395.80670470756</t>
+          <t>82288.22863247864</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>36258.0</t>
+          <t>9279.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>16891</v>
+        <v>18210.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>10195.3</t>
+          <t>10729.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>10437.66</v>
+        <v>8369.26</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>390.5343885617743</t>
+          <t>779.7799219306776</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>3886.843171294131</t>
+          <t>2920.630355459645</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>36258.0</t>
+          <t>9279.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>105.68</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1979.388</t>
+          <t>1109.996</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.23</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>85.93</t>
+          <t>96.41</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.78</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.69</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>24.48</v>
+        <v>24.5</v>
       </c>
       <c r="AN13" t="n">
-        <v>25.98</v>
+        <v>25.92</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>25.69</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-112.46</t>
+          <t>-111.26</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>212264527.542796</t>
+          <t>212022541.2264957</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>50208048.0</t>
+          <t>28260089.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>47031077</v>
+        <v>45946725</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>42799022.1</t>
+          <t>42792268.9</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>181073786.02</v>
+        <v>160844320.62</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>4232054</t>
+          <t>3154456</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-10049480.33360537</t>
+          <t>-9389140.083963865</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-4892474.579853766</t>
+          <t>-5757268.710935593</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>50208048.0</t>
+          <t>28260089.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>27.50</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>139.52</t>
+          <t>138.52</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>9655</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1677.95</t>
+          <t>1979.388</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,79 +6058,79 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-0.59</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-1.31</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>9.89</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
           <t>24.8</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-3.64</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>13.97</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>24.8</t>
-        </is>
-      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>27.45</t>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>6.92</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>60.48</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-6.15</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>24.41</v>
+        <v>24.48</v>
       </c>
       <c r="AN14" t="n">
-        <v>26.01</v>
+        <v>25.98</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>24.59</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>25.69</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-113.26</t>
+          <t>-112.46</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>212264527.542796</t>
+          <t>212022541.2264957</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>41260499.0</t>
+          <t>50208048.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>46810769.2</v>
+        <v>47031077</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>41071209.8</t>
+          <t>42799022.1</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>184113554.72</v>
+        <v>181073786.02</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>5739559</t>
+          <t>4232054</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-10987117.74337839</t>
+          <t>-10049480.33360537</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-5833890.193313524</t>
+          <t>-4892474.579853766</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>41260499.0</t>
+          <t>50208048.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>27.50</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,17 +6361,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>139.52</t>
+          <t>138.52</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>9655</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6463,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2804.104</t>
+          <t>1677.95</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>13.38</t>
+          <t>13.97</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,68 +6604,68 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>62.79</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>60.48</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-6.14</t>
+          <t>-6.15</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>23.73</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>24.42</v>
+        <v>24.41</v>
       </c>
       <c r="AN15" t="n">
         <v>26.01</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>24.59</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-18.96</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-113.29</t>
+          <t>-113.26</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>212264527.542796</t>
+          <t>212022541.2264957</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>69398365.0</t>
+          <t>41260499.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>46175655.8</v>
+        <v>46810769.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>40727993.5</t>
+          <t>41071209.8</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>194676121.56</v>
+        <v>184113554.72</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>5447662</t>
+          <t>5739559</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-11924068.20702655</t>
+          <t>-10987117.74337839</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-6011750.455637693</t>
+          <t>-5833890.193313524</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>69398365.0</t>
+          <t>41260499.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>139.52</t>
+          <t>138.52</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>9655</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1738.819</t>
+          <t>2804.104</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>13.38</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>62.79</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>28.81</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-6.14</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>24.49</v>
+        <v>24.42</v>
       </c>
       <c r="AN16" t="n">
-        <v>25.98</v>
+        <v>26.01</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-37.74</t>
+          <t>-18.96</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-112.66</t>
+          <t>-113.29</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>212264527.542796</t>
+          <t>212022541.2264957</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>40606624.0</t>
+          <t>69398365.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>40014316.2</v>
+        <v>46175655.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>41687883.7</t>
+          <t>40727993.5</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>195169236.84</v>
+        <v>194676121.56</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-1673567</t>
+          <t>5447662</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-12999035.07091543</t>
+          <t>-11924068.20702655</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-9065902.528399438</t>
+          <t>-6011750.455637693</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>40606624.0</t>
+          <t>69398365.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,17 +7221,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>139.52</t>
+          <t>138.52</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>9655</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1462.411</t>
+          <t>1738.819</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-23.72</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,63 +7464,63 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>24.64</v>
+        <v>24.49</v>
       </c>
       <c r="AN17" t="n">
-        <v>25.97</v>
+        <v>25.98</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-50.35</t>
+          <t>-37.74</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-111.47</t>
+          <t>-112.66</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>212264527.542796</t>
+          <t>212022541.2264957</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>33681849.0</t>
+          <t>40606624.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>39637812.8</v>
+        <v>40014316.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>51965661.4</t>
+          <t>41687883.7</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>195984000.1</v>
+        <v>195169236.84</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-12327848</t>
+          <t>-1673567</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-13714150.07864561</t>
+          <t>-12999035.07091543</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-10020365.29204483</t>
+          <t>-9065902.528399438</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>33681849.0</t>
+          <t>40606624.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>14.50</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>139.52</t>
+          <t>138.52</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>9655</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
+          <t>23.05</t>
+        </is>
+      </c>
+      <c r="CG17" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>22.8</t>
-        </is>
-      </c>
-      <c r="CG17" t="inlineStr">
-        <is>
-          <t>22.9</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2112.165</t>
+          <t>1462.411</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-26.70</t>
+          <t>-23.72</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,12 +7894,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7914,53 +7914,53 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>24.85</v>
+        <v>24.64</v>
       </c>
       <c r="AN18" t="n">
-        <v>25.98</v>
+        <v>25.97</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-48.21</t>
+          <t>-50.35</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-110.02</t>
+          <t>-111.47</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>212264527.542796</t>
+          <t>212022541.2264957</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>49106509.0</t>
+          <t>33681849.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>38566967.2</v>
+        <v>39637812.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>52615128.9</t>
+          <t>51965661.4</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>195992723.02</v>
+        <v>195984000.1</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-14048161</t>
+          <t>-12327848</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-14385747.31257303</t>
+          <t>-13714150.07864561</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-10284073.15825091</t>
+          <t>-10020365.29204483</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>49106509.0</t>
+          <t>33681849.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>15.75</t>
+          <t>14.50</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>139.52</t>
+          <t>138.52</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>9655</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1579.409</t>
+          <t>2112.165</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-32.96</t>
+          <t>-26.70</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,17 +8324,17 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>36.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>6.62</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>23.88</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>25.06</v>
+        <v>24.85</v>
       </c>
       <c r="AN19" t="n">
         <v>25.98</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>24.37</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-39.74</t>
+          <t>-48.21</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-108.82</t>
+          <t>-110.02</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>212264527.542796</t>
+          <t>212022541.2264957</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>38084932.0</t>
+          <t>49106509.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>35331650.4</v>
+        <v>38566967.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>52705529.4</t>
+          <t>52615128.9</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>195762947.24</v>
+        <v>195992723.02</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-17373879</t>
+          <t>-14048161</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-15131506.2497225</t>
+          <t>-14385747.31257303</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-11946152.49717921</t>
+          <t>-10284073.15825091</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>38084932.0</t>
+          <t>49106509.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>21.50</t>
+          <t>15.75</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,17 +8511,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>139.52</t>
+          <t>138.52</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>9655</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8581,17 +8581,17 @@
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1646.332</t>
+          <t>1579.409</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-31.86</t>
+          <t>-32.96</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,63 +8754,63 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.07</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>13.77</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>6.62</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>25.22</v>
+        <v>25.06</v>
       </c>
       <c r="AN20" t="n">
-        <v>25.95</v>
+        <v>25.98</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>24.37</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-54.01</t>
+          <t>-39.74</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-107.94</t>
+          <t>-108.82</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>212264527.542796</t>
+          <t>212022541.2264957</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>38591667.0</t>
+          <t>38084932.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>35280331.2</v>
+        <v>35331650.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>51774555.3</t>
+          <t>52705529.4</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>196053683.56</v>
+        <v>195762947.24</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-16494224</t>
+          <t>-17373879</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-15710661.47745765</t>
+          <t>-15131506.2497225</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-12713019.99932038</t>
+          <t>-11946152.49717921</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>38591667.0</t>
+          <t>38084932.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>21.50</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>139.52</t>
+          <t>138.52</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>9655</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1604.993</t>
+          <t>1646.332</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,72 +9068,72 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>8.48</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-1.31</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-31.86</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
           <t>23.85</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>6.47</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-3.64</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>-18.78</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -9148,12 +9148,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9199,58 +9199,58 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>13.77</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>25.44</v>
+        <v>25.22</v>
       </c>
       <c r="AN21" t="n">
-        <v>25.96</v>
+        <v>25.95</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-27.44</t>
+          <t>-54.01</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-106.87</t>
+          <t>-107.94</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,48 +9270,48 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>212264527.542796</t>
+          <t>212022541.2264957</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>38724107.0</t>
+          <t>38591667.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>43361451.2</v>
+        <v>35280331.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>53384515.1</t>
+          <t>51774555.3</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>197488634.64</v>
+        <v>196053683.56</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-10023063</t>
+          <t>-16494224</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-16255687.20075533</t>
+          <t>-15710661.47745765</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-13408801.60954632</t>
+          <t>-12713019.99932038</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>38724107.0</t>
+          <t>38591667.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>139.52</t>
+          <t>138.52</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>9655</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9473,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1126.956</t>
+          <t>1604.993</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,74 +9498,74 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>5.92</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-1.31</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-18.78</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
           <t>24.9</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>-3.64</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>21.00</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>24.9</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
       <c r="T22" t="inlineStr">
         <is>
           <t>24.8</t>
@@ -9578,14 +9578,14 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
+          <t>-4.22</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>4.40</t>
-        </is>
-      </c>
       <c r="X22" t="inlineStr">
         <is>
           <t>-9.29</t>
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>25.56</v>
+        <v>25.44</v>
       </c>
       <c r="AN22" t="n">
-        <v>25.94</v>
+        <v>25.96</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>-27.44</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-106.40</t>
+          <t>-106.87</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>212264527.542796</t>
+          <t>212022541.2264957</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>28327621.0</t>
+          <t>38724107.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>64293510</v>
+        <v>43361451.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>53134957.6</t>
+          <t>53384515.1</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>197699079.6</v>
+        <v>197488634.64</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>11158552</t>
+          <t>-10023063</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-16773302.76279333</t>
+          <t>-16255687.20075533</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-13938079.56667101</t>
+          <t>-13408801.60954632</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>28327621.0</t>
+          <t>38724107.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>24.50</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>139.52</t>
+          <t>138.52</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>9655</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1301.232</t>
+          <t>1126.956</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,22 +9938,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>21.00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,68 +10044,68 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>71.74</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>25.59</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>25.58</v>
+        <v>25.56</v>
       </c>
       <c r="AN23" t="n">
-        <v>25.88</v>
+        <v>25.94</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>24.19</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>13.70</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-106.48</t>
+          <t>-106.40</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,48 +10130,48 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>212264527.542796</t>
+          <t>212022541.2264957</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>32929925.0</t>
+          <t>28327621.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>66663290.6</v>
+        <v>64293510</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>54706545.9</t>
+          <t>53134957.6</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>197755621.26</v>
+        <v>197699079.6</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>11956744</t>
+          <t>11158552</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-17288797.88936103</t>
+          <t>-16773302.76279333</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-13082493.16375375</t>
+          <t>-13938079.56667101</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>32929925.0</t>
+          <t>28327621.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>24.50</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>139.52</t>
+          <t>138.52</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>9655</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>25.25</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/ITO導電基板.xlsx
+++ b/Result/checksun_type/ITO導電基板.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,54 +1014,54 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>248</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>38.71</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>68.82</t>
+          <t>52.69</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
+          <t>-1.99</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>-1.46</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>-1.90</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>3.92</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>-1.9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>-1.79</t>
-        </is>
-      </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.67</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>22.8</v>
+        <v>22.88</v>
       </c>
       <c r="AN2" t="n">
-        <v>23.25</v>
+        <v>23.22</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>154.33</t>
+          <t>78.99</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-95.95</t>
+          <t>-94.95</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>82288.22863247864</t>
+          <t>82183.42105263157</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>4584.0</t>
+          <t>5739.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>9280.4</v>
+        <v>9625.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>8403.9</t>
+          <t>7974.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>7418.64</v>
+        <v>7390.28</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>425.2400559355071</t>
+          <t>279.4693411980216</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-335.0564372059416</t>
+          <t>-522.2695898581487</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>4584.0</t>
+          <t>5739.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>105.68</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>23.2</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>23.25</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,102 +1338,102 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.48</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>10.43</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-7.74</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>10.87</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>-2.37</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-1.47</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>6.64</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-5.56</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>10.87</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>-0.84</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>248</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>77.42</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>88.17</t>
+          <t>68.82</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>22.74</v>
+        <v>22.8</v>
       </c>
       <c r="AN3" t="n">
-        <v>23.26</v>
+        <v>23.25</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.67</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>362.90</t>
+          <t>154.33</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-97.51</t>
+          <t>-95.95</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>82288.22863247864</t>
+          <t>82183.42105263157</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5793.0</t>
+          <t>4584.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>9462.4</v>
+        <v>9280.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>8873.4</t>
+          <t>8403.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>7472.64</v>
+        <v>7418.64</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>876</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>563.475781961225</t>
+          <t>425.2400559355071</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>68.1072250545676</t>
+          <t>-335.0564372059416</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>5793.0</t>
+          <t>4584.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>105.68</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>361.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,79 +1758,79 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-2.59</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-1.48</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>6.64</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>23.95</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-3.01</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-1.47</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-18.48</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>23.0</t>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>248</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>77.42</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>82.37</t>
+          <t>88.17</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>22.66</v>
+        <v>22.74</v>
       </c>
       <c r="AN4" t="n">
         <v>23.26</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>4280.47</t>
+          <t>362.90</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-99.77</t>
+          <t>-97.51</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>82288.22863247864</t>
+          <t>82183.42105263157</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>9716.799999999999</v>
+        <v>9462.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>11919.9</t>
+          <t>8873.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>7436.54</v>
+        <v>7472.64</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2203</t>
+          <t>589</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>653.54279230789</t>
+          <t>563.475781961225</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>512.0871988176314</t>
+          <t>68.1072250545676</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>105.68</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>24.05</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>24.45</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>361.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-35.31</t>
+          <t>-18.48</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>248</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>72.03</t>
+          <t>82.37</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>22.57</v>
+        <v>22.66</v>
       </c>
       <c r="AN5" t="n">
         <v>23.26</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>430.70</t>
+          <t>4280.47</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-99.77</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>82288.22863247864</t>
+          <t>82183.42105263157</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>9629.200000000001</v>
+        <v>9716.799999999999</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>14884.2</t>
+          <t>11919.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>7449.74</v>
+        <v>7436.54</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-5255</t>
+          <t>-2203</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>679.2619911243006</t>
+          <t>653.54279230789</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>816.5911899499497</t>
+          <t>512.0871988176314</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>105.68</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-51.37</t>
+          <t>-35.31</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>248</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>22.5</v>
+        <v>22.57</v>
       </c>
       <c r="AN6" t="n">
         <v>23.26</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.61</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>160.83</t>
+          <t>430.70</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.65</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>82288.22863247864</t>
+          <t>82183.42105263157</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>6324</v>
+        <v>9629.200000000001</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>13005.4</t>
+          <t>14884.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>7283.74</v>
+        <v>7449.74</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-6681</t>
+          <t>-5255</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>654.2930458832735</t>
+          <t>679.2619911243006</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-343.1385080735217</t>
+          <t>816.5911899499497</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>105.68</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-41.51</t>
+          <t>-51.37</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>248</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>64.93</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>22.46</v>
+        <v>22.5</v>
       </c>
       <c r="AN7" t="n">
-        <v>23.28</v>
+        <v>23.26</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>23.61</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>115.43</t>
+          <t>160.83</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-106.52</t>
+          <t>-104.65</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>82288.22863247864</t>
+          <t>82183.42105263157</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>7527.4</v>
+        <v>6324</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>12868.8</t>
+          <t>13005.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>7378.32</v>
+        <v>7283.74</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-5341</t>
+          <t>-6681</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>835.6442375117817</t>
+          <t>654.2930458832735</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>80.10972718128687</t>
+          <t>-343.1385080735217</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-10.70</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>105.68</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-34.19</t>
+          <t>-41.51</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-10.32</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>248</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>64.93</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>22.45</v>
+        <v>22.46</v>
       </c>
       <c r="AN8" t="n">
-        <v>23.33</v>
+        <v>23.28</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>108.28</t>
+          <t>115.43</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-108.40</t>
+          <t>-106.52</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>82288.22863247864</t>
+          <t>82183.42105263157</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>8284.4</v>
+        <v>7527.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>12587.7</t>
+          <t>12868.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>7563.22</v>
+        <v>7378.32</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-4303</t>
+          <t>-5341</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>973.0141484809627</t>
+          <t>835.6442375117817</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>523.2104301459694</t>
+          <t>80.10972718128687</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-12.06</t>
+          <t>-10.70</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>105.68</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>-34.19</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-10.32</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>248</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>81.76</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>22.46</v>
+        <v>22.45</v>
       </c>
       <c r="AN9" t="n">
-        <v>23.38</v>
+        <v>23.33</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>119.34</t>
+          <t>108.28</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-108.40</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>82288.22863247864</t>
+          <t>82183.42105263157</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>14123</v>
+        <v>8284.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>12216.7</t>
+          <t>12587.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>7629.54</v>
+        <v>7563.22</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>-4303</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1054.796642723689</t>
+          <t>973.0141484809627</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>969.2039190188734</t>
+          <t>523.2104301459694</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-12.06</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>105.68</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>293.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,84 +4338,84 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-1.48</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>15.60</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-1.47</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>73.69</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>0</t>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,274 +4454,274 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>248</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>81.76</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
+          <t>23.49</t>
+        </is>
+      </c>
+      <c r="AM10" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>23.57</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>119.34</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-110.67</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>82183.42105263157</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="n">
+        <v>14123</v>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>12216.7</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>7629.54</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>1054.796642723689</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>969.2039190188734</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>-8.37</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>-13.42998910113004</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-25.43417574544826</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>-6.333574654154932</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>105.45</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>19.70%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>88.59</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>1588</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>安可-光電業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>光電業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>23.45</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>24.05</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="AM10" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>23.42</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>92.50</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-113.86</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>82288.22863247864</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="n">
-        <v>20139.2</v>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>11594.6</t>
-        </is>
-      </c>
-      <c r="AZ10" t="n">
-        <v>7648.36</v>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>8544</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>1070.358956124564</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>1443.473048872349</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>-10.51</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>-13.42998910113004</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>-25.43417574544826</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>-6.333574654154932</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>105.68</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>19.70%</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>-0.85%</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>1592</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>安可-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>光電業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>23.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>426.0</t>
+          <t>293.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>75.73</t>
+          <t>73.69</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>248</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>91.82</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>22.42</v>
+        <v>22.43</v>
       </c>
       <c r="AN11" t="n">
-        <v>23.46</v>
+        <v>23.42</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>87.14</t>
+          <t>92.50</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-113.86</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>82288.22863247864</t>
+          <t>82183.42105263157</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>19686.8</v>
+        <v>20139.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>11202.7</t>
+          <t>11594.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>8102.12</v>
+        <v>7648.36</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>1002.520030170422</t>
+          <t>1070.358956124564</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>2227.590625489014</t>
+          <t>1443.473048872349</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>105.68</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>390.0</t>
+          <t>426.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>75.73</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>248</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>91.82</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>22.38</v>
+        <v>22.42</v>
       </c>
       <c r="AN12" t="n">
-        <v>23.5</v>
+        <v>23.46</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>69.08</t>
+          <t>87.14</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-120.78</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>82288.22863247864</t>
+          <t>82183.42105263157</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>18210.2</v>
+        <v>19686.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>10729.5</t>
+          <t>11202.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>8369.26</v>
+        <v>8102.12</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>779.7799219306776</t>
+          <t>1002.520030170422</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>2920.630355459645</t>
+          <t>2227.590625489014</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>105.68</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5571,17 +5571,17 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
+          <t>23.15</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>23.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1109.996</t>
+          <t>1020.161</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,68 +5749,68 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>94.23</t>
+          <t>98.08</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>96.41</t>
+          <t>97.44</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>25.07</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>24.5</v>
+        <v>24.55</v>
       </c>
       <c r="AN13" t="n">
-        <v>25.92</v>
+        <v>25.85</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>24.78</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>42.52</t>
+          <t>59.31</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-111.26</t>
+          <t>-109.81</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>212022541.2264957</t>
+          <t>211776287.8207681</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>28260089.0</t>
+          <t>25937598.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>45946725</v>
+        <v>43012919.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>42792268.9</t>
+          <t>41513618.0</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>160844320.62</v>
+        <v>145472052.94</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>3154456</t>
+          <t>1499301</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-9389140.083963865</t>
+          <t>-8928176.949495498</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-5757268.710935593</t>
+          <t>-6392879.709919482</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>28260089.0</t>
+          <t>25937598.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>138.52</t>
+          <t>139.4</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>9598</t>
+          <t>9636</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1979.388</t>
+          <t>1109.996</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,68 +6179,68 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.23</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>85.93</t>
+          <t>96.41</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.78</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.69</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>24.48</v>
+        <v>24.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>25.98</v>
+        <v>25.92</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>25.69</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-112.46</t>
+          <t>-111.26</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>212022541.2264957</t>
+          <t>211776287.8207681</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>50208048.0</t>
+          <t>28260089.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>47031077</v>
+        <v>45946725</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>42799022.1</t>
+          <t>42792268.9</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>181073786.02</v>
+        <v>160844320.62</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>4232054</t>
+          <t>3154456</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-10049480.33360537</t>
+          <t>-9389140.083963865</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-4892474.579853766</t>
+          <t>-5757268.710935593</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>50208048.0</t>
+          <t>28260089.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>27.50</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>138.52</t>
+          <t>139.4</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>9598</t>
+          <t>9636</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1677.95</t>
+          <t>1979.388</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,79 +6488,79 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-1.33</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>9.89</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
           <t>24.8</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-1.31</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>13.97</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>24.8</t>
-        </is>
-      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>27.45</t>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>6.92</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,68 +6609,68 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>60.48</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-6.15</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>24.41</v>
+        <v>24.48</v>
       </c>
       <c r="AN15" t="n">
-        <v>26.01</v>
+        <v>25.98</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>24.59</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>25.69</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-113.26</t>
+          <t>-112.46</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>212022541.2264957</t>
+          <t>211776287.8207681</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>41260499.0</t>
+          <t>50208048.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>46810769.2</v>
+        <v>47031077</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>41071209.8</t>
+          <t>42799022.1</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>184113554.72</v>
+        <v>181073786.02</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>5739559</t>
+          <t>4232054</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-10987117.74337839</t>
+          <t>-10049480.33360537</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-5833890.193313524</t>
+          <t>-4892474.579853766</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>41260499.0</t>
+          <t>50208048.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>27.50</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,17 +6791,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>138.52</t>
+          <t>139.4</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>9598</t>
+          <t>9636</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6893,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2804.104</t>
+          <t>1677.95</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>13.38</t>
+          <t>13.97</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,63 +7039,63 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>62.79</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>60.48</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-6.14</t>
+          <t>-6.15</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>23.73</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>24.42</v>
+        <v>24.41</v>
       </c>
       <c r="AN16" t="n">
         <v>26.01</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>24.59</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-18.96</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-113.29</t>
+          <t>-113.26</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>212022541.2264957</t>
+          <t>211776287.8207681</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>69398365.0</t>
+          <t>41260499.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>46175655.8</v>
+        <v>46810769.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>40727993.5</t>
+          <t>41071209.8</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>194676121.56</v>
+        <v>184113554.72</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>5447662</t>
+          <t>5739559</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-11924068.20702655</t>
+          <t>-10987117.74337839</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-6011750.455637693</t>
+          <t>-5833890.193313524</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>69398365.0</t>
+          <t>41260499.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>138.52</t>
+          <t>139.4</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>9598</t>
+          <t>9636</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1738.819</t>
+          <t>2804.104</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>13.38</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,68 +7469,68 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>62.79</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>28.81</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-6.14</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>24.49</v>
+        <v>24.42</v>
       </c>
       <c r="AN17" t="n">
-        <v>25.98</v>
+        <v>26.01</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-37.74</t>
+          <t>-18.96</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-112.66</t>
+          <t>-113.29</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>212022541.2264957</t>
+          <t>211776287.8207681</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>40606624.0</t>
+          <t>69398365.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>40014316.2</v>
+        <v>46175655.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>41687883.7</t>
+          <t>40727993.5</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>195169236.84</v>
+        <v>194676121.56</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-1673567</t>
+          <t>5447662</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-12999035.07091543</t>
+          <t>-11924068.20702655</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-9065902.528399438</t>
+          <t>-6011750.455637693</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>40606624.0</t>
+          <t>69398365.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>138.52</t>
+          <t>139.4</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>9598</t>
+          <t>9636</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1462.411</t>
+          <t>1738.819</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-23.72</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,58 +7899,58 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>24.64</v>
+        <v>24.49</v>
       </c>
       <c r="AN18" t="n">
-        <v>25.97</v>
+        <v>25.98</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-50.35</t>
+          <t>-37.74</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-111.47</t>
+          <t>-112.66</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>212022541.2264957</t>
+          <t>211776287.8207681</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>33681849.0</t>
+          <t>40606624.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>39637812.8</v>
+        <v>40014316.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>51965661.4</t>
+          <t>41687883.7</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>195984000.1</v>
+        <v>195169236.84</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-12327848</t>
+          <t>-1673567</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-13714150.07864561</t>
+          <t>-12999035.07091543</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-10020365.29204483</t>
+          <t>-9065902.528399438</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>33681849.0</t>
+          <t>40606624.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>14.50</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>138.52</t>
+          <t>139.4</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>9598</t>
+          <t>9636</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
+          <t>23.05</t>
+        </is>
+      </c>
+      <c r="CG18" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>22.8</t>
-        </is>
-      </c>
-      <c r="CG18" t="inlineStr">
-        <is>
-          <t>22.9</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2112.165</t>
+          <t>1462.411</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>10.02</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-26.70</t>
+          <t>-23.72</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>24.85</v>
+        <v>24.64</v>
       </c>
       <c r="AN19" t="n">
-        <v>25.98</v>
+        <v>25.97</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-48.21</t>
+          <t>-50.35</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-110.02</t>
+          <t>-111.47</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>212022541.2264957</t>
+          <t>211776287.8207681</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>49106509.0</t>
+          <t>33681849.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>38566967.2</v>
+        <v>39637812.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>52615128.9</t>
+          <t>51965661.4</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>195992723.02</v>
+        <v>195984000.1</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-14048161</t>
+          <t>-12327848</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-14385747.31257303</t>
+          <t>-13714150.07864561</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-10284073.15825091</t>
+          <t>-10020365.29204483</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>49106509.0</t>
+          <t>33681849.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>15.75</t>
+          <t>14.50</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>138.52</t>
+          <t>139.4</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>9598</t>
+          <t>9636</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1579.409</t>
+          <t>2112.165</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-32.96</t>
+          <t>-26.70</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>36.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>6.62</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>23.88</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>25.06</v>
+        <v>24.85</v>
       </c>
       <c r="AN20" t="n">
         <v>25.98</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>24.37</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-39.74</t>
+          <t>-48.21</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-108.82</t>
+          <t>-110.02</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>212022541.2264957</t>
+          <t>211776287.8207681</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>38084932.0</t>
+          <t>49106509.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>35331650.4</v>
+        <v>38566967.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>52705529.4</t>
+          <t>52615128.9</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>195762947.24</v>
+        <v>195992723.02</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-17373879</t>
+          <t>-14048161</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-15131506.2497225</t>
+          <t>-14385747.31257303</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-11946152.49717921</t>
+          <t>-10284073.15825091</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>38084932.0</t>
+          <t>49106509.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>21.50</t>
+          <t>15.75</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>138.52</t>
+          <t>139.4</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>9598</t>
+          <t>9636</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9011,17 +9011,17 @@
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1646.332</t>
+          <t>1579.409</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-31.86</t>
+          <t>-32.96</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,58 +9189,58 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.07</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>13.77</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>6.62</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>25.22</v>
+        <v>25.06</v>
       </c>
       <c r="AN21" t="n">
-        <v>25.95</v>
+        <v>25.98</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>24.37</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-54.01</t>
+          <t>-39.74</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-107.94</t>
+          <t>-108.82</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>212022541.2264957</t>
+          <t>211776287.8207681</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>38591667.0</t>
+          <t>38084932.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>35280331.2</v>
+        <v>35331650.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>51774555.3</t>
+          <t>52705529.4</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>196053683.56</v>
+        <v>195762947.24</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-16494224</t>
+          <t>-17373879</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-15710661.47745765</t>
+          <t>-15131506.2497225</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-12713019.99932038</t>
+          <t>-11946152.49717921</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>38591667.0</t>
+          <t>38084932.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>16.00</t>
+          <t>21.50</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,17 +9371,17 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>138.52</t>
+          <t>139.4</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>9598</t>
+          <t>9636</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1604.993</t>
+          <t>1646.332</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,72 +9498,72 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>8.84</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-1.33</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-31.86</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
           <t>23.85</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>5.92</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>-1.31</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>-18.78</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,58 +9629,58 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>13.77</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>25.44</v>
+        <v>25.22</v>
       </c>
       <c r="AN22" t="n">
-        <v>25.96</v>
+        <v>25.95</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-27.44</t>
+          <t>-54.01</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-106.87</t>
+          <t>-107.94</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,48 +9700,48 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>212022541.2264957</t>
+          <t>211776287.8207681</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>38724107.0</t>
+          <t>38591667.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>43361451.2</v>
+        <v>35280331.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>53384515.1</t>
+          <t>51774555.3</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>197488634.64</v>
+        <v>196053683.56</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-10023063</t>
+          <t>-16494224</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-16255687.20075533</t>
+          <t>-15710661.47745765</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-13408801.60954632</t>
+          <t>-12713019.99932038</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>38724107.0</t>
+          <t>38591667.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>16.00</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>138.52</t>
+          <t>139.4</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>9598</t>
+          <t>9636</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9903,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1126.956</t>
+          <t>1604.993</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,74 +9928,74 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>6.29</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-1.33</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-18.78</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
           <t>24.9</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-1.31</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>21.00</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>24.9</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
       <c r="T23" t="inlineStr">
         <is>
           <t>24.8</t>
@@ -10008,14 +10008,14 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
+          <t>-4.22</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>4.40</t>
-        </is>
-      </c>
       <c r="X23" t="inlineStr">
         <is>
           <t>-9.29</t>
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,68 +10049,68 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>25.56</v>
+        <v>25.44</v>
       </c>
       <c r="AN23" t="n">
-        <v>25.94</v>
+        <v>25.96</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>-27.44</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-106.40</t>
+          <t>-106.87</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>212022541.2264957</t>
+          <t>211776287.8207681</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>28327621.0</t>
+          <t>38724107.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>64293510</v>
+        <v>43361451.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>53134957.6</t>
+          <t>53384515.1</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>197699079.6</v>
+        <v>197488634.64</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>11158552</t>
+          <t>-10023063</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-16773302.76279333</t>
+          <t>-16255687.20075533</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-13938079.56667101</t>
+          <t>-13408801.60954632</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>28327621.0</t>
+          <t>38724107.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>24.50</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>138.52</t>
+          <t>139.4</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>9598</t>
+          <t>9636</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/ITO導電基板.xlsx
+++ b/Result/checksun_type/ITO導電基板.xlsx
@@ -883,7 +883,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>-22.22</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1024,63 +1024,63 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>38.71</t>
+          <t>48.39</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>52.69</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>22.88</v>
+        <v>22.98</v>
       </c>
       <c r="AN2" t="n">
-        <v>23.22</v>
+        <v>23.19</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>78.99</t>
+          <t>48.56</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-94.95</t>
+          <t>-94.25</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>82183.42105263157</t>
+          <t>82079.0859375</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>5739.0</t>
+          <t>5821.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>9625.6</v>
+        <v>6127.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>7974.8</t>
+          <t>7878.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>7390.28</v>
+        <v>7309.38</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>-1750</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>279.4693411980216</t>
+          <t>138.9183568647506</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-522.2695898581487</t>
+          <t>-634.1120569682398</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>5739.0</t>
+          <t>5821.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,7 +1444,7 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1454,44 +1454,44 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>38.71</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>68.82</t>
+          <t>52.69</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
+          <t>-1.99</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>-1.46</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>-1.90</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>3.92</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>-1.9</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>-1.79</t>
-        </is>
-      </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.67</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>22.8</v>
+        <v>22.88</v>
       </c>
       <c r="AN3" t="n">
-        <v>23.25</v>
+        <v>23.22</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1500,17 +1500,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>154.33</t>
+          <t>78.99</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-95.95</t>
+          <t>-94.95</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>82183.42105263157</t>
+          <t>82079.0859375</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4584.0</t>
+          <t>5739.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>9280.4</v>
+        <v>9625.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>8403.9</t>
+          <t>7974.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>7418.64</v>
+        <v>7390.28</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>425.2400559355071</t>
+          <t>279.4693411980216</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-335.0564372059416</t>
+          <t>-522.2695898581487</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>4584.0</t>
+          <t>5739.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>23.2</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>23.25</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-7.74</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,7 +1874,7 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1884,63 +1884,63 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>77.42</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>88.17</t>
+          <t>68.82</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>22.74</v>
+        <v>22.8</v>
       </c>
       <c r="AN4" t="n">
-        <v>23.26</v>
+        <v>23.25</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.67</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>362.90</t>
+          <t>154.33</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-97.51</t>
+          <t>-95.95</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>82183.42105263157</t>
+          <t>82079.0859375</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>5793.0</t>
+          <t>4584.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>9462.4</v>
+        <v>9280.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>8873.4</t>
+          <t>8403.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>7472.64</v>
+        <v>7418.64</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>876</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>563.475781961225</t>
+          <t>425.2400559355071</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>68.1072250545676</t>
+          <t>-335.0564372059416</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>5793.0</t>
+          <t>4584.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>361.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,79 +2188,79 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-1.93</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>6.64</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>23.95</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-3.23</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-1.48</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-18.48</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>23.0</t>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,7 +2304,7 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -2314,63 +2314,63 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>77.42</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>82.37</t>
+          <t>88.17</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>22.66</v>
+        <v>22.74</v>
       </c>
       <c r="AN5" t="n">
         <v>23.26</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>4280.47</t>
+          <t>362.90</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-99.77</t>
+          <t>-97.51</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>82183.42105263157</t>
+          <t>82079.0859375</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>9716.799999999999</v>
+        <v>9462.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>11919.9</t>
+          <t>8873.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>7436.54</v>
+        <v>7472.64</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2203</t>
+          <t>589</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>653.54279230789</t>
+          <t>563.475781961225</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>512.0871988176314</t>
+          <t>68.1072250545676</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
           <t>24.05</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>24.45</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>361.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-35.31</t>
+          <t>-18.48</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,7 +2734,7 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2744,63 +2744,63 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>72.03</t>
+          <t>82.37</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>22.57</v>
+        <v>22.66</v>
       </c>
       <c r="AN6" t="n">
         <v>23.26</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>430.70</t>
+          <t>4280.47</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-99.77</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>82183.42105263157</t>
+          <t>82079.0859375</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>9629.200000000001</v>
+        <v>9716.799999999999</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>14884.2</t>
+          <t>11919.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>7449.74</v>
+        <v>7436.54</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-5255</t>
+          <t>-2203</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>679.2619911243006</t>
+          <t>653.54279230789</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>816.5911899499497</t>
+          <t>512.0871988176314</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-51.37</t>
+          <t>-35.31</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,7 +3164,7 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -3174,63 +3174,63 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>22.5</v>
+        <v>22.57</v>
       </c>
       <c r="AN7" t="n">
         <v>23.26</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.61</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>160.83</t>
+          <t>430.70</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.65</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>82183.42105263157</t>
+          <t>82079.0859375</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>6324</v>
+        <v>9629.200000000001</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>13005.4</t>
+          <t>14884.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>7283.74</v>
+        <v>7449.74</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-6681</t>
+          <t>-5255</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>654.2930458832735</t>
+          <t>679.2619911243006</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-343.1385080735217</t>
+          <t>816.5911899499497</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-41.51</t>
+          <t>-51.37</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,7 +3594,7 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -3604,63 +3604,63 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>64.93</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>22.46</v>
+        <v>22.5</v>
       </c>
       <c r="AN8" t="n">
-        <v>23.28</v>
+        <v>23.26</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>23.61</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>115.43</t>
+          <t>160.83</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-106.52</t>
+          <t>-104.65</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>82183.42105263157</t>
+          <t>82079.0859375</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>7527.4</v>
+        <v>6324</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>12868.8</t>
+          <t>13005.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>7378.32</v>
+        <v>7283.74</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-5341</t>
+          <t>-6681</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>835.6442375117817</t>
+          <t>654.2930458832735</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>80.10972718128687</t>
+          <t>-343.1385080735217</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-10.70</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-34.19</t>
+          <t>-41.51</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-10.32</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,7 +4024,7 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -4034,63 +4034,63 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>64.93</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>22.45</v>
+        <v>22.46</v>
       </c>
       <c r="AN9" t="n">
-        <v>23.33</v>
+        <v>23.28</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>108.28</t>
+          <t>115.43</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-108.40</t>
+          <t>-106.52</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>82183.42105263157</t>
+          <t>82079.0859375</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>8284.4</v>
+        <v>7527.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>12587.7</t>
+          <t>12868.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>7563.22</v>
+        <v>7378.32</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-4303</t>
+          <t>-5341</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>973.0141484809627</t>
+          <t>835.6442375117817</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>523.2104301459694</t>
+          <t>80.10972718128687</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-12.06</t>
+          <t>-10.70</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>-34.19</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-10.32</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,7 +4454,7 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -4464,63 +4464,63 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>81.76</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>22.46</v>
+        <v>22.45</v>
       </c>
       <c r="AN10" t="n">
-        <v>23.38</v>
+        <v>23.33</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>119.34</t>
+          <t>108.28</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-108.40</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>82183.42105263157</t>
+          <t>82079.0859375</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>14123</v>
+        <v>8284.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>12216.7</t>
+          <t>12587.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>7629.54</v>
+        <v>7563.22</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>-4303</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1054.796642723689</t>
+          <t>973.0141484809627</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>969.2039190188734</t>
+          <t>523.2104301459694</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-12.06</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>293.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,84 +4768,84 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>15.60</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.86</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-1.48</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>73.69</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,7 +4884,7 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -4894,264 +4894,264 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>81.76</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
+          <t>23.49</t>
+        </is>
+      </c>
+      <c r="AM11" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>23.57</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>119.34</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-110.67</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>82079.0859375</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="n">
+        <v>14123</v>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>12216.7</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>7629.54</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>1054.796642723689</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>969.2039190188734</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>-8.37</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>-13.42998910113004</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>-25.43417574544826</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>-6.333574654154932</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>106.14</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>19.70%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>90.37</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>1599</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>安可-光電業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>光電業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>23.45</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>24.05</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="AM11" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>23.42</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>92.50</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-113.86</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>82183.42105263157</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="n">
-        <v>20139.2</v>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>11594.6</t>
-        </is>
-      </c>
-      <c r="AZ11" t="n">
-        <v>7648.36</v>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>8544</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>1070.358956124564</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>1443.473048872349</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>-10.51</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>-13.42998910113004</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>-25.43417574544826</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>-6.333574654154932</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>105.45</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>19.70%</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>-0.85%</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>88.59</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>1588</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>安可-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>光電業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>23.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>426.0</t>
+          <t>293.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>75.73</t>
+          <t>73.69</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,7 +5314,7 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -5324,63 +5324,63 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>91.82</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>22.42</v>
+        <v>22.43</v>
       </c>
       <c r="AN12" t="n">
-        <v>23.46</v>
+        <v>23.42</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>87.14</t>
+          <t>92.50</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-113.86</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>82183.42105263157</t>
+          <t>82079.0859375</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>19686.8</v>
+        <v>20139.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>11202.7</t>
+          <t>11594.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>8102.12</v>
+        <v>7648.36</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>1002.520030170422</t>
+          <t>1070.358956124564</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>2227.590625489014</t>
+          <t>1443.473048872349</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1020.161</t>
+          <t>2931.608</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,17 +5744,17 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>98.08</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -5764,53 +5764,53 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.02</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>25.07</t>
+          <t>25.48</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>24.55</v>
+        <v>24.67</v>
       </c>
       <c r="AN13" t="n">
-        <v>25.85</v>
+        <v>25.73</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>24.84</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>59.31</t>
+          <t>99.06</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-109.81</t>
+          <t>-107.86</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>211776287.8207681</t>
+          <t>211640073.8607954</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>25937598.0</t>
+          <t>77254440.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>43012919.8</v>
+        <v>44584134.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>41513618.0</t>
+          <t>45379895.3</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>145472052.94</v>
+        <v>130068528.7</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>1499301</t>
+          <t>-795760</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-8928176.949495498</t>
+          <t>-7989876.229028531</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-6392879.709919482</t>
+          <t>-2829222.266460218</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>25937598.0</t>
+          <t>77254440.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>31.50</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>139.4</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>9636</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1109.996</t>
+          <t>1020.161</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>7.37</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>6.29</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>94.23</t>
+          <t>98.08</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>96.41</t>
+          <t>97.44</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>25.07</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>24.5</v>
+        <v>24.55</v>
       </c>
       <c r="AN14" t="n">
-        <v>25.92</v>
+        <v>25.85</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>24.78</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>42.52</t>
+          <t>59.31</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-111.26</t>
+          <t>-109.81</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>211776287.8207681</t>
+          <t>211640073.8607954</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>28260089.0</t>
+          <t>25937598.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>45946725</v>
+        <v>43012919.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>42792268.9</t>
+          <t>41513618.0</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>160844320.62</v>
+        <v>145472052.94</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>3154456</t>
+          <t>1499301</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-9389140.083963865</t>
+          <t>-8928176.949495498</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-5757268.710935593</t>
+          <t>-6392879.709919482</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>28260089.0</t>
+          <t>25937598.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>139.4</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>9636</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>25.95</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1979.388</t>
+          <t>1109.996</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>7.37</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.23</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>85.93</t>
+          <t>96.41</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5.78</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.69</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>24.48</v>
+        <v>24.5</v>
       </c>
       <c r="AN15" t="n">
-        <v>25.98</v>
+        <v>25.92</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>25.69</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-112.46</t>
+          <t>-111.26</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>211776287.8207681</t>
+          <t>211640073.8607954</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>50208048.0</t>
+          <t>28260089.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>47031077</v>
+        <v>45946725</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>42799022.1</t>
+          <t>42792268.9</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>181073786.02</v>
+        <v>160844320.62</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>4232054</t>
+          <t>3154456</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-10049480.33360537</t>
+          <t>-9389140.083963865</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-4892474.579853766</t>
+          <t>-5757268.710935593</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>50208048.0</t>
+          <t>28260089.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>27.50</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>139.4</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>9636</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.95</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1677.95</t>
+          <t>1979.388</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,79 +6918,79 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>9.89</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
           <t>24.8</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-1.33</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>13.97</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>24.8</t>
-        </is>
-      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>27.45</t>
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>6.92</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>60.48</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-6.15</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>24.41</v>
+        <v>24.48</v>
       </c>
       <c r="AN16" t="n">
-        <v>26.01</v>
+        <v>25.98</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>24.59</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>25.69</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-113.26</t>
+          <t>-112.46</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>211776287.8207681</t>
+          <t>211640073.8607954</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>41260499.0</t>
+          <t>50208048.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>46810769.2</v>
+        <v>47031077</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>41071209.8</t>
+          <t>42799022.1</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>184113554.72</v>
+        <v>181073786.02</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>5739559</t>
+          <t>4232054</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-10987117.74337839</t>
+          <t>-10049480.33360537</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-5833890.193313524</t>
+          <t>-4892474.579853766</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>41260499.0</t>
+          <t>50208048.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>24.00</t>
+          <t>27.50</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,17 +7221,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>139.4</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>9636</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7323,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2804.104</t>
+          <t>1677.95</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>13.38</t>
+          <t>13.97</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,68 +7464,68 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>62.79</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>60.48</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-6.14</t>
+          <t>-6.15</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>23.73</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>24.42</v>
+        <v>24.41</v>
       </c>
       <c r="AN17" t="n">
         <v>26.01</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>24.59</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-18.96</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-113.29</t>
+          <t>-113.26</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>211776287.8207681</t>
+          <t>211640073.8607954</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>69398365.0</t>
+          <t>41260499.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>46175655.8</v>
+        <v>46810769.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>40727993.5</t>
+          <t>41071209.8</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>194676121.56</v>
+        <v>184113554.72</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>5447662</t>
+          <t>5739559</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-11924068.20702655</t>
+          <t>-10987117.74337839</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-6011750.455637693</t>
+          <t>-5833890.193313524</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>69398365.0</t>
+          <t>41260499.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>21.25</t>
+          <t>24.00</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>139.4</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>9636</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>24.25</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1738.819</t>
+          <t>2804.104</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>13.38</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>62.79</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>28.81</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-6.14</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>24.49</v>
+        <v>24.42</v>
       </c>
       <c r="AN18" t="n">
-        <v>25.98</v>
+        <v>26.01</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>24.47</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-37.74</t>
+          <t>-18.96</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-112.66</t>
+          <t>-113.29</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>211776287.8207681</t>
+          <t>211640073.8607954</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>40606624.0</t>
+          <t>69398365.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>40014316.2</v>
+        <v>46175655.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>41687883.7</t>
+          <t>40727993.5</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>195169236.84</v>
+        <v>194676121.56</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-1673567</t>
+          <t>5447662</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-12999035.07091543</t>
+          <t>-11924068.20702655</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-9065902.528399438</t>
+          <t>-6011750.455637693</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>40606624.0</t>
+          <t>69398365.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>21.25</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>139.4</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>9636</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1462.411</t>
+          <t>1738.819</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>10.46</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-23.72</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,63 +8324,63 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>6.30</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>24.64</v>
+        <v>24.49</v>
       </c>
       <c r="AN19" t="n">
-        <v>25.97</v>
+        <v>25.98</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24.47</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-50.35</t>
+          <t>-37.74</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-111.47</t>
+          <t>-112.66</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>211776287.8207681</t>
+          <t>211640073.8607954</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>33681849.0</t>
+          <t>40606624.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>39637812.8</v>
+        <v>40014316.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>51965661.4</t>
+          <t>41687883.7</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>195984000.1</v>
+        <v>195169236.84</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-12327848</t>
+          <t>-1673567</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-13714150.07864561</t>
+          <t>-12999035.07091543</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-10020365.29204483</t>
+          <t>-9065902.528399438</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>33681849.0</t>
+          <t>40606624.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>14.50</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>139.4</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>9636</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
+          <t>23.05</t>
+        </is>
+      </c>
+      <c r="CG19" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>22.8</t>
-        </is>
-      </c>
-      <c r="CG19" t="inlineStr">
-        <is>
-          <t>22.9</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2112.165</t>
+          <t>1462.411</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>12.93</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-26.70</t>
+          <t>-23.72</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>6.30</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>24.85</v>
+        <v>24.64</v>
       </c>
       <c r="AN20" t="n">
-        <v>25.98</v>
+        <v>25.97</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-48.21</t>
+          <t>-50.35</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-110.02</t>
+          <t>-111.47</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>211776287.8207681</t>
+          <t>211640073.8607954</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>49106509.0</t>
+          <t>33681849.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>38566967.2</v>
+        <v>39637812.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>52615128.9</t>
+          <t>51965661.4</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>195992723.02</v>
+        <v>195984000.1</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-14048161</t>
+          <t>-12327848</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-14385747.31257303</t>
+          <t>-13714150.07864561</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-10284073.15825091</t>
+          <t>-10020365.29204483</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>49106509.0</t>
+          <t>33681849.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>15.75</t>
+          <t>14.50</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>139.4</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>9636</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1579.409</t>
+          <t>2112.165</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>11.98</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-32.96</t>
+          <t>-26.70</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,17 +9184,17 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>36.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-3.90</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>6.62</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>24.26</t>
+          <t>23.88</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>25.06</v>
+        <v>24.85</v>
       </c>
       <c r="AN21" t="n">
         <v>25.98</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t